--- a/VerveStacks_EST/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
+++ b/VerveStacks_EST/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29530"/>
   <workbookPr updateLinks="never"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\VerveStacks\assumptions\VerveStacks_ISO_template\SubRES_Tmpl\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\PycharmProjects\ee-times\VerveStacks_EST\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4C48DD9-DED7-479B-A74E-1DB16C47A208}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43D1AB6C-6213-44E6-95F9-17D6D986C9C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28702" yWindow="-98" windowWidth="28995" windowHeight="15675" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="AVA" sheetId="6" r:id="rId1"/>
@@ -591,14 +591,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{268E9BAB-B98F-4B82-9042-51EABC9ED525}">
   <dimension ref="B3:C5"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="3" spans="2:3" x14ac:dyDescent="0.45">
+    <row r="3" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B3" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="4" spans="2:3" x14ac:dyDescent="0.45">
+    <row r="4" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B4" t="s">
         <v>21</v>
       </c>
@@ -606,7 +606,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="5" spans="2:3" x14ac:dyDescent="0.45">
+    <row r="5" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B5" t="s">
         <v>59</v>
       </c>
@@ -622,24 +622,24 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E3954DD3-0F24-46DF-B268-7A98442D0282}">
   <dimension ref="A1:O13"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="7.265625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="5.73046875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.59765625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="29.796875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.59765625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="7.59765625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="8.6640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15.19921875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="7.46484375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="4.9296875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="3.86328125" bestFit="1" customWidth="1"/>
-    <col min="12" max="14" width="4.73046875" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="5.1328125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.26953125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="5.7265625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.6328125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="29.81640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.6328125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="7.6328125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.6328125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.1796875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="7.453125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="4.90625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="3.81640625" bestFit="1" customWidth="1"/>
+    <col min="12" max="14" width="4.7265625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="5.08984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>32</v>
       </c>
@@ -686,7 +686,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>44</v>
       </c>
@@ -733,7 +733,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>44</v>
       </c>
@@ -780,7 +780,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>44</v>
       </c>
@@ -827,7 +827,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>44</v>
       </c>
@@ -874,7 +874,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>44</v>
       </c>
@@ -921,7 +921,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>44</v>
       </c>
@@ -968,7 +968,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>44</v>
       </c>
@@ -1015,7 +1015,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>44</v>
       </c>
@@ -1062,7 +1062,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>44</v>
       </c>
@@ -1109,7 +1109,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>44</v>
       </c>
@@ -1156,7 +1156,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>44</v>
       </c>
@@ -1203,7 +1203,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>44</v>
       </c>
@@ -1258,21 +1258,22 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="C4:X50"/>
-  <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="3" max="3" width="13.3984375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.73046875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.36328125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.7265625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="11" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="4.86328125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="10.3984375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="5.3984375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="5.73046875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="4.81640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.36328125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="5.36328125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="5.7265625" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="5" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="6.265625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="4.265625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="6.26953125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="4.26953125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="11.7265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="4" spans="3:24" x14ac:dyDescent="0.45">
+    <row r="4" spans="3:24" x14ac:dyDescent="0.35">
       <c r="C4" t="s">
         <v>4</v>
       </c>
@@ -1286,7 +1287,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="5" spans="3:24" x14ac:dyDescent="0.45">
+    <row r="5" spans="3:24" x14ac:dyDescent="0.35">
       <c r="C5" t="s">
         <v>3</v>
       </c>
@@ -1312,7 +1313,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="6" spans="3:24" x14ac:dyDescent="0.45">
+    <row r="6" spans="3:24" x14ac:dyDescent="0.35">
       <c r="D6" t="s">
         <v>6</v>
       </c>
@@ -1332,7 +1333,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="7" spans="3:24" x14ac:dyDescent="0.45">
+    <row r="7" spans="3:24" x14ac:dyDescent="0.35">
       <c r="D7" t="s">
         <v>7</v>
       </c>
@@ -1352,7 +1353,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="8" spans="3:24" x14ac:dyDescent="0.45">
+    <row r="8" spans="3:24" x14ac:dyDescent="0.35">
       <c r="D8" t="s">
         <v>8</v>
       </c>
@@ -1363,7 +1364,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="3:24" x14ac:dyDescent="0.45">
+    <row r="9" spans="3:24" x14ac:dyDescent="0.35">
       <c r="D9" t="s">
         <v>9</v>
       </c>
@@ -1374,7 +1375,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="10" spans="3:24" x14ac:dyDescent="0.45">
+    <row r="10" spans="3:24" x14ac:dyDescent="0.35">
       <c r="D10" t="s">
         <v>10</v>
       </c>
@@ -1385,7 +1386,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="11" spans="3:24" x14ac:dyDescent="0.45">
+    <row r="11" spans="3:24" x14ac:dyDescent="0.35">
       <c r="D11" t="s">
         <v>6</v>
       </c>
@@ -1399,7 +1400,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="12" spans="3:24" x14ac:dyDescent="0.45">
+    <row r="12" spans="3:24" x14ac:dyDescent="0.35">
       <c r="P12" s="2" t="s">
         <v>25</v>
       </c>
@@ -1416,7 +1417,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="13" spans="3:24" x14ac:dyDescent="0.45">
+    <row r="13" spans="3:24" x14ac:dyDescent="0.35">
       <c r="C13" t="s">
         <v>4</v>
       </c>
@@ -1443,7 +1444,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="14" spans="3:24" x14ac:dyDescent="0.45">
+    <row r="14" spans="3:24" x14ac:dyDescent="0.35">
       <c r="C14" t="s">
         <v>3</v>
       </c>
@@ -1482,7 +1483,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="15" spans="3:24" x14ac:dyDescent="0.45">
+    <row r="15" spans="3:24" x14ac:dyDescent="0.35">
       <c r="C15" t="s">
         <v>11</v>
       </c>
@@ -1521,7 +1522,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="16" spans="3:24" x14ac:dyDescent="0.45">
+    <row r="16" spans="3:24" x14ac:dyDescent="0.35">
       <c r="D16" t="s">
         <v>6</v>
       </c>
@@ -1554,7 +1555,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="17" spans="3:24" x14ac:dyDescent="0.45">
+    <row r="17" spans="3:24" x14ac:dyDescent="0.35">
       <c r="D17" t="s">
         <v>13</v>
       </c>
@@ -1562,7 +1563,7 @@
         <v>55</v>
       </c>
       <c r="G17">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="P17" s="2" t="s">
         <v>30</v>
@@ -1589,7 +1590,7 @@
         <v>EN[_]Hydro*</v>
       </c>
     </row>
-    <row r="18" spans="3:24" x14ac:dyDescent="0.45">
+    <row r="18" spans="3:24" x14ac:dyDescent="0.35">
       <c r="D18" t="s">
         <v>13</v>
       </c>
@@ -1624,7 +1625,7 @@
         <v>E[_]SPV*</v>
       </c>
     </row>
-    <row r="19" spans="3:24" x14ac:dyDescent="0.45">
+    <row r="19" spans="3:24" x14ac:dyDescent="0.35">
       <c r="D19" t="s">
         <v>7</v>
       </c>
@@ -1659,7 +1660,7 @@
         <v>E[_]WOF*</v>
       </c>
     </row>
-    <row r="20" spans="3:24" x14ac:dyDescent="0.45">
+    <row r="20" spans="3:24" x14ac:dyDescent="0.35">
       <c r="D20" t="s">
         <v>8</v>
       </c>
@@ -1694,7 +1695,7 @@
         <v>E[_]WON*</v>
       </c>
     </row>
-    <row r="21" spans="3:24" x14ac:dyDescent="0.45">
+    <row r="21" spans="3:24" x14ac:dyDescent="0.35">
       <c r="D21" t="s">
         <v>9</v>
       </c>
@@ -1729,7 +1730,7 @@
         <v>EN[_]Hydro*</v>
       </c>
     </row>
-    <row r="22" spans="3:24" x14ac:dyDescent="0.45">
+    <row r="22" spans="3:24" x14ac:dyDescent="0.35">
       <c r="D22" t="s">
         <v>10</v>
       </c>
@@ -1764,18 +1765,18 @@
         <v>E[_]SPV*</v>
       </c>
     </row>
-    <row r="23" spans="3:24" x14ac:dyDescent="0.45">
+    <row r="23" spans="3:24" x14ac:dyDescent="0.35">
       <c r="P23" s="2" t="s">
         <v>31</v>
       </c>
       <c r="Q23" s="2">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="R23" s="2">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="S23" s="2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T23" t="str">
         <f t="shared" si="2"/>
@@ -1790,7 +1791,7 @@
         <v>E[_]WOF*</v>
       </c>
     </row>
-    <row r="24" spans="3:24" x14ac:dyDescent="0.45">
+    <row r="24" spans="3:24" x14ac:dyDescent="0.35">
       <c r="P24" s="2" t="s">
         <v>31</v>
       </c>
@@ -1816,12 +1817,12 @@
         <v>E[_]WON*</v>
       </c>
     </row>
-    <row r="27" spans="3:24" x14ac:dyDescent="0.45">
+    <row r="27" spans="3:24" x14ac:dyDescent="0.35">
       <c r="C27" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="28" spans="3:24" x14ac:dyDescent="0.45">
+    <row r="28" spans="3:24" x14ac:dyDescent="0.35">
       <c r="C28" t="s">
         <v>16</v>
       </c>
@@ -1838,7 +1839,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="29" spans="3:24" x14ac:dyDescent="0.45">
+    <row r="29" spans="3:24" x14ac:dyDescent="0.35">
       <c r="C29" t="s">
         <v>17</v>
       </c>
@@ -1849,7 +1850,7 @@
         <v>8.76</v>
       </c>
     </row>
-    <row r="30" spans="3:24" x14ac:dyDescent="0.45">
+    <row r="30" spans="3:24" x14ac:dyDescent="0.35">
       <c r="C30" t="s">
         <v>53</v>
       </c>
@@ -1860,7 +1861,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="3:24" x14ac:dyDescent="0.45">
+    <row r="31" spans="3:24" x14ac:dyDescent="0.35">
       <c r="C31" t="s">
         <v>17</v>
       </c>
@@ -1871,7 +1872,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="32" spans="3:24" x14ac:dyDescent="0.45">
+    <row r="32" spans="3:24" x14ac:dyDescent="0.35">
       <c r="D32" t="s">
         <v>7</v>
       </c>
@@ -1882,7 +1883,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="33" spans="3:7" x14ac:dyDescent="0.45">
+    <row r="33" spans="3:7" x14ac:dyDescent="0.35">
       <c r="D33" t="s">
         <v>10</v>
       </c>
@@ -1893,7 +1894,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="34" spans="3:7" x14ac:dyDescent="0.45">
+    <row r="34" spans="3:7" x14ac:dyDescent="0.35">
       <c r="D34" t="s">
         <v>9</v>
       </c>
@@ -1904,7 +1905,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="3:7" x14ac:dyDescent="0.45">
+    <row r="35" spans="3:7" x14ac:dyDescent="0.35">
       <c r="C35" t="s">
         <v>17</v>
       </c>
@@ -1918,12 +1919,12 @@
         <v>3</v>
       </c>
     </row>
-    <row r="38" spans="3:7" x14ac:dyDescent="0.45">
+    <row r="38" spans="3:7" x14ac:dyDescent="0.35">
       <c r="C38" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="39" spans="3:7" x14ac:dyDescent="0.45">
+    <row r="39" spans="3:7" x14ac:dyDescent="0.35">
       <c r="C39" t="s">
         <v>21</v>
       </c>
@@ -1934,7 +1935,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="40" spans="3:7" x14ac:dyDescent="0.45">
+    <row r="40" spans="3:7" x14ac:dyDescent="0.35">
       <c r="C40" t="s">
         <v>14</v>
       </c>
@@ -1945,7 +1946,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="41" spans="3:7" x14ac:dyDescent="0.45">
+    <row r="41" spans="3:7" x14ac:dyDescent="0.35">
       <c r="C41" t="s">
         <v>15</v>
       </c>
@@ -1956,7 +1957,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="42" spans="3:7" x14ac:dyDescent="0.45">
+    <row r="42" spans="3:7" x14ac:dyDescent="0.35">
       <c r="C42" t="s">
         <v>57</v>
       </c>
@@ -1967,7 +1968,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="43" spans="3:7" x14ac:dyDescent="0.45">
+    <row r="43" spans="3:7" x14ac:dyDescent="0.35">
       <c r="C43" t="s">
         <v>55</v>
       </c>
@@ -1978,7 +1979,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="44" spans="3:7" x14ac:dyDescent="0.45">
+    <row r="44" spans="3:7" x14ac:dyDescent="0.35">
       <c r="C44" t="s">
         <v>56</v>
       </c>
@@ -1989,12 +1990,12 @@
         <v>24</v>
       </c>
     </row>
-    <row r="47" spans="3:7" x14ac:dyDescent="0.45">
+    <row r="47" spans="3:7" x14ac:dyDescent="0.35">
       <c r="C47" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="48" spans="3:7" x14ac:dyDescent="0.45">
+    <row r="48" spans="3:7" x14ac:dyDescent="0.35">
       <c r="C48" t="s">
         <v>1</v>
       </c>
@@ -2008,7 +2009,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="49" spans="3:6" x14ac:dyDescent="0.45">
+    <row r="49" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C49" t="s">
         <v>64</v>
       </c>
@@ -2022,7 +2023,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="50" spans="3:6" x14ac:dyDescent="0.45">
+    <row r="50" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C50" t="s">
         <v>69</v>
       </c>

--- a/VerveStacks_EST/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
+++ b/VerveStacks_EST/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\PycharmProjects\ee-times\VerveStacks_EST\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43D1AB6C-6213-44E6-95F9-17D6D986C9C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92715A5D-2C44-47C1-A5A4-71CC370EF446}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-38520" yWindow="-5220" windowWidth="38640" windowHeight="21120" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="AVA" sheetId="6" r:id="rId1"/>
@@ -591,14 +591,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{268E9BAB-B98F-4B82-9042-51EABC9ED525}">
   <dimension ref="B3:C5"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="3" spans="2:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="4" spans="2:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
         <v>21</v>
       </c>
@@ -606,7 +606,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="5" spans="2:3" x14ac:dyDescent="0.35">
+    <row r="5" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
         <v>59</v>
       </c>
@@ -622,24 +622,24 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E3954DD3-0F24-46DF-B268-7A98442D0282}">
   <dimension ref="A1:O13"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="7.26953125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="5.7265625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.6328125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="29.81640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.6328125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="7.6328125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="8.6328125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15.1796875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="7.453125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="4.90625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="3.81640625" bestFit="1" customWidth="1"/>
-    <col min="12" max="14" width="4.7265625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="5.08984375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="5.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="29.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="7.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.5703125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="7.42578125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="4.85546875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="3.85546875" bestFit="1" customWidth="1"/>
+    <col min="12" max="14" width="4.7109375" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="5.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>32</v>
       </c>
@@ -686,7 +686,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>44</v>
       </c>
@@ -733,7 +733,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>44</v>
       </c>
@@ -780,7 +780,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>44</v>
       </c>
@@ -827,7 +827,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>44</v>
       </c>
@@ -874,7 +874,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>44</v>
       </c>
@@ -921,7 +921,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>44</v>
       </c>
@@ -968,7 +968,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>44</v>
       </c>
@@ -1015,7 +1015,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>44</v>
       </c>
@@ -1062,7 +1062,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>44</v>
       </c>
@@ -1109,7 +1109,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>44</v>
       </c>
@@ -1156,7 +1156,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>44</v>
       </c>
@@ -1203,7 +1203,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>44</v>
       </c>
@@ -1258,22 +1258,22 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="C4:X50"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="3" max="3" width="13.36328125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.7265625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.7109375" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="11" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="4.81640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="10.36328125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="5.36328125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="5.7265625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="41.28515625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="5.42578125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="5.7109375" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="5" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="6.26953125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="4.26953125" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="11.7265625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="6.28515625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="4.28515625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="11.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="4" spans="3:24" x14ac:dyDescent="0.35">
+    <row r="4" spans="3:24" x14ac:dyDescent="0.25">
       <c r="C4" t="s">
         <v>4</v>
       </c>
@@ -1287,7 +1287,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="5" spans="3:24" x14ac:dyDescent="0.35">
+    <row r="5" spans="3:24" x14ac:dyDescent="0.25">
       <c r="C5" t="s">
         <v>3</v>
       </c>
@@ -1313,7 +1313,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="6" spans="3:24" x14ac:dyDescent="0.35">
+    <row r="6" spans="3:24" x14ac:dyDescent="0.25">
       <c r="D6" t="s">
         <v>6</v>
       </c>
@@ -1333,7 +1333,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="7" spans="3:24" x14ac:dyDescent="0.35">
+    <row r="7" spans="3:24" x14ac:dyDescent="0.25">
       <c r="D7" t="s">
         <v>7</v>
       </c>
@@ -1353,7 +1353,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="8" spans="3:24" x14ac:dyDescent="0.35">
+    <row r="8" spans="3:24" x14ac:dyDescent="0.25">
       <c r="D8" t="s">
         <v>8</v>
       </c>
@@ -1364,7 +1364,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="3:24" x14ac:dyDescent="0.35">
+    <row r="9" spans="3:24" x14ac:dyDescent="0.25">
       <c r="D9" t="s">
         <v>9</v>
       </c>
@@ -1375,7 +1375,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="10" spans="3:24" x14ac:dyDescent="0.35">
+    <row r="10" spans="3:24" x14ac:dyDescent="0.25">
       <c r="D10" t="s">
         <v>10</v>
       </c>
@@ -1386,7 +1386,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="11" spans="3:24" x14ac:dyDescent="0.35">
+    <row r="11" spans="3:24" x14ac:dyDescent="0.25">
       <c r="D11" t="s">
         <v>6</v>
       </c>
@@ -1400,7 +1400,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="12" spans="3:24" x14ac:dyDescent="0.35">
+    <row r="12" spans="3:24" x14ac:dyDescent="0.25">
       <c r="P12" s="2" t="s">
         <v>25</v>
       </c>
@@ -1417,7 +1417,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="13" spans="3:24" x14ac:dyDescent="0.35">
+    <row r="13" spans="3:24" x14ac:dyDescent="0.25">
       <c r="C13" t="s">
         <v>4</v>
       </c>
@@ -1444,7 +1444,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="14" spans="3:24" x14ac:dyDescent="0.35">
+    <row r="14" spans="3:24" x14ac:dyDescent="0.25">
       <c r="C14" t="s">
         <v>3</v>
       </c>
@@ -1483,7 +1483,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="15" spans="3:24" x14ac:dyDescent="0.35">
+    <row r="15" spans="3:24" x14ac:dyDescent="0.25">
       <c r="C15" t="s">
         <v>11</v>
       </c>
@@ -1522,7 +1522,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="16" spans="3:24" x14ac:dyDescent="0.35">
+    <row r="16" spans="3:24" x14ac:dyDescent="0.25">
       <c r="D16" t="s">
         <v>6</v>
       </c>
@@ -1555,7 +1555,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="17" spans="3:24" x14ac:dyDescent="0.35">
+    <row r="17" spans="3:24" x14ac:dyDescent="0.25">
       <c r="D17" t="s">
         <v>13</v>
       </c>
@@ -1590,7 +1590,7 @@
         <v>EN[_]Hydro*</v>
       </c>
     </row>
-    <row r="18" spans="3:24" x14ac:dyDescent="0.35">
+    <row r="18" spans="3:24" x14ac:dyDescent="0.25">
       <c r="D18" t="s">
         <v>13</v>
       </c>
@@ -1625,7 +1625,7 @@
         <v>E[_]SPV*</v>
       </c>
     </row>
-    <row r="19" spans="3:24" x14ac:dyDescent="0.35">
+    <row r="19" spans="3:24" x14ac:dyDescent="0.25">
       <c r="D19" t="s">
         <v>7</v>
       </c>
@@ -1660,7 +1660,7 @@
         <v>E[_]WOF*</v>
       </c>
     </row>
-    <row r="20" spans="3:24" x14ac:dyDescent="0.35">
+    <row r="20" spans="3:24" x14ac:dyDescent="0.25">
       <c r="D20" t="s">
         <v>8</v>
       </c>
@@ -1695,7 +1695,7 @@
         <v>E[_]WON*</v>
       </c>
     </row>
-    <row r="21" spans="3:24" x14ac:dyDescent="0.35">
+    <row r="21" spans="3:24" x14ac:dyDescent="0.25">
       <c r="D21" t="s">
         <v>9</v>
       </c>
@@ -1730,7 +1730,7 @@
         <v>EN[_]Hydro*</v>
       </c>
     </row>
-    <row r="22" spans="3:24" x14ac:dyDescent="0.35">
+    <row r="22" spans="3:24" x14ac:dyDescent="0.25">
       <c r="D22" t="s">
         <v>10</v>
       </c>
@@ -1765,7 +1765,7 @@
         <v>E[_]SPV*</v>
       </c>
     </row>
-    <row r="23" spans="3:24" x14ac:dyDescent="0.35">
+    <row r="23" spans="3:24" x14ac:dyDescent="0.25">
       <c r="P23" s="2" t="s">
         <v>31</v>
       </c>
@@ -1791,7 +1791,7 @@
         <v>E[_]WOF*</v>
       </c>
     </row>
-    <row r="24" spans="3:24" x14ac:dyDescent="0.35">
+    <row r="24" spans="3:24" x14ac:dyDescent="0.25">
       <c r="P24" s="2" t="s">
         <v>31</v>
       </c>
@@ -1817,12 +1817,12 @@
         <v>E[_]WON*</v>
       </c>
     </row>
-    <row r="27" spans="3:24" x14ac:dyDescent="0.35">
+    <row r="27" spans="3:24" x14ac:dyDescent="0.25">
       <c r="C27" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="28" spans="3:24" x14ac:dyDescent="0.35">
+    <row r="28" spans="3:24" x14ac:dyDescent="0.25">
       <c r="C28" t="s">
         <v>16</v>
       </c>
@@ -1839,7 +1839,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="29" spans="3:24" x14ac:dyDescent="0.35">
+    <row r="29" spans="3:24" x14ac:dyDescent="0.25">
       <c r="C29" t="s">
         <v>17</v>
       </c>
@@ -1850,7 +1850,7 @@
         <v>8.76</v>
       </c>
     </row>
-    <row r="30" spans="3:24" x14ac:dyDescent="0.35">
+    <row r="30" spans="3:24" x14ac:dyDescent="0.25">
       <c r="C30" t="s">
         <v>53</v>
       </c>
@@ -1861,7 +1861,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="3:24" x14ac:dyDescent="0.35">
+    <row r="31" spans="3:24" x14ac:dyDescent="0.25">
       <c r="C31" t="s">
         <v>17</v>
       </c>
@@ -1872,7 +1872,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="32" spans="3:24" x14ac:dyDescent="0.35">
+    <row r="32" spans="3:24" x14ac:dyDescent="0.25">
       <c r="D32" t="s">
         <v>7</v>
       </c>
@@ -1883,7 +1883,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="33" spans="3:7" x14ac:dyDescent="0.35">
+    <row r="33" spans="3:7" x14ac:dyDescent="0.25">
       <c r="D33" t="s">
         <v>10</v>
       </c>
@@ -1894,7 +1894,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="34" spans="3:7" x14ac:dyDescent="0.35">
+    <row r="34" spans="3:7" x14ac:dyDescent="0.25">
       <c r="D34" t="s">
         <v>9</v>
       </c>
@@ -1905,7 +1905,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="3:7" x14ac:dyDescent="0.35">
+    <row r="35" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C35" t="s">
         <v>17</v>
       </c>
@@ -1919,12 +1919,12 @@
         <v>3</v>
       </c>
     </row>
-    <row r="38" spans="3:7" x14ac:dyDescent="0.35">
+    <row r="38" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C38" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="39" spans="3:7" x14ac:dyDescent="0.35">
+    <row r="39" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C39" t="s">
         <v>21</v>
       </c>
@@ -1935,7 +1935,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="40" spans="3:7" x14ac:dyDescent="0.35">
+    <row r="40" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C40" t="s">
         <v>14</v>
       </c>
@@ -1946,7 +1946,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="41" spans="3:7" x14ac:dyDescent="0.35">
+    <row r="41" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C41" t="s">
         <v>15</v>
       </c>
@@ -1957,7 +1957,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="42" spans="3:7" x14ac:dyDescent="0.35">
+    <row r="42" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C42" t="s">
         <v>57</v>
       </c>
@@ -1968,7 +1968,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="43" spans="3:7" x14ac:dyDescent="0.35">
+    <row r="43" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C43" t="s">
         <v>55</v>
       </c>
@@ -1979,7 +1979,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="44" spans="3:7" x14ac:dyDescent="0.35">
+    <row r="44" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C44" t="s">
         <v>56</v>
       </c>
@@ -1990,12 +1990,12 @@
         <v>24</v>
       </c>
     </row>
-    <row r="47" spans="3:7" x14ac:dyDescent="0.35">
+    <row r="47" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C47" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="48" spans="3:7" x14ac:dyDescent="0.35">
+    <row r="48" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C48" t="s">
         <v>1</v>
       </c>
@@ -2009,12 +2009,12 @@
         <v>65</v>
       </c>
     </row>
-    <row r="49" spans="3:6" x14ac:dyDescent="0.35">
+    <row r="49" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C49" t="s">
         <v>64</v>
       </c>
       <c r="D49">
-        <v>2025</v>
+        <v>2030</v>
       </c>
       <c r="E49" s="3" t="s">
         <v>67</v>
@@ -2023,7 +2023,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="50" spans="3:6" x14ac:dyDescent="0.35">
+    <row r="50" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C50" t="s">
         <v>69</v>
       </c>

--- a/VerveStacks_EST/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
+++ b/VerveStacks_EST/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\PycharmProjects\ee-times\VerveStacks_EST\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92715A5D-2C44-47C1-A5A4-71CC370EF446}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{122E2282-E13A-4C8F-81F2-984ED8B29792}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-38520" yWindow="-5220" windowWidth="38640" windowHeight="21120" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -244,9 +244,6 @@
     <t>-pasti</t>
   </si>
   <si>
-    <t>solar,wind,coal,gas,nuclear,hydro,bioenergy</t>
-  </si>
-  <si>
     <t>life</t>
   </si>
   <si>
@@ -263,6 +260,9 @@
   </si>
   <si>
     <t>ELC_wo*</t>
+  </si>
+  <si>
+    <t>solar,wind,coal,gas,nuclear,hydro,bioenergy,ElcAgg_Solar,ElcAgg_Wind</t>
   </si>
 </sst>
 </file>
@@ -1951,7 +1951,7 @@
         <v>15</v>
       </c>
       <c r="D41" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E41" t="s">
         <v>24</v>
@@ -1973,7 +1973,7 @@
         <v>55</v>
       </c>
       <c r="D43" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E43" t="s">
         <v>24</v>
@@ -1984,7 +1984,7 @@
         <v>56</v>
       </c>
       <c r="D44" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E44" t="s">
         <v>24</v>
@@ -2020,21 +2020,21 @@
         <v>67</v>
       </c>
       <c r="F49" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
     </row>
     <row r="50" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C50" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D50">
         <v>40</v>
       </c>
       <c r="E50" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="F50" t="s">
         <v>70</v>
-      </c>
-      <c r="F50" t="s">
-        <v>71</v>
       </c>
     </row>
   </sheetData>

--- a/VerveStacks_EST/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
+++ b/VerveStacks_EST/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\PycharmProjects\ee-times\VerveStacks_EST\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{122E2282-E13A-4C8F-81F2-984ED8B29792}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA66A3B0-EA48-4807-AEE4-0137691D7686}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-38520" yWindow="-5220" windowWidth="38640" windowHeight="21120" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="292" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="300" uniqueCount="77">
   <si>
     <t>PSET_PN</t>
   </si>
@@ -244,6 +244,9 @@
     <t>-pasti</t>
   </si>
   <si>
+    <t>solar,wind,coal,gas,nuclear,hydro,bioenergy</t>
+  </si>
+  <si>
     <t>life</t>
   </si>
   <si>
@@ -262,7 +265,10 @@
     <t>ELC_wo*</t>
   </si>
   <si>
-    <t>solar,wind,coal,gas,nuclear,hydro,bioenergy,ElcAgg_Solar,ElcAgg_Wind</t>
+    <t>pset_pn</t>
+  </si>
+  <si>
+    <t>ElcAgg_Solar,ElcAgg_Wind</t>
   </si>
 </sst>
 </file>
@@ -1257,7 +1263,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="C4:X50"/>
+  <dimension ref="C4:X55"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="13.42578125" bestFit="1" customWidth="1"/>
@@ -1951,7 +1957,7 @@
         <v>15</v>
       </c>
       <c r="D41" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E41" t="s">
         <v>24</v>
@@ -1973,7 +1979,7 @@
         <v>55</v>
       </c>
       <c r="D43" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E43" t="s">
         <v>24</v>
@@ -1984,7 +1990,7 @@
         <v>56</v>
       </c>
       <c r="D44" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E44" t="s">
         <v>24</v>
@@ -2020,21 +2026,54 @@
         <v>67</v>
       </c>
       <c r="F49" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
     </row>
     <row r="50" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C50" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D50">
         <v>40</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F50" t="s">
-        <v>70</v>
+        <v>71</v>
+      </c>
+    </row>
+    <row r="53" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C53" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="54" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C54" t="s">
+        <v>1</v>
+      </c>
+      <c r="D54" t="s">
+        <v>26</v>
+      </c>
+      <c r="E54" t="s">
+        <v>66</v>
+      </c>
+      <c r="F54" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="55" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C55" t="s">
+        <v>64</v>
+      </c>
+      <c r="D55">
+        <v>2030</v>
+      </c>
+      <c r="E55" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="F55" t="s">
+        <v>76</v>
       </c>
     </row>
   </sheetData>

--- a/VerveStacks_EST/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
+++ b/VerveStacks_EST/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\PycharmProjects\ee-times\VerveStacks_EST\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA66A3B0-EA48-4807-AEE4-0137691D7686}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32057E53-71D9-411C-B03A-C35A805DC39B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-38520" yWindow="-5220" windowWidth="38640" windowHeight="21120" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -268,7 +268,7 @@
     <t>pset_pn</t>
   </si>
   <si>
-    <t>ElcAgg_Solar,ElcAgg_Wind</t>
+    <t>ElcAgg_Solar,ElcAgg_Wind,EN_STG8hbNREL,EN_STG4hbNREL</t>
   </si>
 </sst>
 </file>

--- a/VerveStacks_EST/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
+++ b/VerveStacks_EST/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\PycharmProjects\ee-times\VerveStacks_EST\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32057E53-71D9-411C-B03A-C35A805DC39B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79C5DFB5-017C-463C-B32E-A0131E436DE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-38520" yWindow="-5220" windowWidth="38640" windowHeight="21120" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="AVA" sheetId="6" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="300" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="303" uniqueCount="78">
   <si>
     <t>PSET_PN</t>
   </si>
@@ -269,6 +269,9 @@
   </si>
   <si>
     <t>ElcAgg_Solar,ElcAgg_Wind,EN_STG8hbNREL,EN_STG4hbNREL</t>
+  </si>
+  <si>
+    <t>cap_bnd~up</t>
   </si>
 </sst>
 </file>
@@ -1619,7 +1622,7 @@
         <v>16</v>
       </c>
       <c r="T18" t="str">
-        <f t="shared" ref="T18:T24" si="2">T14</f>
+        <f t="shared" ref="T18:T26" si="2">T14</f>
         <v>E[_]SPV*</v>
       </c>
       <c r="W18" t="str">
@@ -1821,6 +1824,41 @@
       <c r="X24" t="str">
         <f t="shared" si="1"/>
         <v>E[_]WON*</v>
+      </c>
+    </row>
+    <row r="25" spans="3:24" x14ac:dyDescent="0.25">
+      <c r="P25" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="Q25" s="2">
+        <v>1400</v>
+      </c>
+      <c r="R25" s="2">
+        <v>1400</v>
+      </c>
+      <c r="S25" s="2">
+        <v>1400</v>
+      </c>
+      <c r="T25" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="26" spans="3:24" x14ac:dyDescent="0.25">
+      <c r="P26" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="Q26" s="2">
+        <v>1500</v>
+      </c>
+      <c r="R26" s="2">
+        <v>1500</v>
+      </c>
+      <c r="S26" s="2">
+        <v>1500</v>
+      </c>
+      <c r="T26" t="str">
+        <f t="shared" si="2"/>
+        <v>E[_]SPV*</v>
       </c>
     </row>
     <row r="27" spans="3:24" x14ac:dyDescent="0.25">

--- a/VerveStacks_EST/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
+++ b/VerveStacks_EST/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\PycharmProjects\ee-times\VerveStacks_EST\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79C5DFB5-017C-463C-B32E-A0131E436DE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5347D07B-8601-4082-A133-E856B33DFCC9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1831,13 +1831,13 @@
         <v>77</v>
       </c>
       <c r="Q25" s="2">
-        <v>1400</v>
+        <v>1.4</v>
       </c>
       <c r="R25" s="2">
-        <v>1400</v>
+        <v>1.4</v>
       </c>
       <c r="S25" s="2">
-        <v>1400</v>
+        <v>1.4</v>
       </c>
       <c r="T25" t="s">
         <v>56</v>
@@ -1848,13 +1848,13 @@
         <v>77</v>
       </c>
       <c r="Q26" s="2">
-        <v>1500</v>
+        <v>1.5</v>
       </c>
       <c r="R26" s="2">
-        <v>1500</v>
+        <v>1.5</v>
       </c>
       <c r="S26" s="2">
-        <v>1500</v>
+        <v>1.5</v>
       </c>
       <c r="T26" t="str">
         <f t="shared" si="2"/>

--- a/VerveStacks_EST/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
+++ b/VerveStacks_EST/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\PycharmProjects\ee-times\VerveStacks_EST\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5347D07B-8601-4082-A133-E856B33DFCC9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E67F262-9C8C-414C-9AD5-3C3A01D7E25E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="303" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="308" uniqueCount="78">
   <si>
     <t>PSET_PN</t>
   </si>
@@ -271,7 +271,7 @@
     <t>ElcAgg_Solar,ElcAgg_Wind,EN_STG8hbNREL,EN_STG4hbNREL</t>
   </si>
   <si>
-    <t>cap_bnd~up</t>
+    <t>EST</t>
   </si>
 </sst>
 </file>
@@ -1280,6 +1280,7 @@
     <col min="13" max="13" width="6.28515625" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="4.28515625" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="10.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="4" spans="3:24" x14ac:dyDescent="0.25">
@@ -1622,7 +1623,7 @@
         <v>16</v>
       </c>
       <c r="T18" t="str">
-        <f t="shared" ref="T18:T26" si="2">T14</f>
+        <f t="shared" ref="T18:T24" si="2">T14</f>
         <v>E[_]SPV*</v>
       </c>
       <c r="W18" t="str">
@@ -1826,45 +1827,24 @@
         <v>E[_]WON*</v>
       </c>
     </row>
-    <row r="25" spans="3:24" x14ac:dyDescent="0.25">
-      <c r="P25" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="Q25" s="2">
-        <v>1.4</v>
-      </c>
-      <c r="R25" s="2">
-        <v>1.4</v>
-      </c>
-      <c r="S25" s="2">
-        <v>1.4</v>
-      </c>
-      <c r="T25" t="s">
-        <v>56</v>
-      </c>
-    </row>
     <row r="26" spans="3:24" x14ac:dyDescent="0.25">
       <c r="P26" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="Q26" s="2">
-        <v>1.5</v>
-      </c>
-      <c r="R26" s="2">
-        <v>1.5</v>
-      </c>
-      <c r="S26" s="2">
-        <v>1.5</v>
-      </c>
-      <c r="T26" t="str">
-        <f t="shared" si="2"/>
-        <v>E[_]SPV*</v>
+        <v>4</v>
       </c>
     </row>
     <row r="27" spans="3:24" x14ac:dyDescent="0.25">
       <c r="C27" t="s">
         <v>4</v>
       </c>
+      <c r="P27" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q27" t="s">
+        <v>0</v>
+      </c>
+      <c r="R27" t="s">
+        <v>77</v>
+      </c>
     </row>
     <row r="28" spans="3:24" x14ac:dyDescent="0.25">
       <c r="C28" t="s">
@@ -1882,6 +1862,15 @@
       <c r="G28" t="s">
         <v>5</v>
       </c>
+      <c r="P28" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q28" t="s">
+        <v>56</v>
+      </c>
+      <c r="R28">
+        <v>1.4</v>
+      </c>
     </row>
     <row r="29" spans="3:24" x14ac:dyDescent="0.25">
       <c r="C29" t="s">
@@ -1892,6 +1881,15 @@
       </c>
       <c r="G29" s="1">
         <v>8.76</v>
+      </c>
+      <c r="P29" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q29" t="s">
+        <v>57</v>
+      </c>
+      <c r="R29">
+        <v>1.5</v>
       </c>
     </row>
     <row r="30" spans="3:24" x14ac:dyDescent="0.25">

--- a/VerveStacks_EST/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
+++ b/VerveStacks_EST/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\PycharmProjects\ee-times\VerveStacks_EST\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E67F262-9C8C-414C-9AD5-3C3A01D7E25E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18B8A52E-0258-453E-B017-838171EC8405}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-38520" yWindow="-5220" windowWidth="38640" windowHeight="21120" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="AVA" sheetId="6" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="308" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="300" uniqueCount="77">
   <si>
     <t>PSET_PN</t>
   </si>
@@ -269,9 +269,6 @@
   </si>
   <si>
     <t>ElcAgg_Solar,ElcAgg_Wind,EN_STG8hbNREL,EN_STG4hbNREL</t>
-  </si>
-  <si>
-    <t>EST</t>
   </si>
 </sst>
 </file>
@@ -1828,23 +1825,13 @@
       </c>
     </row>
     <row r="26" spans="3:24" x14ac:dyDescent="0.25">
-      <c r="P26" s="2" t="s">
-        <v>4</v>
-      </c>
+      <c r="P26" s="2"/>
     </row>
     <row r="27" spans="3:24" x14ac:dyDescent="0.25">
       <c r="C27" t="s">
         <v>4</v>
       </c>
-      <c r="P27" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q27" t="s">
-        <v>0</v>
-      </c>
-      <c r="R27" t="s">
-        <v>77</v>
-      </c>
+      <c r="P27" s="2"/>
     </row>
     <row r="28" spans="3:24" x14ac:dyDescent="0.25">
       <c r="C28" t="s">
@@ -1862,15 +1849,7 @@
       <c r="G28" t="s">
         <v>5</v>
       </c>
-      <c r="P28" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="Q28" t="s">
-        <v>56</v>
-      </c>
-      <c r="R28">
-        <v>1.4</v>
-      </c>
+      <c r="P28" s="2"/>
     </row>
     <row r="29" spans="3:24" x14ac:dyDescent="0.25">
       <c r="C29" t="s">
@@ -1882,15 +1861,7 @@
       <c r="G29" s="1">
         <v>8.76</v>
       </c>
-      <c r="P29" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="Q29" t="s">
-        <v>57</v>
-      </c>
-      <c r="R29">
-        <v>1.5</v>
-      </c>
+      <c r="P29" s="2"/>
     </row>
     <row r="30" spans="3:24" x14ac:dyDescent="0.25">
       <c r="C30" t="s">

--- a/VerveStacks_EST/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
+++ b/VerveStacks_EST/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
   <workbookPr updateLinks="never"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\PycharmProjects\ee-times\VerveStacks_EST\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18B8A52E-0258-453E-B017-838171EC8405}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59920AF4-B74E-4B32-9652-DAD1DC895DD7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-38520" yWindow="-5220" windowWidth="38640" windowHeight="21120" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="300" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="301" uniqueCount="78">
   <si>
     <t>PSET_PN</t>
   </si>
@@ -268,7 +268,10 @@
     <t>pset_pn</t>
   </si>
   <si>
-    <t>ElcAgg_Solar,ElcAgg_Wind,EN_STG8hbNREL,EN_STG4hbNREL</t>
+    <t>EN_STG8hbNREL,EN_STG4hbNREL</t>
+  </si>
+  <si>
+    <t>ElcAgg_Solar,ElcAgg_Wind,</t>
   </si>
 </sst>
 </file>
@@ -2022,7 +2025,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="49" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="49" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C49" t="s">
         <v>64</v>
       </c>
@@ -2036,7 +2039,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="50" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="50" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C50" t="s">
         <v>69</v>
       </c>
@@ -2050,12 +2053,12 @@
         <v>71</v>
       </c>
     </row>
-    <row r="53" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="53" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C53" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="54" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="54" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C54" t="s">
         <v>1</v>
       </c>
@@ -2069,7 +2072,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="55" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="55" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C55" t="s">
         <v>64</v>
       </c>
@@ -2081,6 +2084,9 @@
       </c>
       <c r="F55" t="s">
         <v>76</v>
+      </c>
+      <c r="H55" t="s">
+        <v>77</v>
       </c>
     </row>
   </sheetData>

--- a/VerveStacks_EST/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
+++ b/VerveStacks_EST/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\PycharmProjects\ee-times\VerveStacks_EST\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59920AF4-B74E-4B32-9652-DAD1DC895DD7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94ABFF6F-C524-4630-99BF-1DC563923188}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-38520" yWindow="-5220" windowWidth="38640" windowHeight="21120" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-10470" yWindow="10890" windowWidth="19420" windowHeight="11500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="AVA" sheetId="6" r:id="rId1"/>
@@ -37,8 +37,26 @@
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>tc={1BF36063-6E02-40C0-ACF0-91FBA8E0608D}</author>
+  </authors>
+  <commentList>
+    <comment ref="C45" authorId="0" shapeId="0" xr:uid="{1BF36063-6E02-40C0-ACF0-91FBA8E0608D}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Single demand process connected to harku for now</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="301" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="311" uniqueCount="82">
   <si>
     <t>PSET_PN</t>
   </si>
@@ -272,13 +290,25 @@
   </si>
   <si>
     <t>ElcAgg_Solar,ElcAgg_Wind,</t>
+  </si>
+  <si>
+    <t>e_demand</t>
+  </si>
+  <si>
+    <t>~tfm_topins</t>
+  </si>
+  <si>
+    <t>e_harku_330</t>
+  </si>
+  <si>
+    <t>e_demand_agg</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -292,6 +322,12 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -334,6 +370,12 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <person displayName="Kristopher Raik" id="{1A26B760-FB54-48F1-8363-71FD6F653EC5}" userId="S::krraik@taltech.ee::b956339b-354b-46f9-8dd3-3584d8dbf762" providerId="AD"/>
+</personList>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -597,17 +639,31 @@
 </a:theme>
 </file>
 
+<file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
+<ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <threadedComment ref="C45" dT="2026-03-17T14:42:24.14" personId="{1A26B760-FB54-48F1-8363-71FD6F653EC5}" id="{1BF36063-6E02-40C0-ACF0-91FBA8E0608D}">
+    <text>Single demand process connected to harku for now</text>
+  </threadedComment>
+</ThreadedComments>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{268E9BAB-B98F-4B82-9042-51EABC9ED525}">
-  <dimension ref="B3:C5"/>
+  <dimension ref="B3:D16"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="18.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="27.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="49.5703125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="3" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="4" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
         <v>21</v>
       </c>
@@ -615,12 +671,39 @@
         <v>60</v>
       </c>
     </row>
-    <row r="5" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
         <v>59</v>
       </c>
       <c r="C5">
         <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B14" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="15" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B15" t="s">
+        <v>21</v>
+      </c>
+      <c r="C15" t="s">
+        <v>22</v>
+      </c>
+      <c r="D15" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="16" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B16" t="s">
+        <v>81</v>
+      </c>
+      <c r="C16" t="s">
+        <v>80</v>
+      </c>
+      <c r="D16" t="s">
+        <v>24</v>
       </c>
     </row>
   </sheetData>
@@ -1265,12 +1348,12 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="C4:X55"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="3" max="3" width="13.42578125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.7109375" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="11" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="41.28515625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="10.42578125" bestFit="1" customWidth="1"/>
@@ -2006,6 +2089,17 @@
         <v>24</v>
       </c>
     </row>
+    <row r="45" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C45" t="s">
+        <v>78</v>
+      </c>
+      <c r="D45" t="s">
+        <v>80</v>
+      </c>
+      <c r="E45" t="s">
+        <v>24</v>
+      </c>
+    </row>
     <row r="47" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C47" t="s">
         <v>4</v>
@@ -2092,6 +2186,7 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
 

--- a/VerveStacks_EST/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
+++ b/VerveStacks_EST/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\PycharmProjects\ee-times\VerveStacks_EST\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94ABFF6F-C524-4630-99BF-1DC563923188}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94689CF1-EB51-48DE-B4AB-2C081539266A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-10470" yWindow="10890" windowWidth="19420" windowHeight="11500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="AVA" sheetId="6" r:id="rId1"/>
@@ -37,26 +37,8 @@
 </workbook>
 </file>
 
-<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
-  <authors>
-    <author>tc={1BF36063-6E02-40C0-ACF0-91FBA8E0608D}</author>
-  </authors>
-  <commentList>
-    <comment ref="C45" authorId="0" shapeId="0" xr:uid="{1BF36063-6E02-40C0-ACF0-91FBA8E0608D}">
-      <text>
-        <t>[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-    Single demand process connected to harku for now</t>
-      </text>
-    </comment>
-  </commentList>
-</comments>
-</file>
-
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="311" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="301" uniqueCount="78">
   <si>
     <t>PSET_PN</t>
   </si>
@@ -290,25 +272,13 @@
   </si>
   <si>
     <t>ElcAgg_Solar,ElcAgg_Wind,</t>
-  </si>
-  <si>
-    <t>e_demand</t>
-  </si>
-  <si>
-    <t>~tfm_topins</t>
-  </si>
-  <si>
-    <t>e_harku_330</t>
-  </si>
-  <si>
-    <t>e_demand_agg</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -322,12 +292,6 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color indexed="81"/>
-      <name val="Tahoma"/>
-      <charset val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -373,9 +337,7 @@
 </file>
 
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <person displayName="Kristopher Raik" id="{1A26B760-FB54-48F1-8363-71FD6F653EC5}" userId="S::krraik@taltech.ee::b956339b-354b-46f9-8dd3-3584d8dbf762" providerId="AD"/>
-</personList>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -639,31 +601,23 @@
 </a:theme>
 </file>
 
-<file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
-<ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <threadedComment ref="C45" dT="2026-03-17T14:42:24.14" personId="{1A26B760-FB54-48F1-8363-71FD6F653EC5}" id="{1BF36063-6E02-40C0-ACF0-91FBA8E0608D}">
-    <text>Single demand process connected to harku for now</text>
-  </threadedComment>
-</ThreadedComments>
-</file>
-
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{268E9BAB-B98F-4B82-9042-51EABC9ED525}">
-  <dimension ref="B3:D16"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="B3:C5"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="18.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.453125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="27.5703125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="49.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="27.54296875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="49.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B3" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="4" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B4" t="s">
         <v>21</v>
       </c>
@@ -671,39 +625,12 @@
         <v>60</v>
       </c>
     </row>
-    <row r="5" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B5" t="s">
         <v>59</v>
       </c>
       <c r="C5">
         <v>1</v>
-      </c>
-    </row>
-    <row r="14" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B14" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="15" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B15" t="s">
-        <v>21</v>
-      </c>
-      <c r="C15" t="s">
-        <v>22</v>
-      </c>
-      <c r="D15" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="16" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B16" t="s">
-        <v>81</v>
-      </c>
-      <c r="C16" t="s">
-        <v>80</v>
-      </c>
-      <c r="D16" t="s">
-        <v>24</v>
       </c>
     </row>
   </sheetData>
@@ -714,24 +641,24 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E3954DD3-0F24-46DF-B268-7A98442D0282}">
   <dimension ref="A1:O13"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="7.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="5.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.5703125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="29.85546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.5703125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="7.5703125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="8.5703125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15.140625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="7.42578125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="4.85546875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="3.85546875" bestFit="1" customWidth="1"/>
-    <col min="12" max="14" width="4.7109375" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="5.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.26953125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="5.7265625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.54296875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="29.81640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.54296875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="7.54296875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.54296875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.1796875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="7.453125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="4.81640625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="3.81640625" bestFit="1" customWidth="1"/>
+    <col min="12" max="14" width="4.7265625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="5.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>32</v>
       </c>
@@ -778,7 +705,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>44</v>
       </c>
@@ -825,7 +752,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>44</v>
       </c>
@@ -872,7 +799,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>44</v>
       </c>
@@ -919,7 +846,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>44</v>
       </c>
@@ -966,7 +893,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>44</v>
       </c>
@@ -1013,7 +940,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>44</v>
       </c>
@@ -1060,7 +987,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>44</v>
       </c>
@@ -1107,7 +1034,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>44</v>
       </c>
@@ -1154,7 +1081,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>44</v>
       </c>
@@ -1201,7 +1128,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>44</v>
       </c>
@@ -1248,7 +1175,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>44</v>
       </c>
@@ -1295,7 +1222,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>44</v>
       </c>
@@ -1348,25 +1275,25 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="C4:X55"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="3" max="3" width="14.5703125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.54296875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.7265625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="11" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="41.28515625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="10.42578125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="5.42578125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="5.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="41.26953125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.453125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="5.453125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="5.7265625" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="5" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="6.28515625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="4.28515625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="11.7109375" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="6.26953125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="4.26953125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="11.7265625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="10.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="4" spans="3:24" x14ac:dyDescent="0.25">
+    <row r="4" spans="3:24" x14ac:dyDescent="0.35">
       <c r="C4" t="s">
         <v>4</v>
       </c>
@@ -1380,7 +1307,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="5" spans="3:24" x14ac:dyDescent="0.25">
+    <row r="5" spans="3:24" x14ac:dyDescent="0.35">
       <c r="C5" t="s">
         <v>3</v>
       </c>
@@ -1406,7 +1333,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="6" spans="3:24" x14ac:dyDescent="0.25">
+    <row r="6" spans="3:24" x14ac:dyDescent="0.35">
       <c r="D6" t="s">
         <v>6</v>
       </c>
@@ -1426,7 +1353,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="7" spans="3:24" x14ac:dyDescent="0.25">
+    <row r="7" spans="3:24" x14ac:dyDescent="0.35">
       <c r="D7" t="s">
         <v>7</v>
       </c>
@@ -1446,7 +1373,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="8" spans="3:24" x14ac:dyDescent="0.25">
+    <row r="8" spans="3:24" x14ac:dyDescent="0.35">
       <c r="D8" t="s">
         <v>8</v>
       </c>
@@ -1457,7 +1384,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="3:24" x14ac:dyDescent="0.25">
+    <row r="9" spans="3:24" x14ac:dyDescent="0.35">
       <c r="D9" t="s">
         <v>9</v>
       </c>
@@ -1468,7 +1395,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="10" spans="3:24" x14ac:dyDescent="0.25">
+    <row r="10" spans="3:24" x14ac:dyDescent="0.35">
       <c r="D10" t="s">
         <v>10</v>
       </c>
@@ -1479,7 +1406,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="11" spans="3:24" x14ac:dyDescent="0.25">
+    <row r="11" spans="3:24" x14ac:dyDescent="0.35">
       <c r="D11" t="s">
         <v>6</v>
       </c>
@@ -1493,7 +1420,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="12" spans="3:24" x14ac:dyDescent="0.25">
+    <row r="12" spans="3:24" x14ac:dyDescent="0.35">
       <c r="P12" s="2" t="s">
         <v>25</v>
       </c>
@@ -1510,7 +1437,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="13" spans="3:24" x14ac:dyDescent="0.25">
+    <row r="13" spans="3:24" x14ac:dyDescent="0.35">
       <c r="C13" t="s">
         <v>4</v>
       </c>
@@ -1537,7 +1464,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="14" spans="3:24" x14ac:dyDescent="0.25">
+    <row r="14" spans="3:24" x14ac:dyDescent="0.35">
       <c r="C14" t="s">
         <v>3</v>
       </c>
@@ -1576,7 +1503,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="15" spans="3:24" x14ac:dyDescent="0.25">
+    <row r="15" spans="3:24" x14ac:dyDescent="0.35">
       <c r="C15" t="s">
         <v>11</v>
       </c>
@@ -1615,7 +1542,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="16" spans="3:24" x14ac:dyDescent="0.25">
+    <row r="16" spans="3:24" x14ac:dyDescent="0.35">
       <c r="D16" t="s">
         <v>6</v>
       </c>
@@ -1648,7 +1575,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="17" spans="3:24" x14ac:dyDescent="0.25">
+    <row r="17" spans="3:24" x14ac:dyDescent="0.35">
       <c r="D17" t="s">
         <v>13</v>
       </c>
@@ -1683,7 +1610,7 @@
         <v>EN[_]Hydro*</v>
       </c>
     </row>
-    <row r="18" spans="3:24" x14ac:dyDescent="0.25">
+    <row r="18" spans="3:24" x14ac:dyDescent="0.35">
       <c r="D18" t="s">
         <v>13</v>
       </c>
@@ -1718,7 +1645,7 @@
         <v>E[_]SPV*</v>
       </c>
     </row>
-    <row r="19" spans="3:24" x14ac:dyDescent="0.25">
+    <row r="19" spans="3:24" x14ac:dyDescent="0.35">
       <c r="D19" t="s">
         <v>7</v>
       </c>
@@ -1753,7 +1680,7 @@
         <v>E[_]WOF*</v>
       </c>
     </row>
-    <row r="20" spans="3:24" x14ac:dyDescent="0.25">
+    <row r="20" spans="3:24" x14ac:dyDescent="0.35">
       <c r="D20" t="s">
         <v>8</v>
       </c>
@@ -1788,7 +1715,7 @@
         <v>E[_]WON*</v>
       </c>
     </row>
-    <row r="21" spans="3:24" x14ac:dyDescent="0.25">
+    <row r="21" spans="3:24" x14ac:dyDescent="0.35">
       <c r="D21" t="s">
         <v>9</v>
       </c>
@@ -1823,7 +1750,7 @@
         <v>EN[_]Hydro*</v>
       </c>
     </row>
-    <row r="22" spans="3:24" x14ac:dyDescent="0.25">
+    <row r="22" spans="3:24" x14ac:dyDescent="0.35">
       <c r="D22" t="s">
         <v>10</v>
       </c>
@@ -1858,7 +1785,7 @@
         <v>E[_]SPV*</v>
       </c>
     </row>
-    <row r="23" spans="3:24" x14ac:dyDescent="0.25">
+    <row r="23" spans="3:24" x14ac:dyDescent="0.35">
       <c r="P23" s="2" t="s">
         <v>31</v>
       </c>
@@ -1884,7 +1811,7 @@
         <v>E[_]WOF*</v>
       </c>
     </row>
-    <row r="24" spans="3:24" x14ac:dyDescent="0.25">
+    <row r="24" spans="3:24" x14ac:dyDescent="0.35">
       <c r="P24" s="2" t="s">
         <v>31</v>
       </c>
@@ -1910,16 +1837,16 @@
         <v>E[_]WON*</v>
       </c>
     </row>
-    <row r="26" spans="3:24" x14ac:dyDescent="0.25">
+    <row r="26" spans="3:24" x14ac:dyDescent="0.35">
       <c r="P26" s="2"/>
     </row>
-    <row r="27" spans="3:24" x14ac:dyDescent="0.25">
+    <row r="27" spans="3:24" x14ac:dyDescent="0.35">
       <c r="C27" t="s">
         <v>4</v>
       </c>
       <c r="P27" s="2"/>
     </row>
-    <row r="28" spans="3:24" x14ac:dyDescent="0.25">
+    <row r="28" spans="3:24" x14ac:dyDescent="0.35">
       <c r="C28" t="s">
         <v>16</v>
       </c>
@@ -1937,7 +1864,7 @@
       </c>
       <c r="P28" s="2"/>
     </row>
-    <row r="29" spans="3:24" x14ac:dyDescent="0.25">
+    <row r="29" spans="3:24" x14ac:dyDescent="0.35">
       <c r="C29" t="s">
         <v>17</v>
       </c>
@@ -1949,7 +1876,7 @@
       </c>
       <c r="P29" s="2"/>
     </row>
-    <row r="30" spans="3:24" x14ac:dyDescent="0.25">
+    <row r="30" spans="3:24" x14ac:dyDescent="0.35">
       <c r="C30" t="s">
         <v>53</v>
       </c>
@@ -1960,7 +1887,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="3:24" x14ac:dyDescent="0.25">
+    <row r="31" spans="3:24" x14ac:dyDescent="0.35">
       <c r="C31" t="s">
         <v>17</v>
       </c>
@@ -1971,7 +1898,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="32" spans="3:24" x14ac:dyDescent="0.25">
+    <row r="32" spans="3:24" x14ac:dyDescent="0.35">
       <c r="D32" t="s">
         <v>7</v>
       </c>
@@ -1982,7 +1909,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="33" spans="3:7" x14ac:dyDescent="0.25">
+    <row r="33" spans="3:7" x14ac:dyDescent="0.35">
       <c r="D33" t="s">
         <v>10</v>
       </c>
@@ -1993,7 +1920,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="34" spans="3:7" x14ac:dyDescent="0.25">
+    <row r="34" spans="3:7" x14ac:dyDescent="0.35">
       <c r="D34" t="s">
         <v>9</v>
       </c>
@@ -2004,7 +1931,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="3:7" x14ac:dyDescent="0.25">
+    <row r="35" spans="3:7" x14ac:dyDescent="0.35">
       <c r="C35" t="s">
         <v>17</v>
       </c>
@@ -2018,12 +1945,12 @@
         <v>3</v>
       </c>
     </row>
-    <row r="38" spans="3:7" x14ac:dyDescent="0.25">
+    <row r="38" spans="3:7" x14ac:dyDescent="0.35">
       <c r="C38" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="39" spans="3:7" x14ac:dyDescent="0.25">
+    <row r="39" spans="3:7" x14ac:dyDescent="0.35">
       <c r="C39" t="s">
         <v>21</v>
       </c>
@@ -2034,7 +1961,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="40" spans="3:7" x14ac:dyDescent="0.25">
+    <row r="40" spans="3:7" x14ac:dyDescent="0.35">
       <c r="C40" t="s">
         <v>14</v>
       </c>
@@ -2045,7 +1972,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="41" spans="3:7" x14ac:dyDescent="0.25">
+    <row r="41" spans="3:7" x14ac:dyDescent="0.35">
       <c r="C41" t="s">
         <v>15</v>
       </c>
@@ -2056,7 +1983,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="42" spans="3:7" x14ac:dyDescent="0.25">
+    <row r="42" spans="3:7" x14ac:dyDescent="0.35">
       <c r="C42" t="s">
         <v>57</v>
       </c>
@@ -2067,7 +1994,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="43" spans="3:7" x14ac:dyDescent="0.25">
+    <row r="43" spans="3:7" x14ac:dyDescent="0.35">
       <c r="C43" t="s">
         <v>55</v>
       </c>
@@ -2078,7 +2005,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="44" spans="3:7" x14ac:dyDescent="0.25">
+    <row r="44" spans="3:7" x14ac:dyDescent="0.35">
       <c r="C44" t="s">
         <v>56</v>
       </c>
@@ -2089,23 +2016,12 @@
         <v>24</v>
       </c>
     </row>
-    <row r="45" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C45" t="s">
-        <v>78</v>
-      </c>
-      <c r="D45" t="s">
-        <v>80</v>
-      </c>
-      <c r="E45" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="47" spans="3:7" x14ac:dyDescent="0.25">
+    <row r="47" spans="3:7" x14ac:dyDescent="0.35">
       <c r="C47" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="48" spans="3:7" x14ac:dyDescent="0.25">
+    <row r="48" spans="3:7" x14ac:dyDescent="0.35">
       <c r="C48" t="s">
         <v>1</v>
       </c>
@@ -2119,7 +2035,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="49" spans="3:8" x14ac:dyDescent="0.25">
+    <row r="49" spans="3:8" x14ac:dyDescent="0.35">
       <c r="C49" t="s">
         <v>64</v>
       </c>
@@ -2133,7 +2049,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="50" spans="3:8" x14ac:dyDescent="0.25">
+    <row r="50" spans="3:8" x14ac:dyDescent="0.35">
       <c r="C50" t="s">
         <v>69</v>
       </c>
@@ -2147,12 +2063,12 @@
         <v>71</v>
       </c>
     </row>
-    <row r="53" spans="3:8" x14ac:dyDescent="0.25">
+    <row r="53" spans="3:8" x14ac:dyDescent="0.35">
       <c r="C53" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="54" spans="3:8" x14ac:dyDescent="0.25">
+    <row r="54" spans="3:8" x14ac:dyDescent="0.35">
       <c r="C54" t="s">
         <v>1</v>
       </c>
@@ -2166,7 +2082,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="55" spans="3:8" x14ac:dyDescent="0.25">
+    <row r="55" spans="3:8" x14ac:dyDescent="0.35">
       <c r="C55" t="s">
         <v>64</v>
       </c>
@@ -2186,7 +2102,6 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
 

--- a/VerveStacks_EST/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
+++ b/VerveStacks_EST/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\PycharmProjects\ee-times\VerveStacks_EST\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94689CF1-EB51-48DE-B4AB-2C081539266A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2CD20DCC-8DD7-4157-9064-28049531E8B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-10470" yWindow="10890" windowWidth="19420" windowHeight="11500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="AVA" sheetId="6" r:id="rId1"/>
@@ -37,8 +37,44 @@
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>tc={80A2C193-6148-4AA7-9B62-06322F60E0BF}</author>
+    <author>tc={E6F93F18-BBEF-4E19-B2D0-A493D668847A}</author>
+    <author>tc={9326A9B6-D94C-4ED3-9FB8-434C0D4AC388}</author>
+  </authors>
+  <commentList>
+    <comment ref="U14" authorId="0" shapeId="0" xr:uid="{80A2C193-6148-4AA7-9B62-06322F60E0BF}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Utility-scale PV</t>
+      </text>
+    </comment>
+    <comment ref="U15" authorId="1" shapeId="0" xr:uid="{E6F93F18-BBEF-4E19-B2D0-A493D668847A}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    AC fixed</t>
+      </text>
+    </comment>
+    <comment ref="U26" authorId="2" shapeId="0" xr:uid="{9326A9B6-D94C-4ED3-9FB8-434C0D4AC388}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    AC fixed</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="301" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="307" uniqueCount="79">
   <si>
     <t>PSET_PN</t>
   </si>
@@ -272,13 +308,16 @@
   </si>
   <si>
     <t>ElcAgg_Solar,ElcAgg_Wind,</t>
+  </si>
+  <si>
+    <t>act_cost</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -292,6 +331,13 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+      <charset val="186"/>
     </font>
   </fonts>
   <fills count="2">
@@ -337,7 +383,9 @@
 </file>
 
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <person displayName="Kristopher Raik" id="{50AE587C-9924-43E9-9BB9-052BDB346AE2}" userId="S::krraik@taltech.ee::b956339b-354b-46f9-8dd3-3584d8dbf762" providerId="AD"/>
+</personList>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -601,6 +649,20 @@
 </a:theme>
 </file>
 
+<file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
+<ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <threadedComment ref="U14" dT="2026-03-18T13:56:27.06" personId="{50AE587C-9924-43E9-9BB9-052BDB346AE2}" id="{80A2C193-6148-4AA7-9B62-06322F60E0BF}">
+    <text>Utility-scale PV</text>
+  </threadedComment>
+  <threadedComment ref="U15" dT="2026-03-18T13:39:46.05" personId="{50AE587C-9924-43E9-9BB9-052BDB346AE2}" id="{E6F93F18-BBEF-4E19-B2D0-A493D668847A}">
+    <text>AC fixed</text>
+  </threadedComment>
+  <threadedComment ref="U26" dT="2026-03-18T13:39:46.05" personId="{50AE587C-9924-43E9-9BB9-052BDB346AE2}" id="{9326A9B6-D94C-4ED3-9FB8-434C0D4AC388}">
+    <text>AC fixed</text>
+  </threadedComment>
+</ThreadedComments>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{268E9BAB-B98F-4B82-9042-51EABC9ED525}">
   <dimension ref="B3:C5"/>
@@ -1275,8 +1337,8 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="C4:X55"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="C4:Y55"/>
   <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="3" max="3" width="14.54296875" bestFit="1" customWidth="1"/>
@@ -1291,9 +1353,11 @@
     <col min="14" max="14" width="4.26953125" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="11.7265625" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="11.453125" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="31.36328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="4" spans="3:24" x14ac:dyDescent="0.35">
+    <row r="4" spans="3:25" x14ac:dyDescent="0.35">
       <c r="C4" t="s">
         <v>4</v>
       </c>
@@ -1307,7 +1371,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="5" spans="3:24" x14ac:dyDescent="0.35">
+    <row r="5" spans="3:25" x14ac:dyDescent="0.35">
       <c r="C5" t="s">
         <v>3</v>
       </c>
@@ -1333,7 +1397,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="6" spans="3:24" x14ac:dyDescent="0.35">
+    <row r="6" spans="3:25" x14ac:dyDescent="0.35">
       <c r="D6" t="s">
         <v>6</v>
       </c>
@@ -1353,7 +1417,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="7" spans="3:24" x14ac:dyDescent="0.35">
+    <row r="7" spans="3:25" x14ac:dyDescent="0.35">
       <c r="D7" t="s">
         <v>7</v>
       </c>
@@ -1373,7 +1437,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="8" spans="3:24" x14ac:dyDescent="0.35">
+    <row r="8" spans="3:25" x14ac:dyDescent="0.35">
       <c r="D8" t="s">
         <v>8</v>
       </c>
@@ -1384,7 +1448,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="3:24" x14ac:dyDescent="0.35">
+    <row r="9" spans="3:25" x14ac:dyDescent="0.35">
       <c r="D9" t="s">
         <v>9</v>
       </c>
@@ -1395,7 +1459,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="10" spans="3:24" x14ac:dyDescent="0.35">
+    <row r="10" spans="3:25" x14ac:dyDescent="0.35">
       <c r="D10" t="s">
         <v>10</v>
       </c>
@@ -1406,7 +1470,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="11" spans="3:24" x14ac:dyDescent="0.35">
+    <row r="11" spans="3:25" x14ac:dyDescent="0.35">
       <c r="D11" t="s">
         <v>6</v>
       </c>
@@ -1420,7 +1484,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="12" spans="3:24" x14ac:dyDescent="0.35">
+    <row r="12" spans="3:25" x14ac:dyDescent="0.35">
       <c r="P12" s="2" t="s">
         <v>25</v>
       </c>
@@ -1430,14 +1494,17 @@
       <c r="R12" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="S12" s="2" t="s">
+      <c r="S12">
+        <v>2040</v>
+      </c>
+      <c r="T12" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="T12" t="s">
+      <c r="U12" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="13" spans="3:24" x14ac:dyDescent="0.35">
+    <row r="13" spans="3:25" x14ac:dyDescent="0.35">
       <c r="C13" t="s">
         <v>4</v>
       </c>
@@ -1453,18 +1520,21 @@
       <c r="S13" s="2">
         <v>2700</v>
       </c>
-      <c r="T13" t="str">
-        <f>X13</f>
+      <c r="T13" s="2">
+        <v>2700</v>
+      </c>
+      <c r="U13" t="str">
+        <f>Y13</f>
         <v>EN[_]Hydro*</v>
       </c>
-      <c r="W13" t="s">
+      <c r="X13" t="s">
         <v>46</v>
       </c>
-      <c r="X13" t="s">
+      <c r="Y13" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="14" spans="3:24" x14ac:dyDescent="0.35">
+    <row r="14" spans="3:25" x14ac:dyDescent="0.35">
       <c r="C14" t="s">
         <v>3</v>
       </c>
@@ -1484,26 +1554,29 @@
         <v>27</v>
       </c>
       <c r="Q14" s="2">
-        <v>1110</v>
+        <v>560</v>
       </c>
       <c r="R14" s="2">
-        <v>690</v>
-      </c>
-      <c r="S14" s="2">
-        <v>480</v>
-      </c>
-      <c r="T14" t="str">
-        <f t="shared" ref="T14:T16" si="0">X14</f>
+        <v>380</v>
+      </c>
+      <c r="S14">
+        <v>320</v>
+      </c>
+      <c r="T14" s="2">
+        <v>290</v>
+      </c>
+      <c r="U14" t="str">
+        <f t="shared" ref="U14:U16" si="0">Y14</f>
         <v>E[_]SPV*</v>
       </c>
-      <c r="W14" t="s">
+      <c r="X14" t="s">
         <v>49</v>
       </c>
-      <c r="X14" t="s">
+      <c r="Y14" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="15" spans="3:24" x14ac:dyDescent="0.35">
+    <row r="15" spans="3:25" x14ac:dyDescent="0.35">
       <c r="C15" t="s">
         <v>11</v>
       </c>
@@ -1523,26 +1596,29 @@
         <v>27</v>
       </c>
       <c r="Q15" s="2">
-        <v>4060</v>
+        <v>2780</v>
       </c>
       <c r="R15" s="2">
-        <v>2760</v>
+        <v>2390</v>
       </c>
       <c r="S15" s="2">
-        <v>1980</v>
-      </c>
-      <c r="T15" t="str">
+        <v>2140</v>
+      </c>
+      <c r="T15" s="2">
+        <v>1990</v>
+      </c>
+      <c r="U15" t="str">
         <f t="shared" si="0"/>
         <v>E[_]WOF*</v>
       </c>
-      <c r="W15" t="s">
+      <c r="X15" t="s">
         <v>50</v>
       </c>
-      <c r="X15" t="s">
+      <c r="Y15" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="16" spans="3:24" x14ac:dyDescent="0.35">
+    <row r="16" spans="3:25" x14ac:dyDescent="0.35">
       <c r="D16" t="s">
         <v>6</v>
       </c>
@@ -1556,26 +1632,29 @@
         <v>27</v>
       </c>
       <c r="Q16" s="2">
-        <v>1500</v>
+        <v>1180</v>
       </c>
       <c r="R16" s="2">
-        <v>1430</v>
+        <v>1150</v>
       </c>
       <c r="S16" s="2">
-        <v>1370</v>
-      </c>
-      <c r="T16" t="str">
+        <v>1110</v>
+      </c>
+      <c r="T16" s="2">
+        <v>1090</v>
+      </c>
+      <c r="U16" t="str">
         <f t="shared" si="0"/>
         <v>E[_]WON*</v>
       </c>
-      <c r="W16" t="s">
+      <c r="X16" t="s">
         <v>51</v>
       </c>
-      <c r="X16" t="s">
+      <c r="Y16" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="17" spans="3:24" x14ac:dyDescent="0.35">
+    <row r="17" spans="3:25" x14ac:dyDescent="0.35">
       <c r="D17" t="s">
         <v>13</v>
       </c>
@@ -1597,20 +1676,23 @@
       <c r="S17" s="2">
         <v>65</v>
       </c>
-      <c r="T17" t="str">
-        <f>T13</f>
+      <c r="T17" s="2">
+        <v>65</v>
+      </c>
+      <c r="U17" t="str">
+        <f>U13</f>
         <v>EN[_]Hydro*</v>
       </c>
-      <c r="W17" t="str">
-        <f>W13</f>
+      <c r="X17" t="str">
+        <f>X13</f>
         <v>Hydropower - large-scale unit</v>
       </c>
-      <c r="X17" t="str">
-        <f t="shared" ref="X17:X24" si="1">X13</f>
+      <c r="Y17" t="str">
+        <f t="shared" ref="Y17:Y24" si="1">Y13</f>
         <v>EN[_]Hydro*</v>
       </c>
     </row>
-    <row r="18" spans="3:24" x14ac:dyDescent="0.35">
+    <row r="18" spans="3:25" x14ac:dyDescent="0.35">
       <c r="D18" t="s">
         <v>13</v>
       </c>
@@ -1624,28 +1706,31 @@
         <v>30</v>
       </c>
       <c r="Q18" s="2">
-        <v>16</v>
+        <v>11.5</v>
       </c>
       <c r="R18" s="2">
-        <v>16</v>
+        <v>9.5</v>
       </c>
       <c r="S18" s="2">
-        <v>16</v>
-      </c>
-      <c r="T18" t="str">
-        <f t="shared" ref="T18:T24" si="2">T14</f>
+        <v>8.1</v>
+      </c>
+      <c r="T18" s="2">
+        <v>7.4</v>
+      </c>
+      <c r="U18" t="str">
+        <f t="shared" ref="U18:U24" si="2">U14</f>
         <v>E[_]SPV*</v>
       </c>
-      <c r="W18" t="str">
-        <f t="shared" ref="W18" si="3">W14</f>
+      <c r="X18" t="str">
+        <f t="shared" ref="X18" si="3">X14</f>
         <v>Solar photovoltaics - Large scale unit</v>
       </c>
-      <c r="X18" t="str">
+      <c r="Y18" t="str">
         <f t="shared" si="1"/>
         <v>E[_]SPV*</v>
       </c>
     </row>
-    <row r="19" spans="3:24" x14ac:dyDescent="0.35">
+    <row r="19" spans="3:25" x14ac:dyDescent="0.35">
       <c r="D19" t="s">
         <v>7</v>
       </c>
@@ -1659,28 +1744,31 @@
         <v>30</v>
       </c>
       <c r="Q19" s="2">
-        <v>120</v>
+        <v>44</v>
       </c>
       <c r="R19" s="2">
-        <v>95</v>
+        <v>34</v>
       </c>
       <c r="S19" s="2">
-        <v>70</v>
-      </c>
-      <c r="T19" t="str">
+        <v>30</v>
+      </c>
+      <c r="T19" s="2">
+        <v>28</v>
+      </c>
+      <c r="U19" t="str">
         <f t="shared" si="2"/>
         <v>E[_]WOF*</v>
       </c>
-      <c r="W19" t="str">
-        <f t="shared" ref="W19" si="4">W15</f>
+      <c r="X19" t="str">
+        <f t="shared" ref="X19" si="4">X15</f>
         <v>Wind offshore</v>
       </c>
-      <c r="X19" t="str">
+      <c r="Y19" t="str">
         <f t="shared" si="1"/>
         <v>E[_]WOF*</v>
       </c>
     </row>
-    <row r="20" spans="3:24" x14ac:dyDescent="0.35">
+    <row r="20" spans="3:25" x14ac:dyDescent="0.35">
       <c r="D20" t="s">
         <v>8</v>
       </c>
@@ -1694,28 +1782,31 @@
         <v>30</v>
       </c>
       <c r="Q20" s="2">
-        <v>38</v>
+        <v>17.387</v>
       </c>
       <c r="R20" s="2">
-        <v>36</v>
+        <v>16.663</v>
       </c>
       <c r="S20" s="2">
-        <v>36</v>
-      </c>
-      <c r="T20" t="str">
+        <v>15.965</v>
+      </c>
+      <c r="T20" s="2">
+        <v>15.602</v>
+      </c>
+      <c r="U20" t="str">
         <f t="shared" si="2"/>
         <v>E[_]WON*</v>
       </c>
-      <c r="W20" t="str">
-        <f t="shared" ref="W20" si="5">W16</f>
+      <c r="X20" t="str">
+        <f t="shared" ref="X20" si="5">X16</f>
         <v>Wind onshore</v>
       </c>
-      <c r="X20" t="str">
+      <c r="Y20" t="str">
         <f t="shared" si="1"/>
         <v>E[_]WON*</v>
       </c>
     </row>
-    <row r="21" spans="3:24" x14ac:dyDescent="0.35">
+    <row r="21" spans="3:25" x14ac:dyDescent="0.35">
       <c r="D21" t="s">
         <v>9</v>
       </c>
@@ -1737,20 +1828,23 @@
       <c r="S21" s="2">
         <v>4</v>
       </c>
-      <c r="T21" t="str">
+      <c r="T21" s="2">
+        <v>4</v>
+      </c>
+      <c r="U21" t="str">
         <f t="shared" si="2"/>
         <v>EN[_]Hydro*</v>
       </c>
-      <c r="W21" t="str">
-        <f t="shared" ref="W21" si="6">W17</f>
+      <c r="X21" t="str">
+        <f t="shared" ref="X21" si="6">X17</f>
         <v>Hydropower - large-scale unit</v>
       </c>
-      <c r="X21" t="str">
+      <c r="Y21" t="str">
         <f t="shared" si="1"/>
         <v>EN[_]Hydro*</v>
       </c>
     </row>
-    <row r="22" spans="3:24" x14ac:dyDescent="0.35">
+    <row r="22" spans="3:25" x14ac:dyDescent="0.35">
       <c r="D22" t="s">
         <v>10</v>
       </c>
@@ -1764,54 +1858,60 @@
         <v>31</v>
       </c>
       <c r="Q22" s="2">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="R22" s="2">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="S22" s="2">
-        <v>1.5</v>
-      </c>
-      <c r="T22" t="str">
+        <v>0.5</v>
+      </c>
+      <c r="T22" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="U22" t="str">
         <f t="shared" si="2"/>
         <v>E[_]SPV*</v>
       </c>
-      <c r="W22" t="str">
-        <f t="shared" ref="W22" si="7">W18</f>
+      <c r="X22" t="str">
+        <f t="shared" ref="X22" si="7">X18</f>
         <v>Solar photovoltaics - Large scale unit</v>
       </c>
-      <c r="X22" t="str">
+      <c r="Y22" t="str">
         <f t="shared" si="1"/>
         <v>E[_]SPV*</v>
       </c>
     </row>
-    <row r="23" spans="3:24" x14ac:dyDescent="0.35">
+    <row r="23" spans="3:25" x14ac:dyDescent="0.35">
       <c r="P23" s="2" t="s">
         <v>31</v>
       </c>
       <c r="Q23" s="2">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="R23" s="2">
-        <v>7</v>
+        <v>3.5</v>
       </c>
       <c r="S23" s="2">
-        <v>5</v>
-      </c>
-      <c r="T23" t="str">
+        <v>3.5</v>
+      </c>
+      <c r="T23" s="2">
+        <v>3.5</v>
+      </c>
+      <c r="U23" t="str">
         <f t="shared" si="2"/>
         <v>E[_]WOF*</v>
       </c>
-      <c r="W23" t="str">
-        <f t="shared" ref="W23" si="8">W19</f>
+      <c r="X23" t="str">
+        <f t="shared" ref="X23" si="8">X19</f>
         <v>Wind offshore</v>
       </c>
-      <c r="X23" t="str">
+      <c r="Y23" t="str">
         <f t="shared" si="1"/>
         <v>E[_]WOF*</v>
       </c>
     </row>
-    <row r="24" spans="3:24" x14ac:dyDescent="0.35">
+    <row r="24" spans="3:25" x14ac:dyDescent="0.35">
       <c r="P24" s="2" t="s">
         <v>31</v>
       </c>
@@ -1824,29 +1924,86 @@
       <c r="S24" s="2">
         <v>1.5</v>
       </c>
-      <c r="T24" t="str">
+      <c r="T24" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="U24" t="str">
         <f t="shared" si="2"/>
         <v>E[_]WON*</v>
       </c>
-      <c r="W24" t="str">
-        <f t="shared" ref="W24" si="9">W20</f>
+      <c r="X24" t="str">
+        <f t="shared" ref="X24" si="9">X20</f>
         <v>Wind onshore</v>
       </c>
-      <c r="X24" t="str">
+      <c r="Y24" t="str">
         <f t="shared" si="1"/>
         <v>E[_]WON*</v>
       </c>
     </row>
-    <row r="26" spans="3:24" x14ac:dyDescent="0.35">
-      <c r="P26" s="2"/>
-    </row>
-    <row r="27" spans="3:24" x14ac:dyDescent="0.35">
+    <row r="25" spans="3:25" x14ac:dyDescent="0.35">
+      <c r="P25" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="Q25" s="2">
+        <v>0</v>
+      </c>
+      <c r="R25" s="2">
+        <v>0</v>
+      </c>
+      <c r="S25" s="2">
+        <v>0</v>
+      </c>
+      <c r="T25" s="2">
+        <v>0</v>
+      </c>
+      <c r="U25" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="26" spans="3:25" x14ac:dyDescent="0.35">
+      <c r="P26" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="Q26" s="2">
+        <v>4.41</v>
+      </c>
+      <c r="R26" s="2">
+        <v>3.45</v>
+      </c>
+      <c r="S26" s="2">
+        <v>3.16</v>
+      </c>
+      <c r="T26" s="2">
+        <v>2.99</v>
+      </c>
+      <c r="U26" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="27" spans="3:25" x14ac:dyDescent="0.35">
       <c r="C27" t="s">
         <v>4</v>
       </c>
-      <c r="P27" s="2"/>
-    </row>
-    <row r="28" spans="3:24" x14ac:dyDescent="0.35">
+      <c r="P27" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="Q27" s="2">
+        <v>2.06</v>
+      </c>
+      <c r="R27" s="2">
+        <v>1.98</v>
+      </c>
+      <c r="S27" s="2">
+        <v>1.89</v>
+      </c>
+      <c r="T27" s="2">
+        <v>1.85</v>
+      </c>
+      <c r="U27" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="28" spans="3:25" x14ac:dyDescent="0.35">
       <c r="C28" t="s">
         <v>16</v>
       </c>
@@ -1864,7 +2021,7 @@
       </c>
       <c r="P28" s="2"/>
     </row>
-    <row r="29" spans="3:24" x14ac:dyDescent="0.35">
+    <row r="29" spans="3:25" x14ac:dyDescent="0.35">
       <c r="C29" t="s">
         <v>17</v>
       </c>
@@ -1876,7 +2033,7 @@
       </c>
       <c r="P29" s="2"/>
     </row>
-    <row r="30" spans="3:24" x14ac:dyDescent="0.35">
+    <row r="30" spans="3:25" x14ac:dyDescent="0.35">
       <c r="C30" t="s">
         <v>53</v>
       </c>
@@ -1887,7 +2044,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="3:24" x14ac:dyDescent="0.35">
+    <row r="31" spans="3:25" x14ac:dyDescent="0.35">
       <c r="C31" t="s">
         <v>17</v>
       </c>
@@ -1898,7 +2055,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="32" spans="3:24" x14ac:dyDescent="0.35">
+    <row r="32" spans="3:25" x14ac:dyDescent="0.35">
       <c r="D32" t="s">
         <v>7</v>
       </c>
@@ -2102,6 +2259,7 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
 

--- a/VerveStacks_EST/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
+++ b/VerveStacks_EST/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\PycharmProjects\ee-times\VerveStacks_EST\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2CD20DCC-8DD7-4157-9064-28049531E8B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{582F4E77-726D-4476-BD9C-ACF6F81D23BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-10470" yWindow="10890" windowWidth="19420" windowHeight="11500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-38520" yWindow="-5220" windowWidth="38640" windowHeight="21120" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="AVA" sheetId="6" r:id="rId1"/>
@@ -74,7 +74,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="307" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="313" uniqueCount="80">
   <si>
     <t>PSET_PN</t>
   </si>
@@ -311,13 +311,16 @@
   </si>
   <si>
     <t>act_cost</t>
+  </si>
+  <si>
+    <t>E[_]SPV*,E[_]WON*</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -331,13 +334,6 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color indexed="81"/>
-      <name val="Tahoma"/>
-      <family val="2"/>
-      <charset val="186"/>
     </font>
   </fonts>
   <fills count="2">
@@ -666,20 +662,20 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{268E9BAB-B98F-4B82-9042-51EABC9ED525}">
   <dimension ref="B3:C5"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="18.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.42578125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="27.54296875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="49.54296875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="27.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="49.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="4" spans="2:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
         <v>21</v>
       </c>
@@ -687,7 +683,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="5" spans="2:3" x14ac:dyDescent="0.35">
+    <row r="5" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
         <v>59</v>
       </c>
@@ -703,24 +699,24 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E3954DD3-0F24-46DF-B268-7A98442D0282}">
   <dimension ref="A1:O13"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="7.26953125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="5.7265625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.54296875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="29.81640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.54296875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="7.54296875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="8.54296875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15.1796875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="7.453125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="4.81640625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="3.81640625" bestFit="1" customWidth="1"/>
-    <col min="12" max="14" width="4.7265625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="5.1796875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="5.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="29.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="7.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.5703125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="7.42578125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="4.85546875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="3.85546875" bestFit="1" customWidth="1"/>
+    <col min="12" max="14" width="4.7109375" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="5.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>32</v>
       </c>
@@ -767,7 +763,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>44</v>
       </c>
@@ -814,7 +810,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>44</v>
       </c>
@@ -861,7 +857,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>44</v>
       </c>
@@ -908,7 +904,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>44</v>
       </c>
@@ -955,7 +951,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>44</v>
       </c>
@@ -1002,7 +998,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>44</v>
       </c>
@@ -1049,7 +1045,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>44</v>
       </c>
@@ -1096,7 +1092,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>44</v>
       </c>
@@ -1143,7 +1139,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>44</v>
       </c>
@@ -1190,7 +1186,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>44</v>
       </c>
@@ -1237,7 +1233,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>44</v>
       </c>
@@ -1284,7 +1280,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>44</v>
       </c>
@@ -1338,26 +1334,27 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="C4:Y55"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="C4:Y58"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="3" max="3" width="14.54296875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.7265625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.7109375" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="11" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="41.26953125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="10.453125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="5.453125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="5.7265625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="41.28515625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="5.42578125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="5.7109375" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="5" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="6.26953125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="4.26953125" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="11.7265625" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="10.1796875" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="11.453125" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="31.36328125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="6.28515625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="4.28515625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="28.42578125" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="31.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="4" spans="3:25" x14ac:dyDescent="0.35">
+    <row r="4" spans="3:25" x14ac:dyDescent="0.25">
       <c r="C4" t="s">
         <v>4</v>
       </c>
@@ -1371,7 +1368,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="5" spans="3:25" x14ac:dyDescent="0.35">
+    <row r="5" spans="3:25" x14ac:dyDescent="0.25">
       <c r="C5" t="s">
         <v>3</v>
       </c>
@@ -1397,7 +1394,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="6" spans="3:25" x14ac:dyDescent="0.35">
+    <row r="6" spans="3:25" x14ac:dyDescent="0.25">
       <c r="D6" t="s">
         <v>6</v>
       </c>
@@ -1417,7 +1414,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="7" spans="3:25" x14ac:dyDescent="0.35">
+    <row r="7" spans="3:25" x14ac:dyDescent="0.25">
       <c r="D7" t="s">
         <v>7</v>
       </c>
@@ -1437,7 +1434,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="8" spans="3:25" x14ac:dyDescent="0.35">
+    <row r="8" spans="3:25" x14ac:dyDescent="0.25">
       <c r="D8" t="s">
         <v>8</v>
       </c>
@@ -1448,7 +1445,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="3:25" x14ac:dyDescent="0.35">
+    <row r="9" spans="3:25" x14ac:dyDescent="0.25">
       <c r="D9" t="s">
         <v>9</v>
       </c>
@@ -1459,7 +1456,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="10" spans="3:25" x14ac:dyDescent="0.35">
+    <row r="10" spans="3:25" x14ac:dyDescent="0.25">
       <c r="D10" t="s">
         <v>10</v>
       </c>
@@ -1470,7 +1467,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="11" spans="3:25" x14ac:dyDescent="0.35">
+    <row r="11" spans="3:25" x14ac:dyDescent="0.25">
       <c r="D11" t="s">
         <v>6</v>
       </c>
@@ -1484,7 +1481,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="12" spans="3:25" x14ac:dyDescent="0.35">
+    <row r="12" spans="3:25" x14ac:dyDescent="0.25">
       <c r="P12" s="2" t="s">
         <v>25</v>
       </c>
@@ -1504,7 +1501,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="13" spans="3:25" x14ac:dyDescent="0.35">
+    <row r="13" spans="3:25" x14ac:dyDescent="0.25">
       <c r="C13" t="s">
         <v>4</v>
       </c>
@@ -1534,7 +1531,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="14" spans="3:25" x14ac:dyDescent="0.35">
+    <row r="14" spans="3:25" x14ac:dyDescent="0.25">
       <c r="C14" t="s">
         <v>3</v>
       </c>
@@ -1576,7 +1573,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="15" spans="3:25" x14ac:dyDescent="0.35">
+    <row r="15" spans="3:25" x14ac:dyDescent="0.25">
       <c r="C15" t="s">
         <v>11</v>
       </c>
@@ -1618,7 +1615,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="16" spans="3:25" x14ac:dyDescent="0.35">
+    <row r="16" spans="3:25" x14ac:dyDescent="0.25">
       <c r="D16" t="s">
         <v>6</v>
       </c>
@@ -1654,7 +1651,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="17" spans="3:25" x14ac:dyDescent="0.35">
+    <row r="17" spans="3:25" x14ac:dyDescent="0.25">
       <c r="D17" t="s">
         <v>13</v>
       </c>
@@ -1692,7 +1689,7 @@
         <v>EN[_]Hydro*</v>
       </c>
     </row>
-    <row r="18" spans="3:25" x14ac:dyDescent="0.35">
+    <row r="18" spans="3:25" x14ac:dyDescent="0.25">
       <c r="D18" t="s">
         <v>13</v>
       </c>
@@ -1730,7 +1727,7 @@
         <v>E[_]SPV*</v>
       </c>
     </row>
-    <row r="19" spans="3:25" x14ac:dyDescent="0.35">
+    <row r="19" spans="3:25" x14ac:dyDescent="0.25">
       <c r="D19" t="s">
         <v>7</v>
       </c>
@@ -1768,7 +1765,7 @@
         <v>E[_]WOF*</v>
       </c>
     </row>
-    <row r="20" spans="3:25" x14ac:dyDescent="0.35">
+    <row r="20" spans="3:25" x14ac:dyDescent="0.25">
       <c r="D20" t="s">
         <v>8</v>
       </c>
@@ -1806,7 +1803,7 @@
         <v>E[_]WON*</v>
       </c>
     </row>
-    <row r="21" spans="3:25" x14ac:dyDescent="0.35">
+    <row r="21" spans="3:25" x14ac:dyDescent="0.25">
       <c r="D21" t="s">
         <v>9</v>
       </c>
@@ -1844,7 +1841,7 @@
         <v>EN[_]Hydro*</v>
       </c>
     </row>
-    <row r="22" spans="3:25" x14ac:dyDescent="0.35">
+    <row r="22" spans="3:25" x14ac:dyDescent="0.25">
       <c r="D22" t="s">
         <v>10</v>
       </c>
@@ -1882,7 +1879,7 @@
         <v>E[_]SPV*</v>
       </c>
     </row>
-    <row r="23" spans="3:25" x14ac:dyDescent="0.35">
+    <row r="23" spans="3:25" x14ac:dyDescent="0.25">
       <c r="P23" s="2" t="s">
         <v>31</v>
       </c>
@@ -1911,7 +1908,7 @@
         <v>E[_]WOF*</v>
       </c>
     </row>
-    <row r="24" spans="3:25" x14ac:dyDescent="0.35">
+    <row r="24" spans="3:25" x14ac:dyDescent="0.25">
       <c r="P24" s="2" t="s">
         <v>31</v>
       </c>
@@ -1940,7 +1937,7 @@
         <v>E[_]WON*</v>
       </c>
     </row>
-    <row r="25" spans="3:25" x14ac:dyDescent="0.35">
+    <row r="25" spans="3:25" x14ac:dyDescent="0.25">
       <c r="P25" s="2" t="s">
         <v>78</v>
       </c>
@@ -1960,7 +1957,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="26" spans="3:25" x14ac:dyDescent="0.35">
+    <row r="26" spans="3:25" x14ac:dyDescent="0.25">
       <c r="P26" s="2" t="s">
         <v>78</v>
       </c>
@@ -1980,7 +1977,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="27" spans="3:25" x14ac:dyDescent="0.35">
+    <row r="27" spans="3:25" x14ac:dyDescent="0.25">
       <c r="C27" t="s">
         <v>4</v>
       </c>
@@ -2003,7 +2000,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="28" spans="3:25" x14ac:dyDescent="0.35">
+    <row r="28" spans="3:25" x14ac:dyDescent="0.25">
       <c r="C28" t="s">
         <v>16</v>
       </c>
@@ -2021,7 +2018,7 @@
       </c>
       <c r="P28" s="2"/>
     </row>
-    <row r="29" spans="3:25" x14ac:dyDescent="0.35">
+    <row r="29" spans="3:25" x14ac:dyDescent="0.25">
       <c r="C29" t="s">
         <v>17</v>
       </c>
@@ -2033,7 +2030,7 @@
       </c>
       <c r="P29" s="2"/>
     </row>
-    <row r="30" spans="3:25" x14ac:dyDescent="0.35">
+    <row r="30" spans="3:25" x14ac:dyDescent="0.25">
       <c r="C30" t="s">
         <v>53</v>
       </c>
@@ -2044,7 +2041,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="3:25" x14ac:dyDescent="0.35">
+    <row r="31" spans="3:25" x14ac:dyDescent="0.25">
       <c r="C31" t="s">
         <v>17</v>
       </c>
@@ -2055,7 +2052,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="32" spans="3:25" x14ac:dyDescent="0.35">
+    <row r="32" spans="3:25" x14ac:dyDescent="0.25">
       <c r="D32" t="s">
         <v>7</v>
       </c>
@@ -2065,8 +2062,11 @@
       <c r="G32">
         <v>200</v>
       </c>
-    </row>
-    <row r="33" spans="3:7" x14ac:dyDescent="0.35">
+      <c r="P32" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33" spans="3:18" x14ac:dyDescent="0.25">
       <c r="D33" t="s">
         <v>10</v>
       </c>
@@ -2076,8 +2076,17 @@
       <c r="G33">
         <v>30</v>
       </c>
-    </row>
-    <row r="34" spans="3:7" x14ac:dyDescent="0.35">
+      <c r="P33" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q33" t="s">
+        <v>26</v>
+      </c>
+      <c r="R33" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="34" spans="3:18" x14ac:dyDescent="0.25">
       <c r="D34" t="s">
         <v>9</v>
       </c>
@@ -2087,8 +2096,17 @@
       <c r="G34">
         <v>1</v>
       </c>
-    </row>
-    <row r="35" spans="3:7" x14ac:dyDescent="0.35">
+      <c r="P34" t="s">
+        <v>64</v>
+      </c>
+      <c r="Q34">
+        <v>2030</v>
+      </c>
+      <c r="R34" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="35" spans="3:18" x14ac:dyDescent="0.25">
       <c r="C35" t="s">
         <v>17</v>
       </c>
@@ -2102,12 +2120,12 @@
         <v>3</v>
       </c>
     </row>
-    <row r="38" spans="3:7" x14ac:dyDescent="0.35">
+    <row r="38" spans="3:18" x14ac:dyDescent="0.25">
       <c r="C38" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="39" spans="3:7" x14ac:dyDescent="0.35">
+    <row r="39" spans="3:18" x14ac:dyDescent="0.25">
       <c r="C39" t="s">
         <v>21</v>
       </c>
@@ -2118,7 +2136,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="40" spans="3:7" x14ac:dyDescent="0.35">
+    <row r="40" spans="3:18" x14ac:dyDescent="0.25">
       <c r="C40" t="s">
         <v>14</v>
       </c>
@@ -2129,7 +2147,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="41" spans="3:7" x14ac:dyDescent="0.35">
+    <row r="41" spans="3:18" x14ac:dyDescent="0.25">
       <c r="C41" t="s">
         <v>15</v>
       </c>
@@ -2140,7 +2158,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="42" spans="3:7" x14ac:dyDescent="0.35">
+    <row r="42" spans="3:18" x14ac:dyDescent="0.25">
       <c r="C42" t="s">
         <v>57</v>
       </c>
@@ -2151,7 +2169,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="43" spans="3:7" x14ac:dyDescent="0.35">
+    <row r="43" spans="3:18" x14ac:dyDescent="0.25">
       <c r="C43" t="s">
         <v>55</v>
       </c>
@@ -2162,7 +2180,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="44" spans="3:7" x14ac:dyDescent="0.35">
+    <row r="44" spans="3:18" x14ac:dyDescent="0.25">
       <c r="C44" t="s">
         <v>56</v>
       </c>
@@ -2173,12 +2191,12 @@
         <v>24</v>
       </c>
     </row>
-    <row r="47" spans="3:7" x14ac:dyDescent="0.35">
+    <row r="47" spans="3:18" x14ac:dyDescent="0.25">
       <c r="C47" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="48" spans="3:7" x14ac:dyDescent="0.35">
+    <row r="48" spans="3:18" x14ac:dyDescent="0.25">
       <c r="C48" t="s">
         <v>1</v>
       </c>
@@ -2192,7 +2210,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="49" spans="3:8" x14ac:dyDescent="0.35">
+    <row r="49" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C49" t="s">
         <v>64</v>
       </c>
@@ -2206,7 +2224,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="50" spans="3:8" x14ac:dyDescent="0.35">
+    <row r="50" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C50" t="s">
         <v>69</v>
       </c>
@@ -2220,40 +2238,42 @@
         <v>71</v>
       </c>
     </row>
-    <row r="53" spans="3:8" x14ac:dyDescent="0.35">
-      <c r="C53" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="54" spans="3:8" x14ac:dyDescent="0.35">
-      <c r="C54" t="s">
-        <v>1</v>
-      </c>
-      <c r="D54" t="s">
-        <v>26</v>
-      </c>
-      <c r="E54" t="s">
-        <v>66</v>
-      </c>
-      <c r="F54" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="55" spans="3:8" x14ac:dyDescent="0.35">
-      <c r="C55" t="s">
-        <v>64</v>
-      </c>
-      <c r="D55">
-        <v>2030</v>
-      </c>
-      <c r="E55" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="F55" t="s">
-        <v>76</v>
-      </c>
+    <row r="55" spans="3:8" x14ac:dyDescent="0.25">
       <c r="H55" t="s">
         <v>77</v>
+      </c>
+    </row>
+    <row r="56" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="C56" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="57" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="C57" t="s">
+        <v>1</v>
+      </c>
+      <c r="D57" t="s">
+        <v>26</v>
+      </c>
+      <c r="E57" t="s">
+        <v>66</v>
+      </c>
+      <c r="F57" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="58" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="C58" t="s">
+        <v>64</v>
+      </c>
+      <c r="D58">
+        <v>2030</v>
+      </c>
+      <c r="E58" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="F58" t="s">
+        <v>76</v>
       </c>
     </row>
   </sheetData>

--- a/VerveStacks_EST/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
+++ b/VerveStacks_EST/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\PycharmProjects\ee-times\VerveStacks_EST\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{582F4E77-726D-4476-BD9C-ACF6F81D23BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D27662D1-3836-40DD-928A-5735B4951C6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-38520" yWindow="-5220" windowWidth="38640" windowHeight="21120" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="AVA" sheetId="6" r:id="rId1"/>
@@ -313,7 +313,7 @@
     <t>act_cost</t>
   </si>
   <si>
-    <t>E[_]SPV*,E[_]WON*</t>
+    <t>E[_]SPV*,E[_]WON*,E[_]WOF*</t>
   </si>
 </sst>
 </file>

--- a/VerveStacks_EST/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
+++ b/VerveStacks_EST/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\PycharmProjects\ee-times\VerveStacks_EST\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D27662D1-3836-40DD-928A-5735B4951C6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CBD1B215-7523-4B76-AABC-9AA5AD9B276E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -74,7 +74,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="313" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="315" uniqueCount="80">
   <si>
     <t>PSET_PN</t>
   </si>
@@ -313,7 +313,7 @@
     <t>act_cost</t>
   </si>
   <si>
-    <t>E[_]SPV*,E[_]WON*,E[_]WOF*</t>
+    <t>E[_]SPV*,E[_]WON*</t>
   </si>
 </sst>
 </file>
@@ -2119,6 +2119,15 @@
       <c r="G35">
         <v>3</v>
       </c>
+      <c r="P35" t="s">
+        <v>64</v>
+      </c>
+      <c r="Q35">
+        <v>2035</v>
+      </c>
+      <c r="R35" t="s">
+        <v>55</v>
+      </c>
     </row>
     <row r="38" spans="3:18" x14ac:dyDescent="0.25">
       <c r="C38" t="s">

--- a/VerveStacks_EST/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
+++ b/VerveStacks_EST/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
   <workbookPr updateLinks="never"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\PycharmProjects\ee-times\VerveStacks_EST\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CBD1B215-7523-4B76-AABC-9AA5AD9B276E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A79143AB-3EFE-413A-A153-48F6C6FB4B51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -74,7 +74,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="315" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="317" uniqueCount="81">
   <si>
     <t>PSET_PN</t>
   </si>
@@ -289,9 +289,6 @@
     <t>-life</t>
   </si>
   <si>
-    <t>coal,gas,nuclear,bioenergy</t>
-  </si>
-  <si>
     <t>windoff</t>
   </si>
   <si>
@@ -314,6 +311,12 @@
   </si>
   <si>
     <t>E[_]SPV*,E[_]WON*</t>
+  </si>
+  <si>
+    <t>coal,gas,bioenergy,nuclear</t>
+  </si>
+  <si>
+    <t>FERMI NUCLEAR</t>
   </si>
 </sst>
 </file>
@@ -1939,7 +1942,7 @@
     </row>
     <row r="25" spans="3:25" x14ac:dyDescent="0.25">
       <c r="P25" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="Q25" s="2">
         <v>0</v>
@@ -1959,7 +1962,7 @@
     </row>
     <row r="26" spans="3:25" x14ac:dyDescent="0.25">
       <c r="P26" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="Q26" s="2">
         <v>4.41</v>
@@ -1982,7 +1985,7 @@
         <v>4</v>
       </c>
       <c r="P27" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="Q27" s="2">
         <v>2.06</v>
@@ -2103,7 +2106,7 @@
         <v>2030</v>
       </c>
       <c r="R34" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="35" spans="3:18" x14ac:dyDescent="0.25">
@@ -2129,6 +2132,17 @@
         <v>55</v>
       </c>
     </row>
+    <row r="36" spans="3:18" x14ac:dyDescent="0.25">
+      <c r="P36" t="s">
+        <v>64</v>
+      </c>
+      <c r="Q36">
+        <v>2036</v>
+      </c>
+      <c r="R36" t="s">
+        <v>80</v>
+      </c>
+    </row>
     <row r="38" spans="3:18" x14ac:dyDescent="0.25">
       <c r="C38" t="s">
         <v>20</v>
@@ -2161,7 +2175,7 @@
         <v>15</v>
       </c>
       <c r="D41" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E41" t="s">
         <v>24</v>
@@ -2183,7 +2197,7 @@
         <v>55</v>
       </c>
       <c r="D43" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E43" t="s">
         <v>24</v>
@@ -2194,7 +2208,7 @@
         <v>56</v>
       </c>
       <c r="D44" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E44" t="s">
         <v>24</v>
@@ -2244,12 +2258,12 @@
         <v>70</v>
       </c>
       <c r="F50" t="s">
-        <v>71</v>
+        <v>79</v>
       </c>
     </row>
     <row r="55" spans="3:8" x14ac:dyDescent="0.25">
       <c r="H55" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="56" spans="3:8" x14ac:dyDescent="0.25">
@@ -2268,7 +2282,7 @@
         <v>66</v>
       </c>
       <c r="F57" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="58" spans="3:8" x14ac:dyDescent="0.25">
@@ -2282,7 +2296,7 @@
         <v>67</v>
       </c>
       <c r="F58" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
   </sheetData>

--- a/VerveStacks_EST/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
+++ b/VerveStacks_EST/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\PycharmProjects\ee-times\VerveStacks_EST\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A79143AB-3EFE-413A-A153-48F6C6FB4B51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED7709A2-1A65-4FE6-8EF2-D59611DB93BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -74,7 +74,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="317" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="318" uniqueCount="82">
   <si>
     <t>PSET_PN</t>
   </si>
@@ -317,6 +317,9 @@
   </si>
   <si>
     <t>FERMI NUCLEAR</t>
+  </si>
+  <si>
+    <t>~TFM_UPD</t>
   </si>
 </sst>
 </file>
@@ -2132,21 +2135,13 @@
         <v>55</v>
       </c>
     </row>
-    <row r="36" spans="3:18" x14ac:dyDescent="0.25">
-      <c r="P36" t="s">
-        <v>64</v>
-      </c>
-      <c r="Q36">
-        <v>2036</v>
-      </c>
-      <c r="R36" t="s">
-        <v>80</v>
-      </c>
-    </row>
     <row r="38" spans="3:18" x14ac:dyDescent="0.25">
       <c r="C38" t="s">
         <v>20</v>
       </c>
+      <c r="P38" t="s">
+        <v>81</v>
+      </c>
     </row>
     <row r="39" spans="3:18" x14ac:dyDescent="0.25">
       <c r="C39" t="s">
@@ -2157,6 +2152,15 @@
       </c>
       <c r="E39" t="s">
         <v>23</v>
+      </c>
+      <c r="P39" t="s">
+        <v>64</v>
+      </c>
+      <c r="Q39">
+        <v>2036</v>
+      </c>
+      <c r="R39" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="40" spans="3:18" x14ac:dyDescent="0.25">

--- a/VerveStacks_EST/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
+++ b/VerveStacks_EST/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\PycharmProjects\ee-times\VerveStacks_EST\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED7709A2-1A65-4FE6-8EF2-D59611DB93BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B87E3625-3214-409B-99E7-6419C335611F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -74,7 +74,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="318" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="321" uniqueCount="82">
   <si>
     <t>PSET_PN</t>
   </si>
@@ -2154,13 +2154,13 @@
         <v>23</v>
       </c>
       <c r="P39" t="s">
-        <v>64</v>
-      </c>
-      <c r="Q39">
-        <v>2036</v>
+        <v>1</v>
+      </c>
+      <c r="Q39" t="s">
+        <v>26</v>
       </c>
       <c r="R39" t="s">
-        <v>80</v>
+        <v>21</v>
       </c>
     </row>
     <row r="40" spans="3:18" x14ac:dyDescent="0.25">
@@ -2172,6 +2172,15 @@
       </c>
       <c r="E40" t="s">
         <v>24</v>
+      </c>
+      <c r="P40" t="s">
+        <v>64</v>
+      </c>
+      <c r="Q40">
+        <v>2036</v>
+      </c>
+      <c r="R40" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="41" spans="3:18" x14ac:dyDescent="0.25">

--- a/VerveStacks_EST/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
+++ b/VerveStacks_EST/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\PycharmProjects\ee-times\VerveStacks_EST\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B87E3625-3214-409B-99E7-6419C335611F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1950043-3E20-4619-A714-31D99239DDB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -316,10 +316,10 @@
     <t>coal,gas,bioenergy,nuclear</t>
   </si>
   <si>
-    <t>FERMI NUCLEAR</t>
-  </si>
-  <si>
     <t>~TFM_UPD</t>
+  </si>
+  <si>
+    <t>Fermi Nuclear</t>
   </si>
 </sst>
 </file>
@@ -2140,7 +2140,7 @@
         <v>20</v>
       </c>
       <c r="P38" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="39" spans="3:18" x14ac:dyDescent="0.25">
@@ -2180,7 +2180,7 @@
         <v>2036</v>
       </c>
       <c r="R40" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="41" spans="3:18" x14ac:dyDescent="0.25">

--- a/VerveStacks_EST/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
+++ b/VerveStacks_EST/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\PycharmProjects\ee-times\VerveStacks_EST\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1950043-3E20-4619-A714-31D99239DDB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99CAF845-231C-463A-AE2F-693108395F67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -74,7 +74,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="321" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="323" uniqueCount="82">
   <si>
     <t>PSET_PN</t>
   </si>
@@ -280,9 +280,6 @@
     <t>-pasti</t>
   </si>
   <si>
-    <t>solar,wind,coal,gas,nuclear,hydro,bioenergy</t>
-  </si>
-  <si>
     <t>life</t>
   </si>
   <si>
@@ -316,10 +313,13 @@
     <t>coal,gas,bioenergy,nuclear</t>
   </si>
   <si>
-    <t>~TFM_UPD</t>
-  </si>
-  <si>
     <t>Fermi Nuclear</t>
+  </si>
+  <si>
+    <t>solar,wind,coal,gas,hydro,bioenergy</t>
+  </si>
+  <si>
+    <t>Nuclear large</t>
   </si>
 </sst>
 </file>
@@ -1945,7 +1945,7 @@
     </row>
     <row r="25" spans="3:25" x14ac:dyDescent="0.25">
       <c r="P25" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="Q25" s="2">
         <v>0</v>
@@ -1965,7 +1965,7 @@
     </row>
     <row r="26" spans="3:25" x14ac:dyDescent="0.25">
       <c r="P26" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="Q26" s="2">
         <v>4.41</v>
@@ -1988,7 +1988,7 @@
         <v>4</v>
       </c>
       <c r="P27" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="Q27" s="2">
         <v>2.06</v>
@@ -2109,7 +2109,7 @@
         <v>2030</v>
       </c>
       <c r="R34" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="35" spans="3:18" x14ac:dyDescent="0.25">
@@ -2140,7 +2140,7 @@
         <v>20</v>
       </c>
       <c r="P38" t="s">
-        <v>80</v>
+        <v>4</v>
       </c>
     </row>
     <row r="39" spans="3:18" x14ac:dyDescent="0.25">
@@ -2180,7 +2180,7 @@
         <v>2036</v>
       </c>
       <c r="R40" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="41" spans="3:18" x14ac:dyDescent="0.25">
@@ -2188,10 +2188,19 @@
         <v>15</v>
       </c>
       <c r="D41" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E41" t="s">
         <v>24</v>
+      </c>
+      <c r="P41" t="s">
+        <v>64</v>
+      </c>
+      <c r="Q41">
+        <v>2030</v>
+      </c>
+      <c r="R41" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="42" spans="3:18" x14ac:dyDescent="0.25">
@@ -2210,7 +2219,7 @@
         <v>55</v>
       </c>
       <c r="D43" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E43" t="s">
         <v>24</v>
@@ -2221,7 +2230,7 @@
         <v>56</v>
       </c>
       <c r="D44" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E44" t="s">
         <v>24</v>
@@ -2257,26 +2266,26 @@
         <v>67</v>
       </c>
       <c r="F49" t="s">
-        <v>68</v>
+        <v>80</v>
       </c>
     </row>
     <row r="50" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C50" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D50">
         <v>40</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F50" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="55" spans="3:8" x14ac:dyDescent="0.25">
       <c r="H55" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="56" spans="3:8" x14ac:dyDescent="0.25">
@@ -2295,7 +2304,7 @@
         <v>66</v>
       </c>
       <c r="F57" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="58" spans="3:8" x14ac:dyDescent="0.25">
@@ -2309,7 +2318,7 @@
         <v>67</v>
       </c>
       <c r="F58" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
   </sheetData>

--- a/VerveStacks_EST/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
+++ b/VerveStacks_EST/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\PycharmProjects\ee-times\VerveStacks_EST\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB248CC2-2E77-4824-ACA8-5FA8EF37019E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41CCFDA5-602E-4DA6-B599-DAB2B460169E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-38520" yWindow="-5220" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="AVA" sheetId="6" r:id="rId1"/>
@@ -73,7 +73,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="73">
   <si>
     <t>Attribute</t>
   </si>
@@ -299,7 +299,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
   <fonts count="10" x14ac:knownFonts="1">
     <font>
@@ -326,6 +326,8 @@
     <font>
       <sz val="10"/>
       <name val="Arial"/>
+      <family val="2"/>
+      <charset val="186"/>
     </font>
     <font>
       <b/>
@@ -413,7 +415,7 @@
   <cellStyleXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
@@ -426,7 +428,7 @@
     <xf numFmtId="9" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -444,8 +446,7 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="14">
     <cellStyle name="Comma 2" xfId="2" xr:uid="{9640D755-0D23-4E24-A066-51A16F3F8D30}"/>
@@ -1272,50 +1273,6 @@
         <v>47</v>
       </c>
     </row>
-    <row r="41" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="D41" t="s">
-        <v>40</v>
-      </c>
-      <c r="F41">
-        <v>2030</v>
-      </c>
-      <c r="G41" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="42" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="D42" t="s">
-        <v>40</v>
-      </c>
-      <c r="F42">
-        <v>2035</v>
-      </c>
-      <c r="G42" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="43" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="D43" t="s">
-        <v>40</v>
-      </c>
-      <c r="F43">
-        <v>2036</v>
-      </c>
-      <c r="G43" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="44" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="D44" t="s">
-        <v>40</v>
-      </c>
-      <c r="F44">
-        <v>2030</v>
-      </c>
-      <c r="G44" t="s">
-        <v>53</v>
-      </c>
-    </row>
     <row r="47" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B47" s="7" t="s">
         <v>28</v>
@@ -1334,16 +1291,16 @@
       <c r="D48" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="E48" s="13">
+      <c r="E48" s="10">
         <v>2023</v>
       </c>
-      <c r="F48" s="13">
+      <c r="F48" s="10">
         <v>2030</v>
       </c>
       <c r="G48" s="10">
         <v>2040</v>
       </c>
-      <c r="H48" s="13">
+      <c r="H48" s="10">
         <v>2050</v>
       </c>
       <c r="I48" s="12" t="s">
@@ -1783,7 +1740,7 @@
       <c r="I66" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="J66" s="14"/>
+      <c r="J66" s="13"/>
     </row>
     <row r="67" spans="2:10" x14ac:dyDescent="0.25">
       <c r="G67" t="s">

--- a/VerveStacks_EST/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
+++ b/VerveStacks_EST/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\PycharmProjects\ee-times\VerveStacks_EST\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41CCFDA5-602E-4DA6-B599-DAB2B460169E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30ECE5CC-BC7B-433E-88E1-6FF8D6BFBDC6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -73,7 +73,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="73">
   <si>
     <t>Attribute</t>
   </si>
@@ -807,7 +807,7 @@
     <col min="6" max="6" width="41.28515625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="18.85546875" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="10.42578125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="31.140625" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="8.85546875" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="10.7109375" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="6.28515625" bestFit="1" customWidth="1"/>
@@ -1716,84 +1716,71 @@
       <c r="E65" s="4"/>
     </row>
     <row r="66" spans="2:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B66" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="C66" s="8" t="s">
-        <v>2</v>
-      </c>
-      <c r="D66" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="E66" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="F66" s="10" t="s">
-        <v>68</v>
-      </c>
-      <c r="G66" s="12" t="s">
+      <c r="B66" s="12" t="s">
         <v>69</v>
       </c>
-      <c r="H66" s="9" t="s">
+      <c r="C66" s="12" t="s">
         <v>71</v>
       </c>
-      <c r="I66" s="9" t="s">
+      <c r="D66" s="12" t="s">
         <v>72</v>
       </c>
+      <c r="E66" s="8"/>
+      <c r="F66" s="10"/>
       <c r="J66" s="13"/>
     </row>
     <row r="67" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="G67" t="s">
+      <c r="B67" t="s">
         <v>13</v>
       </c>
-      <c r="H67" t="s">
+      <c r="C67" t="s">
         <v>37</v>
       </c>
-      <c r="I67" t="s">
+      <c r="D67" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="68" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="G68" t="s">
+      <c r="B68" t="s">
         <v>14</v>
       </c>
-      <c r="H68" t="s">
+      <c r="C68" t="s">
         <v>46</v>
       </c>
-      <c r="I68" t="s">
+      <c r="D68" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="69" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="G69" t="s">
+      <c r="B69" t="s">
         <v>33</v>
       </c>
-      <c r="H69" t="s">
+      <c r="C69" t="s">
         <v>39</v>
       </c>
-      <c r="I69" t="s">
+      <c r="D69" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="70" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="G70" t="s">
+      <c r="B70" t="s">
         <v>31</v>
       </c>
-      <c r="H70" t="s">
+      <c r="C70" t="s">
         <v>44</v>
       </c>
-      <c r="I70" t="s">
+      <c r="D70" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="71" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="G71" t="s">
+      <c r="B71" t="s">
         <v>32</v>
       </c>
-      <c r="H71" t="s">
+      <c r="C71" t="s">
         <v>45</v>
       </c>
-      <c r="I71" t="s">
+      <c r="D71" t="s">
         <v>20</v>
       </c>
     </row>

--- a/VerveStacks_EST/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
+++ b/VerveStacks_EST/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\PycharmProjects\ee-times\VerveStacks_EST\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30ECE5CC-BC7B-433E-88E1-6FF8D6BFBDC6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD83EE5B-7552-4982-8AEE-6A36809C67B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -73,7 +73,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="74">
   <si>
     <t>Attribute</t>
   </si>
@@ -292,6 +292,9 @@
   </si>
   <si>
     <t>Io</t>
+  </si>
+  <si>
+    <t>* space</t>
   </si>
 </sst>
 </file>
@@ -1232,44 +1235,49 @@
       </c>
     </row>
     <row r="38" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="D38" t="s">
-        <v>40</v>
-      </c>
-      <c r="F38">
-        <v>2030</v>
-      </c>
-      <c r="H38" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="J38" t="s">
-        <v>52</v>
+      <c r="B38" t="s">
+        <v>73</v>
       </c>
     </row>
     <row r="39" spans="2:10" x14ac:dyDescent="0.25">
       <c r="D39" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F39">
-        <v>40</v>
+        <v>2030</v>
       </c>
       <c r="H39" s="3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="J39" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
     </row>
     <row r="40" spans="2:10" x14ac:dyDescent="0.25">
       <c r="D40" t="s">
+        <v>42</v>
+      </c>
+      <c r="F40">
         <v>40</v>
       </c>
-      <c r="F40">
+      <c r="H40" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="J40" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="41" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="D41" t="s">
+        <v>40</v>
+      </c>
+      <c r="F41">
         <v>2030</v>
       </c>
-      <c r="H40" s="3" t="s">
+      <c r="H41" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="I40" t="s">
+      <c r="I41" t="s">
         <v>47</v>
       </c>
     </row>

--- a/VerveStacks_EST/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
+++ b/VerveStacks_EST/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\PycharmProjects\ee-times\VerveStacks_EST\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD83EE5B-7552-4982-8AEE-6A36809C67B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C44BF0EA-2F65-4088-8D0F-94F5F25F713E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -44,7 +44,7 @@
     <author>tc={9326A9B6-D94C-4ED3-9FB8-434C0D4AC388}</author>
   </authors>
   <commentList>
-    <comment ref="I50" authorId="0" shapeId="0" xr:uid="{80A2C193-6148-4AA7-9B62-06322F60E0BF}">
+    <comment ref="I58" authorId="0" shapeId="0" xr:uid="{80A2C193-6148-4AA7-9B62-06322F60E0BF}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -52,7 +52,7 @@
     Utility-scale PV</t>
       </text>
     </comment>
-    <comment ref="I51" authorId="1" shapeId="0" xr:uid="{E6F93F18-BBEF-4E19-B2D0-A493D668847A}">
+    <comment ref="I59" authorId="1" shapeId="0" xr:uid="{E6F93F18-BBEF-4E19-B2D0-A493D668847A}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -60,7 +60,7 @@
     AC fixed</t>
       </text>
     </comment>
-    <comment ref="I62" authorId="2" shapeId="0" xr:uid="{9326A9B6-D94C-4ED3-9FB8-434C0D4AC388}">
+    <comment ref="I70" authorId="2" shapeId="0" xr:uid="{9326A9B6-D94C-4ED3-9FB8-434C0D4AC388}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -73,7 +73,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="73">
   <si>
     <t>Attribute</t>
   </si>
@@ -292,9 +292,6 @@
   </si>
   <si>
     <t>Io</t>
-  </si>
-  <si>
-    <t>* space</t>
   </si>
 </sst>
 </file>
@@ -749,13 +746,13 @@
 
 <file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
 <ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <threadedComment ref="I50" dT="2026-03-18T13:56:27.06" personId="{50AE587C-9924-43E9-9BB9-052BDB346AE2}" id="{80A2C193-6148-4AA7-9B62-06322F60E0BF}">
+  <threadedComment ref="I58" dT="2026-03-18T13:56:27.06" personId="{50AE587C-9924-43E9-9BB9-052BDB346AE2}" id="{80A2C193-6148-4AA7-9B62-06322F60E0BF}">
     <text>Utility-scale PV</text>
   </threadedComment>
-  <threadedComment ref="I51" dT="2026-03-18T13:39:46.05" personId="{50AE587C-9924-43E9-9BB9-052BDB346AE2}" id="{E6F93F18-BBEF-4E19-B2D0-A493D668847A}">
+  <threadedComment ref="I59" dT="2026-03-18T13:39:46.05" personId="{50AE587C-9924-43E9-9BB9-052BDB346AE2}" id="{E6F93F18-BBEF-4E19-B2D0-A493D668847A}">
     <text>AC fixed</text>
   </threadedComment>
-  <threadedComment ref="I62" dT="2026-03-18T13:39:46.05" personId="{50AE587C-9924-43E9-9BB9-052BDB346AE2}" id="{9326A9B6-D94C-4ED3-9FB8-434C0D4AC388}">
+  <threadedComment ref="I70" dT="2026-03-18T13:39:46.05" personId="{50AE587C-9924-43E9-9BB9-052BDB346AE2}" id="{9326A9B6-D94C-4ED3-9FB8-434C0D4AC388}">
     <text>AC fixed</text>
   </threadedComment>
 </ThreadedComments>
@@ -800,7 +797,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="B2:V71"/>
+  <dimension ref="B2:V79"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="14.140625" bestFit="1" customWidth="1"/>
@@ -1234,561 +1231,593 @@
         <v>53</v>
       </c>
     </row>
-    <row r="38" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B38" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="39" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="D39" t="s">
+    <row r="44" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B44" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C44" s="4"/>
+      <c r="D44" s="4"/>
+      <c r="E44" s="4"/>
+    </row>
+    <row r="45" spans="2:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B45" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="C45" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="D45" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="E45" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="F45" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="G45" s="12" t="s">
+        <v>69</v>
+      </c>
+      <c r="H45" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="I45" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="J45" s="9" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="46" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="D46" t="s">
         <v>40</v>
       </c>
-      <c r="F39">
+      <c r="F46">
         <v>2030</v>
       </c>
-      <c r="H39" s="3" t="s">
+      <c r="H46" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="J39" t="s">
+      <c r="J46" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="40" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="D40" t="s">
+    <row r="47" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="D47" t="s">
         <v>42</v>
       </c>
-      <c r="F40">
+      <c r="F47">
         <v>40</v>
       </c>
-      <c r="H40" s="3" t="s">
+      <c r="H47" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="J40" t="s">
+      <c r="J47" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="41" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="D41" t="s">
+    <row r="48" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="D48" t="s">
         <v>40</v>
       </c>
-      <c r="F41">
+      <c r="F48">
         <v>2030</v>
       </c>
-      <c r="H41" s="3" t="s">
+      <c r="H48" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="I41" t="s">
+      <c r="I48" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="47" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B47" s="7" t="s">
+    <row r="55" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B55" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="C47" s="4"/>
-      <c r="D47" s="4"/>
-      <c r="E47" s="4"/>
-    </row>
-    <row r="48" spans="2:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B48" s="8" t="s">
+      <c r="C55" s="4"/>
+      <c r="D55" s="4"/>
+      <c r="E55" s="4"/>
+    </row>
+    <row r="56" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B56" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="C48" s="8" t="s">
+      <c r="C56" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="D48" s="8" t="s">
+      <c r="D56" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="E48" s="10">
+      <c r="E56" s="10">
         <v>2023</v>
       </c>
-      <c r="F48" s="10">
+      <c r="F56" s="10">
         <v>2030</v>
       </c>
-      <c r="G48" s="10">
+      <c r="G56" s="10">
         <v>2040</v>
       </c>
-      <c r="H48" s="10">
+      <c r="H56" s="10">
         <v>2050</v>
       </c>
-      <c r="I48" s="12" t="s">
+      <c r="I56" s="12" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="49" spans="4:13" x14ac:dyDescent="0.25">
-      <c r="D49" s="2" t="s">
+    <row r="57" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="D57" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="E49" s="2">
+      <c r="E57" s="2">
         <v>2700</v>
       </c>
-      <c r="F49" s="2">
+      <c r="F57" s="2">
         <v>2700</v>
       </c>
-      <c r="G49" s="2">
+      <c r="G57" s="2">
         <v>2700</v>
       </c>
-      <c r="H49" s="2">
+      <c r="H57" s="2">
         <v>2700</v>
       </c>
-      <c r="I49" t="str">
-        <f>M49</f>
+      <c r="I57" t="str">
+        <f>M57</f>
         <v>EN[_]Hydro*</v>
       </c>
-      <c r="L49" t="s">
+      <c r="L57" t="s">
         <v>24</v>
       </c>
-      <c r="M49" t="s">
+      <c r="M57" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="50" spans="4:13" x14ac:dyDescent="0.25">
-      <c r="D50" s="2" t="s">
+    <row r="58" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="D58" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="E50" s="2">
+      <c r="E58" s="2">
         <v>560</v>
       </c>
-      <c r="F50" s="2">
+      <c r="F58" s="2">
         <v>380</v>
       </c>
-      <c r="G50">
+      <c r="G58">
         <v>320</v>
       </c>
-      <c r="H50" s="2">
+      <c r="H58" s="2">
         <v>290</v>
       </c>
-      <c r="I50" t="str">
-        <f t="shared" ref="I50:I52" si="0">M50</f>
+      <c r="I58" t="str">
+        <f t="shared" ref="I58:I60" si="0">M58</f>
         <v>E[_]SPV*</v>
       </c>
-      <c r="L50" t="s">
+      <c r="L58" t="s">
         <v>25</v>
       </c>
-      <c r="M50" t="s">
+      <c r="M58" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="51" spans="4:13" x14ac:dyDescent="0.25">
-      <c r="D51" s="2" t="s">
+    <row r="59" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="D59" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="E51" s="2">
+      <c r="E59" s="2">
         <v>2780</v>
       </c>
-      <c r="F51" s="2">
+      <c r="F59" s="2">
         <v>2390</v>
       </c>
-      <c r="G51" s="2">
+      <c r="G59" s="2">
         <v>2140</v>
       </c>
-      <c r="H51" s="2">
+      <c r="H59" s="2">
         <v>1990</v>
       </c>
-      <c r="I51" t="str">
+      <c r="I59" t="str">
         <f t="shared" si="0"/>
         <v>E[_]WOF*</v>
       </c>
-      <c r="L51" t="s">
+      <c r="L59" t="s">
         <v>26</v>
       </c>
-      <c r="M51" t="s">
+      <c r="M59" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="52" spans="4:13" x14ac:dyDescent="0.25">
-      <c r="D52" s="2" t="s">
+    <row r="60" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="D60" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="E52" s="2">
+      <c r="E60" s="2">
         <v>1180</v>
       </c>
-      <c r="F52" s="2">
+      <c r="F60" s="2">
         <v>1150</v>
       </c>
-      <c r="G52" s="2">
+      <c r="G60" s="2">
         <v>1110</v>
       </c>
-      <c r="H52" s="2">
+      <c r="H60" s="2">
         <v>1090</v>
       </c>
-      <c r="I52" t="str">
+      <c r="I60" t="str">
         <f t="shared" si="0"/>
         <v>E[_]WON*</v>
       </c>
-      <c r="L52" t="s">
+      <c r="L60" t="s">
         <v>27</v>
       </c>
-      <c r="M52" t="s">
+      <c r="M60" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="53" spans="4:13" x14ac:dyDescent="0.25">
-      <c r="D53" s="2" t="s">
+    <row r="61" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="D61" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="E53" s="2">
+      <c r="E61" s="2">
         <v>70</v>
       </c>
-      <c r="F53" s="2">
+      <c r="F61" s="2">
         <v>65</v>
       </c>
-      <c r="G53" s="2">
+      <c r="G61" s="2">
         <v>65</v>
       </c>
-      <c r="H53" s="2">
+      <c r="H61" s="2">
         <v>65</v>
       </c>
-      <c r="I53" t="str">
-        <f>I49</f>
+      <c r="I61" t="str">
+        <f>I57</f>
         <v>EN[_]Hydro*</v>
       </c>
-      <c r="L53" t="str">
-        <f>L49</f>
+      <c r="L61" t="str">
+        <f>L57</f>
         <v>Hydropower - large-scale unit</v>
       </c>
-      <c r="M53" t="str">
-        <f t="shared" ref="M53:M60" si="1">M49</f>
+      <c r="M61" t="str">
+        <f t="shared" ref="M61:M68" si="1">M57</f>
         <v>EN[_]Hydro*</v>
       </c>
     </row>
-    <row r="54" spans="4:13" x14ac:dyDescent="0.25">
-      <c r="D54" s="2" t="s">
+    <row r="62" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="D62" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="E54" s="2">
+      <c r="E62" s="2">
         <v>11.5</v>
       </c>
-      <c r="F54" s="2">
+      <c r="F62" s="2">
         <v>9.5</v>
       </c>
-      <c r="G54" s="2">
+      <c r="G62" s="2">
         <v>8.1</v>
       </c>
-      <c r="H54" s="2">
+      <c r="H62" s="2">
         <v>7.4</v>
       </c>
-      <c r="I54" t="str">
-        <f t="shared" ref="I54:I60" si="2">I50</f>
+      <c r="I62" t="str">
+        <f t="shared" ref="I62:I68" si="2">I58</f>
         <v>E[_]SPV*</v>
       </c>
-      <c r="L54" t="str">
-        <f t="shared" ref="L54" si="3">L50</f>
+      <c r="L62" t="str">
+        <f t="shared" ref="L62" si="3">L58</f>
         <v>Solar photovoltaics - Large scale unit</v>
       </c>
-      <c r="M54" t="str">
+      <c r="M62" t="str">
         <f t="shared" si="1"/>
         <v>E[_]SPV*</v>
       </c>
     </row>
-    <row r="55" spans="4:13" x14ac:dyDescent="0.25">
-      <c r="D55" s="2" t="s">
+    <row r="63" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="D63" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="E55" s="2">
+      <c r="E63" s="2">
         <v>44</v>
       </c>
-      <c r="F55" s="2">
+      <c r="F63" s="2">
         <v>34</v>
       </c>
-      <c r="G55" s="2">
+      <c r="G63" s="2">
         <v>30</v>
       </c>
-      <c r="H55" s="2">
+      <c r="H63" s="2">
         <v>28</v>
       </c>
-      <c r="I55" t="str">
+      <c r="I63" t="str">
         <f t="shared" si="2"/>
         <v>E[_]WOF*</v>
       </c>
-      <c r="L55" t="str">
-        <f t="shared" ref="L55" si="4">L51</f>
+      <c r="L63" t="str">
+        <f t="shared" ref="L63" si="4">L59</f>
         <v>Wind offshore</v>
       </c>
-      <c r="M55" t="str">
+      <c r="M63" t="str">
         <f t="shared" si="1"/>
         <v>E[_]WOF*</v>
       </c>
     </row>
-    <row r="56" spans="4:13" x14ac:dyDescent="0.25">
-      <c r="D56" s="2" t="s">
+    <row r="64" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="D64" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="E56" s="2">
+      <c r="E64" s="2">
         <v>17.387</v>
       </c>
-      <c r="F56" s="2">
+      <c r="F64" s="2">
         <v>16.663</v>
       </c>
-      <c r="G56" s="2">
+      <c r="G64" s="2">
         <v>15.965</v>
       </c>
-      <c r="H56" s="2">
+      <c r="H64" s="2">
         <v>15.602</v>
       </c>
-      <c r="I56" t="str">
+      <c r="I64" t="str">
         <f t="shared" si="2"/>
         <v>E[_]WON*</v>
       </c>
-      <c r="L56" t="str">
-        <f t="shared" ref="L56" si="5">L52</f>
+      <c r="L64" t="str">
+        <f t="shared" ref="L64" si="5">L60</f>
         <v>Wind onshore</v>
       </c>
-      <c r="M56" t="str">
+      <c r="M64" t="str">
         <f t="shared" si="1"/>
         <v>E[_]WON*</v>
       </c>
     </row>
-    <row r="57" spans="4:13" x14ac:dyDescent="0.25">
-      <c r="D57" s="2" t="s">
+    <row r="65" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="D65" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="E57" s="2">
+      <c r="E65" s="2">
         <v>4</v>
       </c>
-      <c r="F57" s="2">
+      <c r="F65" s="2">
         <v>4</v>
       </c>
-      <c r="G57" s="2">
+      <c r="G65" s="2">
         <v>4</v>
       </c>
-      <c r="H57" s="2">
+      <c r="H65" s="2">
         <v>4</v>
       </c>
-      <c r="I57" t="str">
+      <c r="I65" t="str">
         <f t="shared" si="2"/>
         <v>EN[_]Hydro*</v>
       </c>
-      <c r="L57" t="str">
-        <f t="shared" ref="L57" si="6">L53</f>
+      <c r="L65" t="str">
+        <f t="shared" ref="L65" si="6">L61</f>
         <v>Hydropower - large-scale unit</v>
       </c>
-      <c r="M57" t="str">
+      <c r="M65" t="str">
         <f t="shared" si="1"/>
         <v>EN[_]Hydro*</v>
       </c>
     </row>
-    <row r="58" spans="4:13" x14ac:dyDescent="0.25">
-      <c r="D58" s="2" t="s">
+    <row r="66" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="D66" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="E58" s="2">
+      <c r="E66" s="2">
         <v>0.5</v>
       </c>
-      <c r="F58" s="2">
+      <c r="F66" s="2">
         <v>0.5</v>
       </c>
-      <c r="G58" s="2">
+      <c r="G66" s="2">
         <v>0.5</v>
       </c>
-      <c r="H58" s="2">
+      <c r="H66" s="2">
         <v>0.5</v>
       </c>
-      <c r="I58" t="str">
+      <c r="I66" t="str">
         <f t="shared" si="2"/>
         <v>E[_]SPV*</v>
       </c>
-      <c r="L58" t="str">
-        <f t="shared" ref="L58" si="7">L54</f>
+      <c r="L66" t="str">
+        <f t="shared" ref="L66" si="7">L62</f>
         <v>Solar photovoltaics - Large scale unit</v>
       </c>
-      <c r="M58" t="str">
+      <c r="M66" t="str">
         <f t="shared" si="1"/>
         <v>E[_]SPV*</v>
       </c>
     </row>
-    <row r="59" spans="4:13" x14ac:dyDescent="0.25">
-      <c r="D59" s="2" t="s">
+    <row r="67" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="D67" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="E59" s="2">
+      <c r="E67" s="2">
         <v>5</v>
       </c>
-      <c r="F59" s="2">
+      <c r="F67" s="2">
         <v>3.5</v>
       </c>
-      <c r="G59" s="2">
+      <c r="G67" s="2">
         <v>3.5</v>
       </c>
-      <c r="H59" s="2">
+      <c r="H67" s="2">
         <v>3.5</v>
       </c>
-      <c r="I59" t="str">
+      <c r="I67" t="str">
         <f t="shared" si="2"/>
         <v>E[_]WOF*</v>
       </c>
-      <c r="L59" t="str">
-        <f t="shared" ref="L59" si="8">L55</f>
+      <c r="L67" t="str">
+        <f t="shared" ref="L67" si="8">L63</f>
         <v>Wind offshore</v>
       </c>
-      <c r="M59" t="str">
+      <c r="M67" t="str">
         <f t="shared" si="1"/>
         <v>E[_]WOF*</v>
       </c>
     </row>
-    <row r="60" spans="4:13" x14ac:dyDescent="0.25">
-      <c r="D60" s="2" t="s">
+    <row r="68" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="D68" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="E60" s="2">
+      <c r="E68" s="2">
         <v>1.5</v>
       </c>
-      <c r="F60" s="2">
+      <c r="F68" s="2">
         <v>1.5</v>
       </c>
-      <c r="G60" s="2">
+      <c r="G68" s="2">
         <v>1.5</v>
       </c>
-      <c r="H60" s="2">
+      <c r="H68" s="2">
         <v>1.5</v>
       </c>
-      <c r="I60" t="str">
+      <c r="I68" t="str">
         <f t="shared" si="2"/>
         <v>E[_]WON*</v>
       </c>
-      <c r="L60" t="str">
-        <f t="shared" ref="L60" si="9">L56</f>
+      <c r="L68" t="str">
+        <f t="shared" ref="L68" si="9">L64</f>
         <v>Wind onshore</v>
       </c>
-      <c r="M60" t="str">
+      <c r="M68" t="str">
         <f t="shared" si="1"/>
         <v>E[_]WON*</v>
       </c>
     </row>
-    <row r="61" spans="4:13" x14ac:dyDescent="0.25">
-      <c r="D61" s="2" t="s">
+    <row r="69" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="D69" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="E61" s="2">
+      <c r="E69" s="2">
         <v>0</v>
       </c>
-      <c r="F61" s="2">
+      <c r="F69" s="2">
         <v>0</v>
       </c>
-      <c r="G61" s="2">
+      <c r="G69" s="2">
         <v>0</v>
       </c>
-      <c r="H61" s="2">
+      <c r="H69" s="2">
         <v>0</v>
       </c>
-      <c r="I61" t="s">
+      <c r="I69" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="62" spans="4:13" x14ac:dyDescent="0.25">
-      <c r="D62" s="2" t="s">
+    <row r="70" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="D70" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="E62" s="2">
+      <c r="E70" s="2">
         <v>4.41</v>
       </c>
-      <c r="F62" s="2">
+      <c r="F70" s="2">
         <v>3.45</v>
       </c>
-      <c r="G62" s="2">
+      <c r="G70" s="2">
         <v>3.16</v>
       </c>
-      <c r="H62" s="2">
+      <c r="H70" s="2">
         <v>2.99</v>
       </c>
-      <c r="I62" t="s">
+      <c r="I70" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="63" spans="4:13" x14ac:dyDescent="0.25">
-      <c r="D63" s="2" t="s">
+    <row r="71" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="D71" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="E63" s="2">
+      <c r="E71" s="2">
         <v>2.06</v>
       </c>
-      <c r="F63" s="2">
+      <c r="F71" s="2">
         <v>1.98</v>
       </c>
-      <c r="G63" s="2">
+      <c r="G71" s="2">
         <v>1.89</v>
       </c>
-      <c r="H63" s="2">
+      <c r="H71" s="2">
         <v>1.85</v>
       </c>
-      <c r="I63" t="s">
+      <c r="I71" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="65" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B65" s="7" t="s">
+    <row r="73" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B73" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="C65" s="4"/>
-      <c r="D65" s="4"/>
-      <c r="E65" s="4"/>
-    </row>
-    <row r="66" spans="2:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B66" s="12" t="s">
+      <c r="C73" s="4"/>
+      <c r="D73" s="4"/>
+      <c r="E73" s="4"/>
+    </row>
+    <row r="74" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B74" s="12" t="s">
         <v>69</v>
       </c>
-      <c r="C66" s="12" t="s">
+      <c r="C74" s="12" t="s">
         <v>71</v>
       </c>
-      <c r="D66" s="12" t="s">
+      <c r="D74" s="12" t="s">
         <v>72</v>
       </c>
-      <c r="E66" s="8"/>
-      <c r="F66" s="10"/>
-      <c r="J66" s="13"/>
-    </row>
-    <row r="67" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B67" t="s">
+      <c r="E74" s="8"/>
+      <c r="F74" s="10"/>
+      <c r="J74" s="13"/>
+    </row>
+    <row r="75" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B75" t="s">
         <v>13</v>
       </c>
-      <c r="C67" t="s">
+      <c r="C75" t="s">
         <v>37</v>
       </c>
-      <c r="D67" t="s">
+      <c r="D75" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="68" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B68" t="s">
+    <row r="76" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B76" t="s">
         <v>14</v>
       </c>
-      <c r="C68" t="s">
+      <c r="C76" t="s">
         <v>46</v>
       </c>
-      <c r="D68" t="s">
+      <c r="D76" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="69" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B69" t="s">
+    <row r="77" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B77" t="s">
         <v>33</v>
       </c>
-      <c r="C69" t="s">
+      <c r="C77" t="s">
         <v>39</v>
       </c>
-      <c r="D69" t="s">
+      <c r="D77" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="70" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B70" t="s">
+    <row r="78" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B78" t="s">
         <v>31</v>
       </c>
-      <c r="C70" t="s">
+      <c r="C78" t="s">
         <v>44</v>
       </c>
-      <c r="D70" t="s">
+      <c r="D78" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="71" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B71" t="s">
+    <row r="79" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B79" t="s">
         <v>32</v>
       </c>
-      <c r="C71" t="s">
+      <c r="C79" t="s">
         <v>45</v>
       </c>
-      <c r="D71" t="s">
+      <c r="D79" t="s">
         <v>20</v>
       </c>
     </row>

--- a/VerveStacks_EST/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
+++ b/VerveStacks_EST/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\PycharmProjects\ee-times\VerveStacks_EST\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C44BF0EA-2F65-4088-8D0F-94F5F25F713E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E12E6D9B-8156-43B2-BBF1-F8710A46B0C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -44,7 +44,7 @@
     <author>tc={9326A9B6-D94C-4ED3-9FB8-434C0D4AC388}</author>
   </authors>
   <commentList>
-    <comment ref="I58" authorId="0" shapeId="0" xr:uid="{80A2C193-6148-4AA7-9B62-06322F60E0BF}">
+    <comment ref="I49" authorId="0" shapeId="0" xr:uid="{80A2C193-6148-4AA7-9B62-06322F60E0BF}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -52,7 +52,7 @@
     Utility-scale PV</t>
       </text>
     </comment>
-    <comment ref="I59" authorId="1" shapeId="0" xr:uid="{E6F93F18-BBEF-4E19-B2D0-A493D668847A}">
+    <comment ref="I50" authorId="1" shapeId="0" xr:uid="{E6F93F18-BBEF-4E19-B2D0-A493D668847A}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -60,7 +60,7 @@
     AC fixed</t>
       </text>
     </comment>
-    <comment ref="I70" authorId="2" shapeId="0" xr:uid="{9326A9B6-D94C-4ED3-9FB8-434C0D4AC388}">
+    <comment ref="I61" authorId="2" shapeId="0" xr:uid="{9326A9B6-D94C-4ED3-9FB8-434C0D4AC388}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -73,7 +73,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="73">
   <si>
     <t>Attribute</t>
   </si>
@@ -746,13 +746,13 @@
 
 <file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
 <ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <threadedComment ref="I58" dT="2026-03-18T13:56:27.06" personId="{50AE587C-9924-43E9-9BB9-052BDB346AE2}" id="{80A2C193-6148-4AA7-9B62-06322F60E0BF}">
+  <threadedComment ref="I49" dT="2026-03-18T13:56:27.06" personId="{50AE587C-9924-43E9-9BB9-052BDB346AE2}" id="{80A2C193-6148-4AA7-9B62-06322F60E0BF}">
     <text>Utility-scale PV</text>
   </threadedComment>
-  <threadedComment ref="I59" dT="2026-03-18T13:39:46.05" personId="{50AE587C-9924-43E9-9BB9-052BDB346AE2}" id="{E6F93F18-BBEF-4E19-B2D0-A493D668847A}">
+  <threadedComment ref="I50" dT="2026-03-18T13:39:46.05" personId="{50AE587C-9924-43E9-9BB9-052BDB346AE2}" id="{E6F93F18-BBEF-4E19-B2D0-A493D668847A}">
     <text>AC fixed</text>
   </threadedComment>
-  <threadedComment ref="I70" dT="2026-03-18T13:39:46.05" personId="{50AE587C-9924-43E9-9BB9-052BDB346AE2}" id="{9326A9B6-D94C-4ED3-9FB8-434C0D4AC388}">
+  <threadedComment ref="I61" dT="2026-03-18T13:39:46.05" personId="{50AE587C-9924-43E9-9BB9-052BDB346AE2}" id="{9326A9B6-D94C-4ED3-9FB8-434C0D4AC388}">
     <text>AC fixed</text>
   </threadedComment>
 </ThreadedComments>
@@ -797,7 +797,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="B2:V79"/>
+  <dimension ref="B2:V70"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="14.140625" bestFit="1" customWidth="1"/>
@@ -1158,7 +1158,7 @@
       <c r="D32" s="4"/>
       <c r="E32" s="4"/>
     </row>
-    <row r="33" spans="2:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B33" s="8" t="s">
         <v>54</v>
       </c>
@@ -1181,13 +1181,10 @@
         <v>70</v>
       </c>
       <c r="I33" s="9" t="s">
-        <v>58</v>
-      </c>
-      <c r="J33" s="9" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="34" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:13" x14ac:dyDescent="0.25">
       <c r="D34" t="s">
         <v>40</v>
       </c>
@@ -1198,7 +1195,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="35" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:13" x14ac:dyDescent="0.25">
       <c r="D35" t="s">
         <v>40</v>
       </c>
@@ -1209,7 +1206,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="36" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="36" spans="2:13" x14ac:dyDescent="0.25">
       <c r="D36" t="s">
         <v>40</v>
       </c>
@@ -1220,7 +1217,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="37" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="37" spans="2:13" x14ac:dyDescent="0.25">
       <c r="D37" t="s">
         <v>40</v>
       </c>
@@ -1231,593 +1228,556 @@
         <v>53</v>
       </c>
     </row>
-    <row r="44" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B44" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="C44" s="4"/>
-      <c r="D44" s="4"/>
-      <c r="E44" s="4"/>
-    </row>
-    <row r="45" spans="2:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B45" s="8" t="s">
+    <row r="38" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="D38" t="s">
+        <v>40</v>
+      </c>
+      <c r="F38">
+        <v>2030</v>
+      </c>
+      <c r="H38" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="I38" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="39" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="D39" t="s">
+        <v>42</v>
+      </c>
+      <c r="F39">
+        <v>40</v>
+      </c>
+      <c r="H39" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="I39" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="40" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="D40" t="s">
+        <v>40</v>
+      </c>
+      <c r="F40">
+        <v>2030</v>
+      </c>
+      <c r="G40" t="s">
+        <v>47</v>
+      </c>
+      <c r="H40" s="3" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="46" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B46" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="C46" s="4"/>
+      <c r="D46" s="4"/>
+      <c r="E46" s="4"/>
+    </row>
+    <row r="47" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B47" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="C45" s="8" t="s">
+      <c r="C47" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="D45" s="8" t="s">
+      <c r="D47" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="E45" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="F45" s="10" t="s">
-        <v>68</v>
-      </c>
-      <c r="G45" s="12" t="s">
+      <c r="E47" s="10">
+        <v>2023</v>
+      </c>
+      <c r="F47" s="10">
+        <v>2030</v>
+      </c>
+      <c r="G47" s="10">
+        <v>2040</v>
+      </c>
+      <c r="H47" s="10">
+        <v>2050</v>
+      </c>
+      <c r="I47" s="12" t="s">
         <v>69</v>
       </c>
-      <c r="H45" s="9" t="s">
+    </row>
+    <row r="48" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="D48" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="E48" s="2">
+        <v>2700</v>
+      </c>
+      <c r="F48" s="2">
+        <v>2700</v>
+      </c>
+      <c r="G48" s="2">
+        <v>2700</v>
+      </c>
+      <c r="H48" s="2">
+        <v>2700</v>
+      </c>
+      <c r="I48" t="str">
+        <f>M48</f>
+        <v>EN[_]Hydro*</v>
+      </c>
+      <c r="L48" t="s">
+        <v>24</v>
+      </c>
+      <c r="M48" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="49" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="D49" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="E49" s="2">
+        <v>560</v>
+      </c>
+      <c r="F49" s="2">
+        <v>380</v>
+      </c>
+      <c r="G49">
+        <v>320</v>
+      </c>
+      <c r="H49" s="2">
+        <v>290</v>
+      </c>
+      <c r="I49" t="str">
+        <f t="shared" ref="I49:I51" si="0">M49</f>
+        <v>E[_]SPV*</v>
+      </c>
+      <c r="L49" t="s">
+        <v>25</v>
+      </c>
+      <c r="M49" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="50" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="D50" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="E50" s="2">
+        <v>2780</v>
+      </c>
+      <c r="F50" s="2">
+        <v>2390</v>
+      </c>
+      <c r="G50" s="2">
+        <v>2140</v>
+      </c>
+      <c r="H50" s="2">
+        <v>1990</v>
+      </c>
+      <c r="I50" t="str">
+        <f t="shared" si="0"/>
+        <v>E[_]WOF*</v>
+      </c>
+      <c r="L50" t="s">
+        <v>26</v>
+      </c>
+      <c r="M50" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="51" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="D51" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="E51" s="2">
+        <v>1180</v>
+      </c>
+      <c r="F51" s="2">
+        <v>1150</v>
+      </c>
+      <c r="G51" s="2">
+        <v>1110</v>
+      </c>
+      <c r="H51" s="2">
+        <v>1090</v>
+      </c>
+      <c r="I51" t="str">
+        <f t="shared" si="0"/>
+        <v>E[_]WON*</v>
+      </c>
+      <c r="L51" t="s">
+        <v>27</v>
+      </c>
+      <c r="M51" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="52" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="D52" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E52" s="2">
         <v>70</v>
       </c>
-      <c r="I45" s="9" t="s">
-        <v>58</v>
-      </c>
-      <c r="J45" s="9" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="46" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="D46" t="s">
-        <v>40</v>
-      </c>
-      <c r="F46">
-        <v>2030</v>
-      </c>
-      <c r="H46" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="J46" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="47" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="D47" t="s">
-        <v>42</v>
-      </c>
-      <c r="F47">
-        <v>40</v>
-      </c>
-      <c r="H47" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="J47" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="48" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="D48" t="s">
-        <v>40</v>
-      </c>
-      <c r="F48">
-        <v>2030</v>
-      </c>
-      <c r="H48" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="I48" t="s">
-        <v>47</v>
+      <c r="F52" s="2">
+        <v>65</v>
+      </c>
+      <c r="G52" s="2">
+        <v>65</v>
+      </c>
+      <c r="H52" s="2">
+        <v>65</v>
+      </c>
+      <c r="I52" t="str">
+        <f>I48</f>
+        <v>EN[_]Hydro*</v>
+      </c>
+      <c r="L52" t="str">
+        <f>L48</f>
+        <v>Hydropower - large-scale unit</v>
+      </c>
+      <c r="M52" t="str">
+        <f t="shared" ref="M52:M59" si="1">M48</f>
+        <v>EN[_]Hydro*</v>
+      </c>
+    </row>
+    <row r="53" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="D53" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E53" s="2">
+        <v>11.5</v>
+      </c>
+      <c r="F53" s="2">
+        <v>9.5</v>
+      </c>
+      <c r="G53" s="2">
+        <v>8.1</v>
+      </c>
+      <c r="H53" s="2">
+        <v>7.4</v>
+      </c>
+      <c r="I53" t="str">
+        <f t="shared" ref="I53:I59" si="2">I49</f>
+        <v>E[_]SPV*</v>
+      </c>
+      <c r="L53" t="str">
+        <f t="shared" ref="L53" si="3">L49</f>
+        <v>Solar photovoltaics - Large scale unit</v>
+      </c>
+      <c r="M53" t="str">
+        <f t="shared" si="1"/>
+        <v>E[_]SPV*</v>
+      </c>
+    </row>
+    <row r="54" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="D54" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E54" s="2">
+        <v>44</v>
+      </c>
+      <c r="F54" s="2">
+        <v>34</v>
+      </c>
+      <c r="G54" s="2">
+        <v>30</v>
+      </c>
+      <c r="H54" s="2">
+        <v>28</v>
+      </c>
+      <c r="I54" t="str">
+        <f t="shared" si="2"/>
+        <v>E[_]WOF*</v>
+      </c>
+      <c r="L54" t="str">
+        <f t="shared" ref="L54" si="4">L50</f>
+        <v>Wind offshore</v>
+      </c>
+      <c r="M54" t="str">
+        <f t="shared" si="1"/>
+        <v>E[_]WOF*</v>
       </c>
     </row>
     <row r="55" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B55" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="C55" s="4"/>
-      <c r="D55" s="4"/>
-      <c r="E55" s="4"/>
-    </row>
-    <row r="56" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B56" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="C56" s="8" t="s">
-        <v>2</v>
-      </c>
-      <c r="D56" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="E56" s="10">
-        <v>2023</v>
-      </c>
-      <c r="F56" s="10">
-        <v>2030</v>
-      </c>
-      <c r="G56" s="10">
-        <v>2040</v>
-      </c>
-      <c r="H56" s="10">
-        <v>2050</v>
-      </c>
-      <c r="I56" s="12" t="s">
-        <v>69</v>
+      <c r="D55" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E55" s="2">
+        <v>17.387</v>
+      </c>
+      <c r="F55" s="2">
+        <v>16.663</v>
+      </c>
+      <c r="G55" s="2">
+        <v>15.965</v>
+      </c>
+      <c r="H55" s="2">
+        <v>15.602</v>
+      </c>
+      <c r="I55" t="str">
+        <f t="shared" si="2"/>
+        <v>E[_]WON*</v>
+      </c>
+      <c r="L55" t="str">
+        <f t="shared" ref="L55" si="5">L51</f>
+        <v>Wind onshore</v>
+      </c>
+      <c r="M55" t="str">
+        <f t="shared" si="1"/>
+        <v>E[_]WON*</v>
+      </c>
+    </row>
+    <row r="56" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="D56" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E56" s="2">
+        <v>4</v>
+      </c>
+      <c r="F56" s="2">
+        <v>4</v>
+      </c>
+      <c r="G56" s="2">
+        <v>4</v>
+      </c>
+      <c r="H56" s="2">
+        <v>4</v>
+      </c>
+      <c r="I56" t="str">
+        <f t="shared" si="2"/>
+        <v>EN[_]Hydro*</v>
+      </c>
+      <c r="L56" t="str">
+        <f t="shared" ref="L56" si="6">L52</f>
+        <v>Hydropower - large-scale unit</v>
+      </c>
+      <c r="M56" t="str">
+        <f t="shared" si="1"/>
+        <v>EN[_]Hydro*</v>
       </c>
     </row>
     <row r="57" spans="2:13" x14ac:dyDescent="0.25">
       <c r="D57" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E57" s="2">
-        <v>2700</v>
+        <v>0.5</v>
       </c>
       <c r="F57" s="2">
-        <v>2700</v>
+        <v>0.5</v>
       </c>
       <c r="G57" s="2">
-        <v>2700</v>
+        <v>0.5</v>
       </c>
       <c r="H57" s="2">
-        <v>2700</v>
+        <v>0.5</v>
       </c>
       <c r="I57" t="str">
-        <f>M57</f>
-        <v>EN[_]Hydro*</v>
-      </c>
-      <c r="L57" t="s">
-        <v>24</v>
-      </c>
-      <c r="M57" t="s">
-        <v>17</v>
+        <f t="shared" si="2"/>
+        <v>E[_]SPV*</v>
+      </c>
+      <c r="L57" t="str">
+        <f t="shared" ref="L57" si="7">L53</f>
+        <v>Solar photovoltaics - Large scale unit</v>
+      </c>
+      <c r="M57" t="str">
+        <f t="shared" si="1"/>
+        <v>E[_]SPV*</v>
       </c>
     </row>
     <row r="58" spans="2:13" x14ac:dyDescent="0.25">
       <c r="D58" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E58" s="2">
-        <v>560</v>
+        <v>5</v>
       </c>
       <c r="F58" s="2">
-        <v>380</v>
-      </c>
-      <c r="G58">
-        <v>320</v>
+        <v>3.5</v>
+      </c>
+      <c r="G58" s="2">
+        <v>3.5</v>
       </c>
       <c r="H58" s="2">
-        <v>290</v>
+        <v>3.5</v>
       </c>
       <c r="I58" t="str">
-        <f t="shared" ref="I58:I60" si="0">M58</f>
-        <v>E[_]SPV*</v>
-      </c>
-      <c r="L58" t="s">
-        <v>25</v>
-      </c>
-      <c r="M58" t="s">
-        <v>33</v>
+        <f t="shared" si="2"/>
+        <v>E[_]WOF*</v>
+      </c>
+      <c r="L58" t="str">
+        <f t="shared" ref="L58" si="8">L54</f>
+        <v>Wind offshore</v>
+      </c>
+      <c r="M58" t="str">
+        <f t="shared" si="1"/>
+        <v>E[_]WOF*</v>
       </c>
     </row>
     <row r="59" spans="2:13" x14ac:dyDescent="0.25">
       <c r="D59" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E59" s="2">
-        <v>2780</v>
+        <v>1.5</v>
       </c>
       <c r="F59" s="2">
-        <v>2390</v>
+        <v>1.5</v>
       </c>
       <c r="G59" s="2">
-        <v>2140</v>
+        <v>1.5</v>
       </c>
       <c r="H59" s="2">
-        <v>1990</v>
+        <v>1.5</v>
       </c>
       <c r="I59" t="str">
-        <f t="shared" si="0"/>
-        <v>E[_]WOF*</v>
-      </c>
-      <c r="L59" t="s">
-        <v>26</v>
-      </c>
-      <c r="M59" t="s">
-        <v>31</v>
+        <f t="shared" si="2"/>
+        <v>E[_]WON*</v>
+      </c>
+      <c r="L59" t="str">
+        <f t="shared" ref="L59" si="9">L55</f>
+        <v>Wind onshore</v>
+      </c>
+      <c r="M59" t="str">
+        <f t="shared" si="1"/>
+        <v>E[_]WON*</v>
       </c>
     </row>
     <row r="60" spans="2:13" x14ac:dyDescent="0.25">
       <c r="D60" s="2" t="s">
-        <v>21</v>
+        <v>48</v>
       </c>
       <c r="E60" s="2">
-        <v>1180</v>
+        <v>0</v>
       </c>
       <c r="F60" s="2">
-        <v>1150</v>
+        <v>0</v>
       </c>
       <c r="G60" s="2">
-        <v>1110</v>
+        <v>0</v>
       </c>
       <c r="H60" s="2">
-        <v>1090</v>
-      </c>
-      <c r="I60" t="str">
-        <f t="shared" si="0"/>
-        <v>E[_]WON*</v>
-      </c>
-      <c r="L60" t="s">
-        <v>27</v>
-      </c>
-      <c r="M60" t="s">
-        <v>32</v>
+        <v>0</v>
+      </c>
+      <c r="I60" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="61" spans="2:13" x14ac:dyDescent="0.25">
       <c r="D61" s="2" t="s">
-        <v>22</v>
+        <v>48</v>
       </c>
       <c r="E61" s="2">
-        <v>70</v>
+        <v>4.41</v>
       </c>
       <c r="F61" s="2">
-        <v>65</v>
+        <v>3.45</v>
       </c>
       <c r="G61" s="2">
-        <v>65</v>
+        <v>3.16</v>
       </c>
       <c r="H61" s="2">
-        <v>65</v>
-      </c>
-      <c r="I61" t="str">
-        <f>I57</f>
-        <v>EN[_]Hydro*</v>
-      </c>
-      <c r="L61" t="str">
-        <f>L57</f>
-        <v>Hydropower - large-scale unit</v>
-      </c>
-      <c r="M61" t="str">
-        <f t="shared" ref="M61:M68" si="1">M57</f>
-        <v>EN[_]Hydro*</v>
+        <v>2.99</v>
+      </c>
+      <c r="I61" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="62" spans="2:13" x14ac:dyDescent="0.25">
       <c r="D62" s="2" t="s">
-        <v>22</v>
+        <v>48</v>
       </c>
       <c r="E62" s="2">
-        <v>11.5</v>
+        <v>2.06</v>
       </c>
       <c r="F62" s="2">
-        <v>9.5</v>
+        <v>1.98</v>
       </c>
       <c r="G62" s="2">
-        <v>8.1</v>
+        <v>1.89</v>
       </c>
       <c r="H62" s="2">
-        <v>7.4</v>
-      </c>
-      <c r="I62" t="str">
-        <f t="shared" ref="I62:I68" si="2">I58</f>
-        <v>E[_]SPV*</v>
-      </c>
-      <c r="L62" t="str">
-        <f t="shared" ref="L62" si="3">L58</f>
-        <v>Solar photovoltaics - Large scale unit</v>
-      </c>
-      <c r="M62" t="str">
-        <f t="shared" si="1"/>
-        <v>E[_]SPV*</v>
-      </c>
-    </row>
-    <row r="63" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="D63" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="E63" s="2">
+        <v>1.85</v>
+      </c>
+      <c r="I62" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="64" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B64" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C64" s="4"/>
+      <c r="D64" s="4"/>
+      <c r="E64" s="4"/>
+    </row>
+    <row r="65" spans="2:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B65" s="12" t="s">
+        <v>69</v>
+      </c>
+      <c r="C65" s="12" t="s">
+        <v>71</v>
+      </c>
+      <c r="D65" s="12" t="s">
+        <v>72</v>
+      </c>
+      <c r="E65" s="8"/>
+      <c r="F65" s="10"/>
+      <c r="J65" s="13"/>
+    </row>
+    <row r="66" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B66" t="s">
+        <v>13</v>
+      </c>
+      <c r="C66" t="s">
+        <v>37</v>
+      </c>
+      <c r="D66" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="67" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B67" t="s">
+        <v>14</v>
+      </c>
+      <c r="C67" t="s">
+        <v>46</v>
+      </c>
+      <c r="D67" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="68" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B68" t="s">
+        <v>33</v>
+      </c>
+      <c r="C68" t="s">
+        <v>39</v>
+      </c>
+      <c r="D68" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="69" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B69" t="s">
+        <v>31</v>
+      </c>
+      <c r="C69" t="s">
         <v>44</v>
       </c>
-      <c r="F63" s="2">
-        <v>34</v>
-      </c>
-      <c r="G63" s="2">
-        <v>30</v>
-      </c>
-      <c r="H63" s="2">
-        <v>28</v>
-      </c>
-      <c r="I63" t="str">
-        <f t="shared" si="2"/>
-        <v>E[_]WOF*</v>
-      </c>
-      <c r="L63" t="str">
-        <f t="shared" ref="L63" si="4">L59</f>
-        <v>Wind offshore</v>
-      </c>
-      <c r="M63" t="str">
-        <f t="shared" si="1"/>
-        <v>E[_]WOF*</v>
-      </c>
-    </row>
-    <row r="64" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="D64" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="E64" s="2">
-        <v>17.387</v>
-      </c>
-      <c r="F64" s="2">
-        <v>16.663</v>
-      </c>
-      <c r="G64" s="2">
-        <v>15.965</v>
-      </c>
-      <c r="H64" s="2">
-        <v>15.602</v>
-      </c>
-      <c r="I64" t="str">
-        <f t="shared" si="2"/>
-        <v>E[_]WON*</v>
-      </c>
-      <c r="L64" t="str">
-        <f t="shared" ref="L64" si="5">L60</f>
-        <v>Wind onshore</v>
-      </c>
-      <c r="M64" t="str">
-        <f t="shared" si="1"/>
-        <v>E[_]WON*</v>
-      </c>
-    </row>
-    <row r="65" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="D65" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="E65" s="2">
-        <v>4</v>
-      </c>
-      <c r="F65" s="2">
-        <v>4</v>
-      </c>
-      <c r="G65" s="2">
-        <v>4</v>
-      </c>
-      <c r="H65" s="2">
-        <v>4</v>
-      </c>
-      <c r="I65" t="str">
-        <f t="shared" si="2"/>
-        <v>EN[_]Hydro*</v>
-      </c>
-      <c r="L65" t="str">
-        <f t="shared" ref="L65" si="6">L61</f>
-        <v>Hydropower - large-scale unit</v>
-      </c>
-      <c r="M65" t="str">
-        <f t="shared" si="1"/>
-        <v>EN[_]Hydro*</v>
-      </c>
-    </row>
-    <row r="66" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="D66" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="E66" s="2">
-        <v>0.5</v>
-      </c>
-      <c r="F66" s="2">
-        <v>0.5</v>
-      </c>
-      <c r="G66" s="2">
-        <v>0.5</v>
-      </c>
-      <c r="H66" s="2">
-        <v>0.5</v>
-      </c>
-      <c r="I66" t="str">
-        <f t="shared" si="2"/>
-        <v>E[_]SPV*</v>
-      </c>
-      <c r="L66" t="str">
-        <f t="shared" ref="L66" si="7">L62</f>
-        <v>Solar photovoltaics - Large scale unit</v>
-      </c>
-      <c r="M66" t="str">
-        <f t="shared" si="1"/>
-        <v>E[_]SPV*</v>
-      </c>
-    </row>
-    <row r="67" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="D67" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="E67" s="2">
-        <v>5</v>
-      </c>
-      <c r="F67" s="2">
-        <v>3.5</v>
-      </c>
-      <c r="G67" s="2">
-        <v>3.5</v>
-      </c>
-      <c r="H67" s="2">
-        <v>3.5</v>
-      </c>
-      <c r="I67" t="str">
-        <f t="shared" si="2"/>
-        <v>E[_]WOF*</v>
-      </c>
-      <c r="L67" t="str">
-        <f t="shared" ref="L67" si="8">L63</f>
-        <v>Wind offshore</v>
-      </c>
-      <c r="M67" t="str">
-        <f t="shared" si="1"/>
-        <v>E[_]WOF*</v>
-      </c>
-    </row>
-    <row r="68" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="D68" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="E68" s="2">
-        <v>1.5</v>
-      </c>
-      <c r="F68" s="2">
-        <v>1.5</v>
-      </c>
-      <c r="G68" s="2">
-        <v>1.5</v>
-      </c>
-      <c r="H68" s="2">
-        <v>1.5</v>
-      </c>
-      <c r="I68" t="str">
-        <f t="shared" si="2"/>
-        <v>E[_]WON*</v>
-      </c>
-      <c r="L68" t="str">
-        <f t="shared" ref="L68" si="9">L64</f>
-        <v>Wind onshore</v>
-      </c>
-      <c r="M68" t="str">
-        <f t="shared" si="1"/>
-        <v>E[_]WON*</v>
-      </c>
-    </row>
-    <row r="69" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="D69" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="E69" s="2">
-        <v>0</v>
-      </c>
-      <c r="F69" s="2">
-        <v>0</v>
-      </c>
-      <c r="G69" s="2">
-        <v>0</v>
-      </c>
-      <c r="H69" s="2">
-        <v>0</v>
-      </c>
-      <c r="I69" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="70" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="D70" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="E70" s="2">
-        <v>4.41</v>
-      </c>
-      <c r="F70" s="2">
-        <v>3.45</v>
-      </c>
-      <c r="G70" s="2">
-        <v>3.16</v>
-      </c>
-      <c r="H70" s="2">
-        <v>2.99</v>
-      </c>
-      <c r="I70" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="71" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="D71" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="E71" s="2">
-        <v>2.06</v>
-      </c>
-      <c r="F71" s="2">
-        <v>1.98</v>
-      </c>
-      <c r="G71" s="2">
-        <v>1.89</v>
-      </c>
-      <c r="H71" s="2">
-        <v>1.85</v>
-      </c>
-      <c r="I71" t="s">
+      <c r="D69" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="70" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B70" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="73" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B73" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="C73" s="4"/>
-      <c r="D73" s="4"/>
-      <c r="E73" s="4"/>
-    </row>
-    <row r="74" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B74" s="12" t="s">
-        <v>69</v>
-      </c>
-      <c r="C74" s="12" t="s">
-        <v>71</v>
-      </c>
-      <c r="D74" s="12" t="s">
-        <v>72</v>
-      </c>
-      <c r="E74" s="8"/>
-      <c r="F74" s="10"/>
-      <c r="J74" s="13"/>
-    </row>
-    <row r="75" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B75" t="s">
-        <v>13</v>
-      </c>
-      <c r="C75" t="s">
-        <v>37</v>
-      </c>
-      <c r="D75" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="76" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B76" t="s">
-        <v>14</v>
-      </c>
-      <c r="C76" t="s">
-        <v>46</v>
-      </c>
-      <c r="D76" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="77" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B77" t="s">
-        <v>33</v>
-      </c>
-      <c r="C77" t="s">
-        <v>39</v>
-      </c>
-      <c r="D77" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="78" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B78" t="s">
-        <v>31</v>
-      </c>
-      <c r="C78" t="s">
-        <v>44</v>
-      </c>
-      <c r="D78" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="79" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B79" t="s">
-        <v>32</v>
-      </c>
-      <c r="C79" t="s">
+      <c r="C70" t="s">
         <v>45</v>
       </c>
-      <c r="D79" t="s">
+      <c r="D70" t="s">
         <v>20</v>
       </c>
     </row>

--- a/VerveStacks_EST/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
+++ b/VerveStacks_EST/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\PycharmProjects\ee-times\VerveStacks_EST\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E12E6D9B-8156-43B2-BBF1-F8710A46B0C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04A43350-D461-41B5-8F5E-D185526C1F16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -428,7 +428,7 @@
     <xf numFmtId="9" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -447,6 +447,7 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="14">
     <cellStyle name="Comma 2" xfId="2" xr:uid="{9640D755-0D23-4E24-A066-51A16F3F8D30}"/>
@@ -1722,8 +1723,8 @@
       <c r="D65" s="12" t="s">
         <v>72</v>
       </c>
-      <c r="E65" s="8"/>
-      <c r="F65" s="10"/>
+      <c r="E65" s="14"/>
+      <c r="F65" s="14"/>
       <c r="J65" s="13"/>
     </row>
     <row r="66" spans="2:10" x14ac:dyDescent="0.25">

--- a/VerveStacks_EST/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
+++ b/VerveStacks_EST/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr updateLinks="never"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\PycharmProjects\ee-times\VerveStacks_EST\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04A43350-D461-41B5-8F5E-D185526C1F16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D992C96-FDE9-4B7A-B27A-C618BD6D1AA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="40" windowWidth="19200" windowHeight="11240" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="AVA" sheetId="6" r:id="rId1"/>
@@ -447,7 +447,7 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="14">
     <cellStyle name="Comma 2" xfId="2" xr:uid="{9640D755-0D23-4E24-A066-51A16F3F8D30}"/>
@@ -762,20 +762,20 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{268E9BAB-B98F-4B82-9042-51EABC9ED525}">
   <dimension ref="B3:C5"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="18.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.453125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="27.5703125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="49.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="27.54296875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="49.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B3" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="4" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B4" t="s">
         <v>19</v>
       </c>
@@ -783,7 +783,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="5" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B5" t="s">
         <v>35</v>
       </c>
@@ -799,28 +799,28 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="B2:V70"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="14.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.5703125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.1796875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.54296875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.7265625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="11" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="41.28515625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="18.85546875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.42578125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="31.140625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="8.85546875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="10.7109375" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="6.28515625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="4.28515625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="41.26953125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="18.81640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.453125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="31.1796875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="10.7265625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="6.26953125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="4.26953125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="11.7265625" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="16" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="28.42578125" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="11.42578125" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="31.42578125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="28.453125" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="11.453125" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="31.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:22" x14ac:dyDescent="0.35">
       <c r="B2" s="7" t="s">
         <v>3</v>
       </c>
@@ -839,7 +839,7 @@
       <c r="O2" s="5"/>
       <c r="P2" s="5"/>
     </row>
-    <row r="3" spans="2:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:22" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B3" s="8" t="s">
         <v>54</v>
       </c>
@@ -886,12 +886,12 @@
         <v>64</v>
       </c>
     </row>
-    <row r="4" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="J4" s="11" t="s">
+    <row r="4" spans="2:22" x14ac:dyDescent="0.35">
+      <c r="D4" s="11" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="5" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:22" x14ac:dyDescent="0.35">
       <c r="C5" t="s">
         <v>10</v>
       </c>
@@ -908,7 +908,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="6" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:22" x14ac:dyDescent="0.35">
       <c r="D6" t="s">
         <v>5</v>
       </c>
@@ -919,7 +919,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="7" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:22" x14ac:dyDescent="0.35">
       <c r="D7" t="s">
         <v>12</v>
       </c>
@@ -930,7 +930,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="8" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:22" x14ac:dyDescent="0.35">
       <c r="D8" t="s">
         <v>12</v>
       </c>
@@ -941,7 +941,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="9" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:22" x14ac:dyDescent="0.35">
       <c r="D9" t="s">
         <v>6</v>
       </c>
@@ -952,7 +952,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="10" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:22" x14ac:dyDescent="0.35">
       <c r="D10" t="s">
         <v>7</v>
       </c>
@@ -963,7 +963,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="11" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:22" x14ac:dyDescent="0.35">
       <c r="D11" t="s">
         <v>8</v>
       </c>
@@ -974,7 +974,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="12" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:22" x14ac:dyDescent="0.35">
       <c r="D12" t="s">
         <v>9</v>
       </c>
@@ -989,12 +989,12 @@
       <c r="T12" s="2"/>
       <c r="V12" s="2"/>
     </row>
-    <row r="13" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="J13" s="11" t="s">
+    <row r="13" spans="2:22" x14ac:dyDescent="0.35">
+      <c r="D13" s="11" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="14" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:22" x14ac:dyDescent="0.35">
       <c r="D14" t="s">
         <v>5</v>
       </c>
@@ -1005,7 +1005,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="15" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:22" x14ac:dyDescent="0.35">
       <c r="D15" t="s">
         <v>6</v>
       </c>
@@ -1016,7 +1016,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="16" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:22" x14ac:dyDescent="0.35">
       <c r="D16" t="s">
         <v>7</v>
       </c>
@@ -1027,7 +1027,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="17" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:18" x14ac:dyDescent="0.35">
       <c r="D17" t="s">
         <v>8</v>
       </c>
@@ -1038,7 +1038,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="18" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:18" x14ac:dyDescent="0.35">
       <c r="D18" t="s">
         <v>9</v>
       </c>
@@ -1049,7 +1049,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="19" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:18" x14ac:dyDescent="0.35">
       <c r="D19" t="s">
         <v>5</v>
       </c>
@@ -1060,12 +1060,12 @@
         <v>38</v>
       </c>
     </row>
-    <row r="20" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="J20" s="11" t="s">
+    <row r="20" spans="2:18" x14ac:dyDescent="0.35">
+      <c r="D20" s="11" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="21" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:18" x14ac:dyDescent="0.35">
       <c r="D21" t="s">
         <v>5</v>
       </c>
@@ -1076,7 +1076,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="22" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:18" x14ac:dyDescent="0.35">
       <c r="D22" t="s">
         <v>7</v>
       </c>
@@ -1087,7 +1087,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="23" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:18" x14ac:dyDescent="0.35">
       <c r="D23" t="s">
         <v>16</v>
       </c>
@@ -1098,7 +1098,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="24" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:18" x14ac:dyDescent="0.35">
       <c r="D24" t="s">
         <v>6</v>
       </c>
@@ -1109,7 +1109,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="25" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:18" x14ac:dyDescent="0.35">
       <c r="D25" t="s">
         <v>9</v>
       </c>
@@ -1120,7 +1120,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="26" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:18" x14ac:dyDescent="0.35">
       <c r="D26" t="s">
         <v>8</v>
       </c>
@@ -1131,7 +1131,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="27" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:18" x14ac:dyDescent="0.35">
       <c r="D27" t="s">
         <v>11</v>
       </c>
@@ -1145,13 +1145,13 @@
         <v>15</v>
       </c>
     </row>
-    <row r="28" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:18" x14ac:dyDescent="0.35">
       <c r="R28" s="2"/>
     </row>
-    <row r="29" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:18" x14ac:dyDescent="0.35">
       <c r="R29" s="2"/>
     </row>
-    <row r="32" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:18" x14ac:dyDescent="0.35">
       <c r="B32" s="7" t="s">
         <v>3</v>
       </c>
@@ -1159,7 +1159,7 @@
       <c r="D32" s="4"/>
       <c r="E32" s="4"/>
     </row>
-    <row r="33" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="2:13" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B33" s="8" t="s">
         <v>54</v>
       </c>
@@ -1185,7 +1185,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="34" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:13" x14ac:dyDescent="0.35">
       <c r="D34" t="s">
         <v>40</v>
       </c>
@@ -1196,7 +1196,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="35" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:13" x14ac:dyDescent="0.35">
       <c r="D35" t="s">
         <v>40</v>
       </c>
@@ -1207,7 +1207,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="36" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="36" spans="2:13" x14ac:dyDescent="0.35">
       <c r="D36" t="s">
         <v>40</v>
       </c>
@@ -1218,7 +1218,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="37" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="37" spans="2:13" x14ac:dyDescent="0.35">
       <c r="D37" t="s">
         <v>40</v>
       </c>
@@ -1229,7 +1229,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="38" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="38" spans="2:13" x14ac:dyDescent="0.35">
       <c r="D38" t="s">
         <v>40</v>
       </c>
@@ -1243,7 +1243,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="39" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="39" spans="2:13" x14ac:dyDescent="0.35">
       <c r="D39" t="s">
         <v>42</v>
       </c>
@@ -1257,7 +1257,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="40" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="40" spans="2:13" x14ac:dyDescent="0.35">
       <c r="D40" t="s">
         <v>40</v>
       </c>
@@ -1271,7 +1271,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="46" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="46" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B46" s="7" t="s">
         <v>28</v>
       </c>
@@ -1279,7 +1279,7 @@
       <c r="D46" s="4"/>
       <c r="E46" s="4"/>
     </row>
-    <row r="47" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="2:13" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B47" s="8" t="s">
         <v>54</v>
       </c>
@@ -1305,7 +1305,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="48" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="48" spans="2:13" x14ac:dyDescent="0.35">
       <c r="D48" s="2" t="s">
         <v>21</v>
       </c>
@@ -1332,7 +1332,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="49" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="49" spans="2:13" x14ac:dyDescent="0.35">
       <c r="D49" s="2" t="s">
         <v>21</v>
       </c>
@@ -1359,7 +1359,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="50" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="50" spans="2:13" x14ac:dyDescent="0.35">
       <c r="D50" s="2" t="s">
         <v>21</v>
       </c>
@@ -1386,7 +1386,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="51" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="51" spans="2:13" x14ac:dyDescent="0.35">
       <c r="D51" s="2" t="s">
         <v>21</v>
       </c>
@@ -1413,7 +1413,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="52" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="52" spans="2:13" x14ac:dyDescent="0.35">
       <c r="D52" s="2" t="s">
         <v>22</v>
       </c>
@@ -1442,7 +1442,7 @@
         <v>EN[_]Hydro*</v>
       </c>
     </row>
-    <row r="53" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="53" spans="2:13" x14ac:dyDescent="0.35">
       <c r="D53" s="2" t="s">
         <v>22</v>
       </c>
@@ -1471,7 +1471,7 @@
         <v>E[_]SPV*</v>
       </c>
     </row>
-    <row r="54" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="54" spans="2:13" x14ac:dyDescent="0.35">
       <c r="D54" s="2" t="s">
         <v>22</v>
       </c>
@@ -1500,7 +1500,7 @@
         <v>E[_]WOF*</v>
       </c>
     </row>
-    <row r="55" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="55" spans="2:13" x14ac:dyDescent="0.35">
       <c r="D55" s="2" t="s">
         <v>22</v>
       </c>
@@ -1529,7 +1529,7 @@
         <v>E[_]WON*</v>
       </c>
     </row>
-    <row r="56" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="56" spans="2:13" x14ac:dyDescent="0.35">
       <c r="D56" s="2" t="s">
         <v>23</v>
       </c>
@@ -1558,7 +1558,7 @@
         <v>EN[_]Hydro*</v>
       </c>
     </row>
-    <row r="57" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="57" spans="2:13" x14ac:dyDescent="0.35">
       <c r="D57" s="2" t="s">
         <v>23</v>
       </c>
@@ -1587,7 +1587,7 @@
         <v>E[_]SPV*</v>
       </c>
     </row>
-    <row r="58" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="58" spans="2:13" x14ac:dyDescent="0.35">
       <c r="D58" s="2" t="s">
         <v>23</v>
       </c>
@@ -1616,7 +1616,7 @@
         <v>E[_]WOF*</v>
       </c>
     </row>
-    <row r="59" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="59" spans="2:13" x14ac:dyDescent="0.35">
       <c r="D59" s="2" t="s">
         <v>23</v>
       </c>
@@ -1645,7 +1645,7 @@
         <v>E[_]WON*</v>
       </c>
     </row>
-    <row r="60" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="60" spans="2:13" x14ac:dyDescent="0.35">
       <c r="D60" s="2" t="s">
         <v>48</v>
       </c>
@@ -1665,7 +1665,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="61" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="61" spans="2:13" x14ac:dyDescent="0.35">
       <c r="D61" s="2" t="s">
         <v>48</v>
       </c>
@@ -1685,7 +1685,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="62" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="62" spans="2:13" x14ac:dyDescent="0.35">
       <c r="D62" s="2" t="s">
         <v>48</v>
       </c>
@@ -1705,7 +1705,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="64" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="64" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B64" s="7" t="s">
         <v>18</v>
       </c>
@@ -1713,7 +1713,7 @@
       <c r="D64" s="4"/>
       <c r="E64" s="4"/>
     </row>
-    <row r="65" spans="2:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B65" s="12" t="s">
         <v>69</v>
       </c>
@@ -1727,7 +1727,7 @@
       <c r="F65" s="14"/>
       <c r="J65" s="13"/>
     </row>
-    <row r="66" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="66" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B66" t="s">
         <v>13</v>
       </c>
@@ -1738,7 +1738,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="67" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="67" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B67" t="s">
         <v>14</v>
       </c>
@@ -1749,7 +1749,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="68" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="68" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B68" t="s">
         <v>33</v>
       </c>
@@ -1760,7 +1760,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="69" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="69" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B69" t="s">
         <v>31</v>
       </c>
@@ -1771,7 +1771,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="70" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="70" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B70" t="s">
         <v>32</v>
       </c>

--- a/VerveStacks_EST/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
+++ b/VerveStacks_EST/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\PycharmProjects\ee-times\VerveStacks_EST\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D992C96-FDE9-4B7A-B27A-C618BD6D1AA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B24621C-47C9-4BB7-9FBD-A9B12784A57F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="40" windowWidth="19200" windowHeight="11240" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -44,7 +44,7 @@
     <author>tc={9326A9B6-D94C-4ED3-9FB8-434C0D4AC388}</author>
   </authors>
   <commentList>
-    <comment ref="I49" authorId="0" shapeId="0" xr:uid="{80A2C193-6148-4AA7-9B62-06322F60E0BF}">
+    <comment ref="I48" authorId="0" shapeId="0" xr:uid="{80A2C193-6148-4AA7-9B62-06322F60E0BF}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -52,7 +52,7 @@
     Utility-scale PV</t>
       </text>
     </comment>
-    <comment ref="I50" authorId="1" shapeId="0" xr:uid="{E6F93F18-BBEF-4E19-B2D0-A493D668847A}">
+    <comment ref="I49" authorId="1" shapeId="0" xr:uid="{E6F93F18-BBEF-4E19-B2D0-A493D668847A}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -60,7 +60,7 @@
     AC fixed</t>
       </text>
     </comment>
-    <comment ref="I61" authorId="2" shapeId="0" xr:uid="{9326A9B6-D94C-4ED3-9FB8-434C0D4AC388}">
+    <comment ref="I60" authorId="2" shapeId="0" xr:uid="{9326A9B6-D94C-4ED3-9FB8-434C0D4AC388}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -73,7 +73,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="72">
   <si>
     <t>Attribute</t>
   </si>
@@ -214,9 +214,6 @@
   </si>
   <si>
     <t>ELC_wo*</t>
-  </si>
-  <si>
-    <t>EN_STG8hbNREL,EN_STG4hbNREL</t>
   </si>
   <si>
     <t>act_cost</t>
@@ -747,13 +744,13 @@
 
 <file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
 <ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <threadedComment ref="I49" dT="2026-03-18T13:56:27.06" personId="{50AE587C-9924-43E9-9BB9-052BDB346AE2}" id="{80A2C193-6148-4AA7-9B62-06322F60E0BF}">
+  <threadedComment ref="I48" dT="2026-03-18T13:56:27.06" personId="{50AE587C-9924-43E9-9BB9-052BDB346AE2}" id="{80A2C193-6148-4AA7-9B62-06322F60E0BF}">
     <text>Utility-scale PV</text>
   </threadedComment>
-  <threadedComment ref="I50" dT="2026-03-18T13:39:46.05" personId="{50AE587C-9924-43E9-9BB9-052BDB346AE2}" id="{E6F93F18-BBEF-4E19-B2D0-A493D668847A}">
+  <threadedComment ref="I49" dT="2026-03-18T13:39:46.05" personId="{50AE587C-9924-43E9-9BB9-052BDB346AE2}" id="{E6F93F18-BBEF-4E19-B2D0-A493D668847A}">
     <text>AC fixed</text>
   </threadedComment>
-  <threadedComment ref="I61" dT="2026-03-18T13:39:46.05" personId="{50AE587C-9924-43E9-9BB9-052BDB346AE2}" id="{9326A9B6-D94C-4ED3-9FB8-434C0D4AC388}">
+  <threadedComment ref="I60" dT="2026-03-18T13:39:46.05" personId="{50AE587C-9924-43E9-9BB9-052BDB346AE2}" id="{9326A9B6-D94C-4ED3-9FB8-434C0D4AC388}">
     <text>AC fixed</text>
   </threadedComment>
 </ThreadedComments>
@@ -798,7 +795,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="B2:V70"/>
+  <dimension ref="B2:V69"/>
   <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="14.1796875" bestFit="1" customWidth="1"/>
@@ -806,7 +803,7 @@
     <col min="4" max="4" width="12.7265625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="11" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="41.26953125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="18.81640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="30.453125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="10.453125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="31.1796875" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="15" bestFit="1" customWidth="1"/>
@@ -841,7 +838,7 @@
     </row>
     <row r="3" spans="2:22" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B3" s="8" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C3" s="8" t="s">
         <v>2</v>
@@ -856,39 +853,39 @@
         <v>4</v>
       </c>
       <c r="G3" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="H3" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="H3" s="10" t="s">
+      <c r="I3" s="9" t="s">
         <v>56</v>
       </c>
-      <c r="I3" s="9" t="s">
+      <c r="J3" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="J3" s="9" t="s">
+      <c r="K3" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="K3" s="9" t="s">
+      <c r="L3" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="L3" s="9" t="s">
+      <c r="M3" s="9" t="s">
         <v>60</v>
       </c>
-      <c r="M3" s="9" t="s">
+      <c r="N3" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="N3" s="9" t="s">
+      <c r="O3" s="9" t="s">
         <v>62</v>
       </c>
-      <c r="O3" s="9" t="s">
+      <c r="P3" s="9" t="s">
         <v>63</v>
-      </c>
-      <c r="P3" s="9" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="4" spans="2:22" x14ac:dyDescent="0.35">
       <c r="D4" s="11" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="5" spans="2:22" x14ac:dyDescent="0.35">
@@ -991,7 +988,7 @@
     </row>
     <row r="13" spans="2:22" x14ac:dyDescent="0.35">
       <c r="D13" s="11" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="14" spans="2:22" x14ac:dyDescent="0.35">
@@ -1062,7 +1059,7 @@
     </row>
     <row r="20" spans="2:18" x14ac:dyDescent="0.35">
       <c r="D20" s="11" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="21" spans="2:18" x14ac:dyDescent="0.35">
@@ -1161,7 +1158,7 @@
     </row>
     <row r="33" spans="2:13" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B33" s="8" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C33" s="8" t="s">
         <v>2</v>
@@ -1173,16 +1170,16 @@
         <v>1</v>
       </c>
       <c r="F33" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="G33" s="12" t="s">
         <v>68</v>
       </c>
-      <c r="G33" s="12" t="s">
+      <c r="H33" s="9" t="s">
         <v>69</v>
       </c>
-      <c r="H33" s="9" t="s">
-        <v>70</v>
-      </c>
       <c r="I33" s="9" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="34" spans="2:13" x14ac:dyDescent="0.35">
@@ -1193,7 +1190,7 @@
         <v>2030</v>
       </c>
       <c r="G34" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="35" spans="2:13" x14ac:dyDescent="0.35">
@@ -1215,7 +1212,7 @@
         <v>2036</v>
       </c>
       <c r="G36" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="37" spans="2:13" x14ac:dyDescent="0.35">
@@ -1226,7 +1223,7 @@
         <v>2030</v>
       </c>
       <c r="G37" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="38" spans="2:13" x14ac:dyDescent="0.35">
@@ -1240,7 +1237,7 @@
         <v>41</v>
       </c>
       <c r="I38" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="39" spans="2:13" x14ac:dyDescent="0.35">
@@ -1254,55 +1251,68 @@
         <v>43</v>
       </c>
       <c r="I39" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="40" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="D40" t="s">
-        <v>40</v>
-      </c>
-      <c r="F40">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="45" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B45" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="C45" s="4"/>
+      <c r="D45" s="4"/>
+      <c r="E45" s="4"/>
+    </row>
+    <row r="46" spans="2:13" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B46" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="C46" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="D46" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="E46" s="10">
+        <v>2023</v>
+      </c>
+      <c r="F46" s="10">
         <v>2030</v>
       </c>
-      <c r="G40" t="s">
-        <v>47</v>
-      </c>
-      <c r="H40" s="3" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="46" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="B46" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="C46" s="4"/>
-      <c r="D46" s="4"/>
-      <c r="E46" s="4"/>
-    </row>
-    <row r="47" spans="2:13" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B47" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="C47" s="8" t="s">
-        <v>2</v>
-      </c>
-      <c r="D47" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="E47" s="10">
-        <v>2023</v>
-      </c>
-      <c r="F47" s="10">
-        <v>2030</v>
-      </c>
-      <c r="G47" s="10">
+      <c r="G46" s="10">
         <v>2040</v>
       </c>
-      <c r="H47" s="10">
+      <c r="H46" s="10">
         <v>2050</v>
       </c>
-      <c r="I47" s="12" t="s">
-        <v>69</v>
+      <c r="I46" s="12" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="47" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="D47" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="E47" s="2">
+        <v>2700</v>
+      </c>
+      <c r="F47" s="2">
+        <v>2700</v>
+      </c>
+      <c r="G47" s="2">
+        <v>2700</v>
+      </c>
+      <c r="H47" s="2">
+        <v>2700</v>
+      </c>
+      <c r="I47" t="str">
+        <f>M47</f>
+        <v>EN[_]Hydro*</v>
+      </c>
+      <c r="L47" t="s">
+        <v>24</v>
+      </c>
+      <c r="M47" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="48" spans="2:13" x14ac:dyDescent="0.35">
@@ -1310,26 +1320,26 @@
         <v>21</v>
       </c>
       <c r="E48" s="2">
-        <v>2700</v>
+        <v>560</v>
       </c>
       <c r="F48" s="2">
-        <v>2700</v>
-      </c>
-      <c r="G48" s="2">
-        <v>2700</v>
+        <v>380</v>
+      </c>
+      <c r="G48">
+        <v>320</v>
       </c>
       <c r="H48" s="2">
-        <v>2700</v>
+        <v>290</v>
       </c>
       <c r="I48" t="str">
-        <f>M48</f>
-        <v>EN[_]Hydro*</v>
+        <f t="shared" ref="I48:I50" si="0">M48</f>
+        <v>E[_]SPV*</v>
       </c>
       <c r="L48" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="M48" t="s">
-        <v>17</v>
+        <v>33</v>
       </c>
     </row>
     <row r="49" spans="2:13" x14ac:dyDescent="0.35">
@@ -1337,26 +1347,26 @@
         <v>21</v>
       </c>
       <c r="E49" s="2">
-        <v>560</v>
+        <v>2780</v>
       </c>
       <c r="F49" s="2">
-        <v>380</v>
-      </c>
-      <c r="G49">
-        <v>320</v>
+        <v>2390</v>
+      </c>
+      <c r="G49" s="2">
+        <v>2140</v>
       </c>
       <c r="H49" s="2">
-        <v>290</v>
+        <v>1990</v>
       </c>
       <c r="I49" t="str">
-        <f t="shared" ref="I49:I51" si="0">M49</f>
-        <v>E[_]SPV*</v>
+        <f t="shared" si="0"/>
+        <v>E[_]WOF*</v>
       </c>
       <c r="L49" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M49" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="50" spans="2:13" x14ac:dyDescent="0.35">
@@ -1364,53 +1374,55 @@
         <v>21</v>
       </c>
       <c r="E50" s="2">
-        <v>2780</v>
+        <v>1180</v>
       </c>
       <c r="F50" s="2">
-        <v>2390</v>
+        <v>1150</v>
       </c>
       <c r="G50" s="2">
-        <v>2140</v>
+        <v>1110</v>
       </c>
       <c r="H50" s="2">
-        <v>1990</v>
+        <v>1090</v>
       </c>
       <c r="I50" t="str">
         <f t="shared" si="0"/>
-        <v>E[_]WOF*</v>
+        <v>E[_]WON*</v>
       </c>
       <c r="L50" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="M50" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="51" spans="2:13" x14ac:dyDescent="0.35">
       <c r="D51" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E51" s="2">
-        <v>1180</v>
+        <v>70</v>
       </c>
       <c r="F51" s="2">
-        <v>1150</v>
+        <v>65</v>
       </c>
       <c r="G51" s="2">
-        <v>1110</v>
+        <v>65</v>
       </c>
       <c r="H51" s="2">
-        <v>1090</v>
+        <v>65</v>
       </c>
       <c r="I51" t="str">
-        <f t="shared" si="0"/>
-        <v>E[_]WON*</v>
-      </c>
-      <c r="L51" t="s">
-        <v>27</v>
-      </c>
-      <c r="M51" t="s">
-        <v>32</v>
+        <f>I47</f>
+        <v>EN[_]Hydro*</v>
+      </c>
+      <c r="L51" t="str">
+        <f>L47</f>
+        <v>Hydropower - large-scale unit</v>
+      </c>
+      <c r="M51" t="str">
+        <f t="shared" ref="M51:M58" si="1">M47</f>
+        <v>EN[_]Hydro*</v>
       </c>
     </row>
     <row r="52" spans="2:13" x14ac:dyDescent="0.35">
@@ -1418,28 +1430,28 @@
         <v>22</v>
       </c>
       <c r="E52" s="2">
-        <v>70</v>
+        <v>11.5</v>
       </c>
       <c r="F52" s="2">
-        <v>65</v>
+        <v>9.5</v>
       </c>
       <c r="G52" s="2">
-        <v>65</v>
+        <v>8.1</v>
       </c>
       <c r="H52" s="2">
-        <v>65</v>
+        <v>7.4</v>
       </c>
       <c r="I52" t="str">
-        <f>I48</f>
-        <v>EN[_]Hydro*</v>
+        <f t="shared" ref="I52:I58" si="2">I48</f>
+        <v>E[_]SPV*</v>
       </c>
       <c r="L52" t="str">
-        <f>L48</f>
-        <v>Hydropower - large-scale unit</v>
+        <f t="shared" ref="L52" si="3">L48</f>
+        <v>Solar photovoltaics - Large scale unit</v>
       </c>
       <c r="M52" t="str">
-        <f t="shared" ref="M52:M59" si="1">M48</f>
-        <v>EN[_]Hydro*</v>
+        <f t="shared" si="1"/>
+        <v>E[_]SPV*</v>
       </c>
     </row>
     <row r="53" spans="2:13" x14ac:dyDescent="0.35">
@@ -1447,28 +1459,28 @@
         <v>22</v>
       </c>
       <c r="E53" s="2">
-        <v>11.5</v>
+        <v>44</v>
       </c>
       <c r="F53" s="2">
-        <v>9.5</v>
+        <v>34</v>
       </c>
       <c r="G53" s="2">
-        <v>8.1</v>
+        <v>30</v>
       </c>
       <c r="H53" s="2">
-        <v>7.4</v>
+        <v>28</v>
       </c>
       <c r="I53" t="str">
-        <f t="shared" ref="I53:I59" si="2">I49</f>
-        <v>E[_]SPV*</v>
+        <f t="shared" si="2"/>
+        <v>E[_]WOF*</v>
       </c>
       <c r="L53" t="str">
-        <f t="shared" ref="L53" si="3">L49</f>
-        <v>Solar photovoltaics - Large scale unit</v>
+        <f t="shared" ref="L53" si="4">L49</f>
+        <v>Wind offshore</v>
       </c>
       <c r="M53" t="str">
         <f t="shared" si="1"/>
-        <v>E[_]SPV*</v>
+        <v>E[_]WOF*</v>
       </c>
     </row>
     <row r="54" spans="2:13" x14ac:dyDescent="0.35">
@@ -1476,57 +1488,57 @@
         <v>22</v>
       </c>
       <c r="E54" s="2">
-        <v>44</v>
+        <v>17.387</v>
       </c>
       <c r="F54" s="2">
-        <v>34</v>
+        <v>16.663</v>
       </c>
       <c r="G54" s="2">
-        <v>30</v>
+        <v>15.965</v>
       </c>
       <c r="H54" s="2">
-        <v>28</v>
+        <v>15.602</v>
       </c>
       <c r="I54" t="str">
         <f t="shared" si="2"/>
-        <v>E[_]WOF*</v>
+        <v>E[_]WON*</v>
       </c>
       <c r="L54" t="str">
-        <f t="shared" ref="L54" si="4">L50</f>
-        <v>Wind offshore</v>
+        <f t="shared" ref="L54" si="5">L50</f>
+        <v>Wind onshore</v>
       </c>
       <c r="M54" t="str">
         <f t="shared" si="1"/>
-        <v>E[_]WOF*</v>
+        <v>E[_]WON*</v>
       </c>
     </row>
     <row r="55" spans="2:13" x14ac:dyDescent="0.35">
       <c r="D55" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E55" s="2">
-        <v>17.387</v>
+        <v>4</v>
       </c>
       <c r="F55" s="2">
-        <v>16.663</v>
+        <v>4</v>
       </c>
       <c r="G55" s="2">
-        <v>15.965</v>
+        <v>4</v>
       </c>
       <c r="H55" s="2">
-        <v>15.602</v>
+        <v>4</v>
       </c>
       <c r="I55" t="str">
         <f t="shared" si="2"/>
-        <v>E[_]WON*</v>
+        <v>EN[_]Hydro*</v>
       </c>
       <c r="L55" t="str">
-        <f t="shared" ref="L55" si="5">L51</f>
-        <v>Wind onshore</v>
+        <f t="shared" ref="L55" si="6">L51</f>
+        <v>Hydropower - large-scale unit</v>
       </c>
       <c r="M55" t="str">
         <f t="shared" si="1"/>
-        <v>E[_]WON*</v>
+        <v>EN[_]Hydro*</v>
       </c>
     </row>
     <row r="56" spans="2:13" x14ac:dyDescent="0.35">
@@ -1534,28 +1546,28 @@
         <v>23</v>
       </c>
       <c r="E56" s="2">
-        <v>4</v>
+        <v>0.5</v>
       </c>
       <c r="F56" s="2">
-        <v>4</v>
+        <v>0.5</v>
       </c>
       <c r="G56" s="2">
-        <v>4</v>
+        <v>0.5</v>
       </c>
       <c r="H56" s="2">
-        <v>4</v>
+        <v>0.5</v>
       </c>
       <c r="I56" t="str">
         <f t="shared" si="2"/>
-        <v>EN[_]Hydro*</v>
+        <v>E[_]SPV*</v>
       </c>
       <c r="L56" t="str">
-        <f t="shared" ref="L56" si="6">L52</f>
-        <v>Hydropower - large-scale unit</v>
+        <f t="shared" ref="L56" si="7">L52</f>
+        <v>Solar photovoltaics - Large scale unit</v>
       </c>
       <c r="M56" t="str">
         <f t="shared" si="1"/>
-        <v>EN[_]Hydro*</v>
+        <v>E[_]SPV*</v>
       </c>
     </row>
     <row r="57" spans="2:13" x14ac:dyDescent="0.35">
@@ -1563,28 +1575,28 @@
         <v>23</v>
       </c>
       <c r="E57" s="2">
-        <v>0.5</v>
+        <v>5</v>
       </c>
       <c r="F57" s="2">
-        <v>0.5</v>
+        <v>3.5</v>
       </c>
       <c r="G57" s="2">
-        <v>0.5</v>
+        <v>3.5</v>
       </c>
       <c r="H57" s="2">
-        <v>0.5</v>
+        <v>3.5</v>
       </c>
       <c r="I57" t="str">
         <f t="shared" si="2"/>
-        <v>E[_]SPV*</v>
+        <v>E[_]WOF*</v>
       </c>
       <c r="L57" t="str">
-        <f t="shared" ref="L57" si="7">L53</f>
-        <v>Solar photovoltaics - Large scale unit</v>
+        <f t="shared" ref="L57" si="8">L53</f>
+        <v>Wind offshore</v>
       </c>
       <c r="M57" t="str">
         <f t="shared" si="1"/>
-        <v>E[_]SPV*</v>
+        <v>E[_]WOF*</v>
       </c>
     </row>
     <row r="58" spans="2:13" x14ac:dyDescent="0.35">
@@ -1592,193 +1604,164 @@
         <v>23</v>
       </c>
       <c r="E58" s="2">
-        <v>5</v>
+        <v>1.5</v>
       </c>
       <c r="F58" s="2">
-        <v>3.5</v>
+        <v>1.5</v>
       </c>
       <c r="G58" s="2">
-        <v>3.5</v>
+        <v>1.5</v>
       </c>
       <c r="H58" s="2">
-        <v>3.5</v>
+        <v>1.5</v>
       </c>
       <c r="I58" t="str">
         <f t="shared" si="2"/>
-        <v>E[_]WOF*</v>
+        <v>E[_]WON*</v>
       </c>
       <c r="L58" t="str">
-        <f t="shared" ref="L58" si="8">L54</f>
-        <v>Wind offshore</v>
+        <f t="shared" ref="L58" si="9">L54</f>
+        <v>Wind onshore</v>
       </c>
       <c r="M58" t="str">
         <f t="shared" si="1"/>
-        <v>E[_]WOF*</v>
+        <v>E[_]WON*</v>
       </c>
     </row>
     <row r="59" spans="2:13" x14ac:dyDescent="0.35">
       <c r="D59" s="2" t="s">
-        <v>23</v>
+        <v>47</v>
       </c>
       <c r="E59" s="2">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="F59" s="2">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="G59" s="2">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="H59" s="2">
-        <v>1.5</v>
-      </c>
-      <c r="I59" t="str">
-        <f t="shared" si="2"/>
-        <v>E[_]WON*</v>
-      </c>
-      <c r="L59" t="str">
-        <f t="shared" ref="L59" si="9">L55</f>
-        <v>Wind onshore</v>
-      </c>
-      <c r="M59" t="str">
-        <f t="shared" si="1"/>
-        <v>E[_]WON*</v>
+        <v>0</v>
+      </c>
+      <c r="I59" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="60" spans="2:13" x14ac:dyDescent="0.35">
       <c r="D60" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E60" s="2">
-        <v>0</v>
+        <v>4.41</v>
       </c>
       <c r="F60" s="2">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="G60" s="2">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="H60" s="2">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="I60" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="61" spans="2:13" x14ac:dyDescent="0.35">
       <c r="D61" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E61" s="2">
-        <v>4.41</v>
+        <v>2.06</v>
       </c>
       <c r="F61" s="2">
-        <v>3.45</v>
+        <v>1.98</v>
       </c>
       <c r="G61" s="2">
-        <v>3.16</v>
+        <v>1.89</v>
       </c>
       <c r="H61" s="2">
-        <v>2.99</v>
+        <v>1.85</v>
       </c>
       <c r="I61" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="62" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="D62" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="E62" s="2">
-        <v>2.06</v>
-      </c>
-      <c r="F62" s="2">
-        <v>1.98</v>
-      </c>
-      <c r="G62" s="2">
-        <v>1.89</v>
-      </c>
-      <c r="H62" s="2">
-        <v>1.85</v>
-      </c>
-      <c r="I62" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="64" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="B64" s="7" t="s">
+    <row r="63" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B63" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="C64" s="4"/>
-      <c r="D64" s="4"/>
-      <c r="E64" s="4"/>
-    </row>
-    <row r="65" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B65" s="12" t="s">
-        <v>69</v>
-      </c>
-      <c r="C65" s="12" t="s">
+      <c r="C63" s="4"/>
+      <c r="D63" s="4"/>
+      <c r="E63" s="4"/>
+    </row>
+    <row r="64" spans="2:13" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B64" s="12" t="s">
+        <v>68</v>
+      </c>
+      <c r="C64" s="12" t="s">
+        <v>70</v>
+      </c>
+      <c r="D64" s="12" t="s">
         <v>71</v>
       </c>
-      <c r="D65" s="12" t="s">
-        <v>72</v>
-      </c>
-      <c r="E65" s="14"/>
-      <c r="F65" s="14"/>
-      <c r="J65" s="13"/>
-    </row>
-    <row r="66" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="E64" s="14"/>
+      <c r="F64" s="14"/>
+      <c r="J64" s="13"/>
+    </row>
+    <row r="65" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B65" t="s">
+        <v>13</v>
+      </c>
+      <c r="C65" t="s">
+        <v>37</v>
+      </c>
+      <c r="D65" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="66" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B66" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C66" t="s">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="D66" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="67" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="67" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B67" t="s">
-        <v>14</v>
+        <v>33</v>
       </c>
       <c r="C67" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="D67" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="68" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="68" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B68" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C68" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="D68" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="69" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="69" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B69" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C69" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D69" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="70" spans="2:10" x14ac:dyDescent="0.35">
-      <c r="B70" t="s">
-        <v>32</v>
-      </c>
-      <c r="C70" t="s">
-        <v>45</v>
-      </c>
-      <c r="D70" t="s">
         <v>20</v>
       </c>
     </row>

--- a/VerveStacks_EST/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
+++ b/VerveStacks_EST/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\PycharmProjects\ee-times\VerveStacks_EST\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B24621C-47C9-4BB7-9FBD-A9B12784A57F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D32F304-E7C5-4C8B-B1EB-C0CA94F1406C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="40" windowWidth="19200" windowHeight="11240" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="AVA" sheetId="6" r:id="rId1"/>
@@ -44,7 +44,7 @@
     <author>tc={9326A9B6-D94C-4ED3-9FB8-434C0D4AC388}</author>
   </authors>
   <commentList>
-    <comment ref="I48" authorId="0" shapeId="0" xr:uid="{80A2C193-6148-4AA7-9B62-06322F60E0BF}">
+    <comment ref="I53" authorId="0" shapeId="0" xr:uid="{80A2C193-6148-4AA7-9B62-06322F60E0BF}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -52,7 +52,7 @@
     Utility-scale PV</t>
       </text>
     </comment>
-    <comment ref="I49" authorId="1" shapeId="0" xr:uid="{E6F93F18-BBEF-4E19-B2D0-A493D668847A}">
+    <comment ref="I54" authorId="1" shapeId="0" xr:uid="{E6F93F18-BBEF-4E19-B2D0-A493D668847A}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -60,7 +60,7 @@
     AC fixed</t>
       </text>
     </comment>
-    <comment ref="I60" authorId="2" shapeId="0" xr:uid="{9326A9B6-D94C-4ED3-9FB8-434C0D4AC388}">
+    <comment ref="I65" authorId="2" shapeId="0" xr:uid="{9326A9B6-D94C-4ED3-9FB8-434C0D4AC388}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -744,13 +744,13 @@
 
 <file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
 <ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <threadedComment ref="I48" dT="2026-03-18T13:56:27.06" personId="{50AE587C-9924-43E9-9BB9-052BDB346AE2}" id="{80A2C193-6148-4AA7-9B62-06322F60E0BF}">
+  <threadedComment ref="I53" dT="2026-03-18T13:56:27.06" personId="{50AE587C-9924-43E9-9BB9-052BDB346AE2}" id="{80A2C193-6148-4AA7-9B62-06322F60E0BF}">
     <text>Utility-scale PV</text>
   </threadedComment>
-  <threadedComment ref="I49" dT="2026-03-18T13:39:46.05" personId="{50AE587C-9924-43E9-9BB9-052BDB346AE2}" id="{E6F93F18-BBEF-4E19-B2D0-A493D668847A}">
+  <threadedComment ref="I54" dT="2026-03-18T13:39:46.05" personId="{50AE587C-9924-43E9-9BB9-052BDB346AE2}" id="{E6F93F18-BBEF-4E19-B2D0-A493D668847A}">
     <text>AC fixed</text>
   </threadedComment>
-  <threadedComment ref="I60" dT="2026-03-18T13:39:46.05" personId="{50AE587C-9924-43E9-9BB9-052BDB346AE2}" id="{9326A9B6-D94C-4ED3-9FB8-434C0D4AC388}">
+  <threadedComment ref="I65" dT="2026-03-18T13:39:46.05" personId="{50AE587C-9924-43E9-9BB9-052BDB346AE2}" id="{9326A9B6-D94C-4ED3-9FB8-434C0D4AC388}">
     <text>AC fixed</text>
   </threadedComment>
 </ThreadedComments>
@@ -795,7 +795,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="B2:V69"/>
+  <dimension ref="B2:V74"/>
   <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="14.1796875" bestFit="1" customWidth="1"/>
@@ -1024,7 +1024,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="17" spans="2:18" x14ac:dyDescent="0.35">
+    <row r="17" spans="4:18" x14ac:dyDescent="0.35">
       <c r="D17" t="s">
         <v>8</v>
       </c>
@@ -1035,7 +1035,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="18" spans="2:18" x14ac:dyDescent="0.35">
+    <row r="18" spans="4:18" x14ac:dyDescent="0.35">
       <c r="D18" t="s">
         <v>9</v>
       </c>
@@ -1046,7 +1046,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="19" spans="2:18" x14ac:dyDescent="0.35">
+    <row r="19" spans="4:18" x14ac:dyDescent="0.35">
       <c r="D19" t="s">
         <v>5</v>
       </c>
@@ -1057,12 +1057,12 @@
         <v>38</v>
       </c>
     </row>
-    <row r="20" spans="2:18" x14ac:dyDescent="0.35">
+    <row r="20" spans="4:18" x14ac:dyDescent="0.35">
       <c r="D20" s="11" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="21" spans="2:18" x14ac:dyDescent="0.35">
+    <row r="21" spans="4:18" x14ac:dyDescent="0.35">
       <c r="D21" t="s">
         <v>5</v>
       </c>
@@ -1073,7 +1073,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="22" spans="2:18" x14ac:dyDescent="0.35">
+    <row r="22" spans="4:18" x14ac:dyDescent="0.35">
       <c r="D22" t="s">
         <v>7</v>
       </c>
@@ -1084,7 +1084,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="23" spans="2:18" x14ac:dyDescent="0.35">
+    <row r="23" spans="4:18" x14ac:dyDescent="0.35">
       <c r="D23" t="s">
         <v>16</v>
       </c>
@@ -1095,673 +1095,679 @@
         <v>15</v>
       </c>
     </row>
-    <row r="24" spans="2:18" x14ac:dyDescent="0.35">
+    <row r="24" spans="4:18" x14ac:dyDescent="0.35">
       <c r="D24" t="s">
+        <v>11</v>
+      </c>
+      <c r="E24">
+        <v>0</v>
+      </c>
+      <c r="F24">
+        <v>3</v>
+      </c>
+      <c r="I24" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="25" spans="4:18" x14ac:dyDescent="0.35">
+      <c r="D25" t="s">
         <v>6</v>
       </c>
-      <c r="F24">
+      <c r="F25">
         <v>200</v>
-      </c>
-      <c r="J24" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="25" spans="2:18" x14ac:dyDescent="0.35">
-      <c r="D25" t="s">
-        <v>9</v>
-      </c>
-      <c r="F25">
-        <v>30</v>
       </c>
       <c r="J25" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="26" spans="2:18" x14ac:dyDescent="0.35">
+    <row r="26" spans="4:18" x14ac:dyDescent="0.35">
       <c r="D26" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F26">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="J26" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="27" spans="2:18" x14ac:dyDescent="0.35">
+    <row r="27" spans="4:18" x14ac:dyDescent="0.35">
       <c r="D27" t="s">
-        <v>11</v>
-      </c>
-      <c r="E27">
+        <v>8</v>
+      </c>
+      <c r="F27">
+        <v>1</v>
+      </c>
+      <c r="J27" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="28" spans="4:18" x14ac:dyDescent="0.35">
+      <c r="R28" s="2"/>
+    </row>
+    <row r="29" spans="4:18" x14ac:dyDescent="0.35">
+      <c r="R29" s="2"/>
+    </row>
+    <row r="33" spans="2:18" x14ac:dyDescent="0.35">
+      <c r="R33" s="2"/>
+    </row>
+    <row r="34" spans="2:18" x14ac:dyDescent="0.35">
+      <c r="R34" s="2"/>
+    </row>
+    <row r="37" spans="2:18" x14ac:dyDescent="0.35">
+      <c r="B37" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C37" s="4"/>
+      <c r="D37" s="4"/>
+      <c r="E37" s="4"/>
+    </row>
+    <row r="38" spans="2:18" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B38" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="C38" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="D38" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="F27">
-        <v>3</v>
-      </c>
-      <c r="I27" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="28" spans="2:18" x14ac:dyDescent="0.35">
-      <c r="R28" s="2"/>
-    </row>
-    <row r="29" spans="2:18" x14ac:dyDescent="0.35">
-      <c r="R29" s="2"/>
-    </row>
-    <row r="32" spans="2:18" x14ac:dyDescent="0.35">
-      <c r="B32" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="C32" s="4"/>
-      <c r="D32" s="4"/>
-      <c r="E32" s="4"/>
-    </row>
-    <row r="33" spans="2:13" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B33" s="8" t="s">
+      <c r="E38" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="F38" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="G38" s="12" t="s">
+        <v>68</v>
+      </c>
+      <c r="H38" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="I38" s="9" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="39" spans="2:18" x14ac:dyDescent="0.35">
+      <c r="D39" t="s">
+        <v>40</v>
+      </c>
+      <c r="F39">
+        <v>2030</v>
+      </c>
+      <c r="G39" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="40" spans="2:18" x14ac:dyDescent="0.35">
+      <c r="D40" t="s">
+        <v>40</v>
+      </c>
+      <c r="F40">
+        <v>2035</v>
+      </c>
+      <c r="G40" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="41" spans="2:18" x14ac:dyDescent="0.35">
+      <c r="D41" t="s">
+        <v>40</v>
+      </c>
+      <c r="F41">
+        <v>2036</v>
+      </c>
+      <c r="G41" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="42" spans="2:18" x14ac:dyDescent="0.35">
+      <c r="D42" t="s">
+        <v>40</v>
+      </c>
+      <c r="F42">
+        <v>2030</v>
+      </c>
+      <c r="G42" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="43" spans="2:18" x14ac:dyDescent="0.35">
+      <c r="D43" t="s">
+        <v>40</v>
+      </c>
+      <c r="F43">
+        <v>2030</v>
+      </c>
+      <c r="H43" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="I43" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="44" spans="2:18" x14ac:dyDescent="0.35">
+      <c r="D44" t="s">
+        <v>42</v>
+      </c>
+      <c r="F44">
+        <v>40</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="I44" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="50" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B50" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="C50" s="4"/>
+      <c r="D50" s="4"/>
+      <c r="E50" s="4"/>
+    </row>
+    <row r="51" spans="2:13" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B51" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="C33" s="8" t="s">
+      <c r="C51" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="D33" s="8" t="s">
+      <c r="D51" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="E33" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="F33" s="10" t="s">
-        <v>67</v>
-      </c>
-      <c r="G33" s="12" t="s">
+      <c r="E51" s="10">
+        <v>2023</v>
+      </c>
+      <c r="F51" s="10">
+        <v>2030</v>
+      </c>
+      <c r="G51" s="10">
+        <v>2040</v>
+      </c>
+      <c r="H51" s="10">
+        <v>2050</v>
+      </c>
+      <c r="I51" s="12" t="s">
         <v>68</v>
       </c>
-      <c r="H33" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="I33" s="9" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="34" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="D34" t="s">
-        <v>40</v>
-      </c>
-      <c r="F34">
-        <v>2030</v>
-      </c>
-      <c r="G34" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="35" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="D35" t="s">
-        <v>40</v>
-      </c>
-      <c r="F35">
-        <v>2035</v>
-      </c>
-      <c r="G35" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="36" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="D36" t="s">
-        <v>40</v>
-      </c>
-      <c r="F36">
-        <v>2036</v>
-      </c>
-      <c r="G36" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="37" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="D37" t="s">
-        <v>40</v>
-      </c>
-      <c r="F37">
-        <v>2030</v>
-      </c>
-      <c r="G37" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="38" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="D38" t="s">
-        <v>40</v>
-      </c>
-      <c r="F38">
-        <v>2030</v>
-      </c>
-      <c r="H38" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="I38" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="39" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="D39" t="s">
-        <v>42</v>
-      </c>
-      <c r="F39">
-        <v>40</v>
-      </c>
-      <c r="H39" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="I39" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="45" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="B45" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="C45" s="4"/>
-      <c r="D45" s="4"/>
-      <c r="E45" s="4"/>
-    </row>
-    <row r="46" spans="2:13" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B46" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="C46" s="8" t="s">
-        <v>2</v>
-      </c>
-      <c r="D46" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="E46" s="10">
-        <v>2023</v>
-      </c>
-      <c r="F46" s="10">
-        <v>2030</v>
-      </c>
-      <c r="G46" s="10">
-        <v>2040</v>
-      </c>
-      <c r="H46" s="10">
-        <v>2050</v>
-      </c>
-      <c r="I46" s="12" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="47" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="D47" s="2" t="s">
+    </row>
+    <row r="52" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="D52" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="E47" s="2">
+      <c r="E52" s="2">
         <v>2700</v>
       </c>
-      <c r="F47" s="2">
+      <c r="F52" s="2">
         <v>2700</v>
       </c>
-      <c r="G47" s="2">
+      <c r="G52" s="2">
         <v>2700</v>
       </c>
-      <c r="H47" s="2">
+      <c r="H52" s="2">
         <v>2700</v>
       </c>
-      <c r="I47" t="str">
-        <f>M47</f>
+      <c r="I52" t="str">
+        <f>M52</f>
         <v>EN[_]Hydro*</v>
       </c>
-      <c r="L47" t="s">
+      <c r="L52" t="s">
         <v>24</v>
       </c>
-      <c r="M47" t="s">
+      <c r="M52" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="48" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="D48" s="2" t="s">
+    <row r="53" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="D53" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="E48" s="2">
+      <c r="E53" s="2">
         <v>560</v>
       </c>
-      <c r="F48" s="2">
+      <c r="F53" s="2">
         <v>380</v>
       </c>
-      <c r="G48">
+      <c r="G53">
         <v>320</v>
       </c>
-      <c r="H48" s="2">
+      <c r="H53" s="2">
         <v>290</v>
       </c>
-      <c r="I48" t="str">
-        <f t="shared" ref="I48:I50" si="0">M48</f>
+      <c r="I53" t="str">
+        <f t="shared" ref="I53:I55" si="0">M53</f>
         <v>E[_]SPV*</v>
       </c>
-      <c r="L48" t="s">
+      <c r="L53" t="s">
         <v>25</v>
       </c>
-      <c r="M48" t="s">
+      <c r="M53" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="49" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="D49" s="2" t="s">
+    <row r="54" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="D54" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="E49" s="2">
+      <c r="E54" s="2">
         <v>2780</v>
       </c>
-      <c r="F49" s="2">
+      <c r="F54" s="2">
         <v>2390</v>
       </c>
-      <c r="G49" s="2">
+      <c r="G54" s="2">
         <v>2140</v>
       </c>
-      <c r="H49" s="2">
+      <c r="H54" s="2">
         <v>1990</v>
       </c>
-      <c r="I49" t="str">
+      <c r="I54" t="str">
         <f t="shared" si="0"/>
         <v>E[_]WOF*</v>
       </c>
-      <c r="L49" t="s">
+      <c r="L54" t="s">
         <v>26</v>
       </c>
-      <c r="M49" t="s">
+      <c r="M54" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="50" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="D50" s="2" t="s">
+    <row r="55" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="D55" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="E50" s="2">
+      <c r="E55" s="2">
         <v>1180</v>
       </c>
-      <c r="F50" s="2">
+      <c r="F55" s="2">
         <v>1150</v>
       </c>
-      <c r="G50" s="2">
+      <c r="G55" s="2">
         <v>1110</v>
       </c>
-      <c r="H50" s="2">
+      <c r="H55" s="2">
         <v>1090</v>
       </c>
-      <c r="I50" t="str">
+      <c r="I55" t="str">
         <f t="shared" si="0"/>
         <v>E[_]WON*</v>
       </c>
-      <c r="L50" t="s">
+      <c r="L55" t="s">
         <v>27</v>
       </c>
-      <c r="M50" t="s">
+      <c r="M55" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="51" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="D51" s="2" t="s">
+    <row r="56" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="D56" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="E51" s="2">
+      <c r="E56" s="2">
         <v>70</v>
       </c>
-      <c r="F51" s="2">
+      <c r="F56" s="2">
         <v>65</v>
       </c>
-      <c r="G51" s="2">
+      <c r="G56" s="2">
         <v>65</v>
       </c>
-      <c r="H51" s="2">
+      <c r="H56" s="2">
         <v>65</v>
       </c>
-      <c r="I51" t="str">
-        <f>I47</f>
+      <c r="I56" t="str">
+        <f>I52</f>
         <v>EN[_]Hydro*</v>
       </c>
-      <c r="L51" t="str">
-        <f>L47</f>
+      <c r="L56" t="str">
+        <f>L52</f>
         <v>Hydropower - large-scale unit</v>
       </c>
-      <c r="M51" t="str">
-        <f t="shared" ref="M51:M58" si="1">M47</f>
+      <c r="M56" t="str">
+        <f t="shared" ref="M56:M63" si="1">M52</f>
         <v>EN[_]Hydro*</v>
       </c>
     </row>
-    <row r="52" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="D52" s="2" t="s">
+    <row r="57" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="D57" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="E52" s="2">
+      <c r="E57" s="2">
         <v>11.5</v>
       </c>
-      <c r="F52" s="2">
+      <c r="F57" s="2">
         <v>9.5</v>
       </c>
-      <c r="G52" s="2">
+      <c r="G57" s="2">
         <v>8.1</v>
       </c>
-      <c r="H52" s="2">
+      <c r="H57" s="2">
         <v>7.4</v>
       </c>
-      <c r="I52" t="str">
-        <f t="shared" ref="I52:I58" si="2">I48</f>
+      <c r="I57" t="str">
+        <f t="shared" ref="I57:I63" si="2">I53</f>
         <v>E[_]SPV*</v>
       </c>
-      <c r="L52" t="str">
-        <f t="shared" ref="L52" si="3">L48</f>
+      <c r="L57" t="str">
+        <f t="shared" ref="L57" si="3">L53</f>
         <v>Solar photovoltaics - Large scale unit</v>
       </c>
-      <c r="M52" t="str">
+      <c r="M57" t="str">
         <f t="shared" si="1"/>
         <v>E[_]SPV*</v>
       </c>
     </row>
-    <row r="53" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="D53" s="2" t="s">
+    <row r="58" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="D58" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="E53" s="2">
+      <c r="E58" s="2">
         <v>44</v>
       </c>
-      <c r="F53" s="2">
+      <c r="F58" s="2">
         <v>34</v>
       </c>
-      <c r="G53" s="2">
+      <c r="G58" s="2">
         <v>30</v>
       </c>
-      <c r="H53" s="2">
+      <c r="H58" s="2">
         <v>28</v>
       </c>
-      <c r="I53" t="str">
+      <c r="I58" t="str">
         <f t="shared" si="2"/>
         <v>E[_]WOF*</v>
       </c>
-      <c r="L53" t="str">
-        <f t="shared" ref="L53" si="4">L49</f>
+      <c r="L58" t="str">
+        <f t="shared" ref="L58" si="4">L54</f>
         <v>Wind offshore</v>
       </c>
-      <c r="M53" t="str">
+      <c r="M58" t="str">
         <f t="shared" si="1"/>
         <v>E[_]WOF*</v>
       </c>
     </row>
-    <row r="54" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="D54" s="2" t="s">
+    <row r="59" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="D59" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="E54" s="2">
+      <c r="E59" s="2">
         <v>17.387</v>
       </c>
-      <c r="F54" s="2">
+      <c r="F59" s="2">
         <v>16.663</v>
       </c>
-      <c r="G54" s="2">
+      <c r="G59" s="2">
         <v>15.965</v>
       </c>
-      <c r="H54" s="2">
+      <c r="H59" s="2">
         <v>15.602</v>
       </c>
-      <c r="I54" t="str">
+      <c r="I59" t="str">
         <f t="shared" si="2"/>
         <v>E[_]WON*</v>
       </c>
-      <c r="L54" t="str">
-        <f t="shared" ref="L54" si="5">L50</f>
+      <c r="L59" t="str">
+        <f t="shared" ref="L59" si="5">L55</f>
         <v>Wind onshore</v>
       </c>
-      <c r="M54" t="str">
+      <c r="M59" t="str">
         <f t="shared" si="1"/>
         <v>E[_]WON*</v>
       </c>
     </row>
-    <row r="55" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="D55" s="2" t="s">
+    <row r="60" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="D60" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="E55" s="2">
+      <c r="E60" s="2">
         <v>4</v>
       </c>
-      <c r="F55" s="2">
+      <c r="F60" s="2">
         <v>4</v>
       </c>
-      <c r="G55" s="2">
+      <c r="G60" s="2">
         <v>4</v>
       </c>
-      <c r="H55" s="2">
+      <c r="H60" s="2">
         <v>4</v>
       </c>
-      <c r="I55" t="str">
+      <c r="I60" t="str">
         <f t="shared" si="2"/>
         <v>EN[_]Hydro*</v>
       </c>
-      <c r="L55" t="str">
-        <f t="shared" ref="L55" si="6">L51</f>
+      <c r="L60" t="str">
+        <f t="shared" ref="L60" si="6">L56</f>
         <v>Hydropower - large-scale unit</v>
       </c>
-      <c r="M55" t="str">
+      <c r="M60" t="str">
         <f t="shared" si="1"/>
         <v>EN[_]Hydro*</v>
       </c>
     </row>
-    <row r="56" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="D56" s="2" t="s">
+    <row r="61" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="D61" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="E56" s="2">
+      <c r="E61" s="2">
         <v>0.5</v>
       </c>
-      <c r="F56" s="2">
+      <c r="F61" s="2">
         <v>0.5</v>
       </c>
-      <c r="G56" s="2">
+      <c r="G61" s="2">
         <v>0.5</v>
       </c>
-      <c r="H56" s="2">
+      <c r="H61" s="2">
         <v>0.5</v>
       </c>
-      <c r="I56" t="str">
+      <c r="I61" t="str">
         <f t="shared" si="2"/>
         <v>E[_]SPV*</v>
       </c>
-      <c r="L56" t="str">
-        <f t="shared" ref="L56" si="7">L52</f>
+      <c r="L61" t="str">
+        <f t="shared" ref="L61" si="7">L57</f>
         <v>Solar photovoltaics - Large scale unit</v>
       </c>
-      <c r="M56" t="str">
+      <c r="M61" t="str">
         <f t="shared" si="1"/>
         <v>E[_]SPV*</v>
       </c>
     </row>
-    <row r="57" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="D57" s="2" t="s">
+    <row r="62" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="D62" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="E57" s="2">
+      <c r="E62" s="2">
         <v>5</v>
       </c>
-      <c r="F57" s="2">
+      <c r="F62" s="2">
         <v>3.5</v>
       </c>
-      <c r="G57" s="2">
+      <c r="G62" s="2">
         <v>3.5</v>
       </c>
-      <c r="H57" s="2">
+      <c r="H62" s="2">
         <v>3.5</v>
       </c>
-      <c r="I57" t="str">
+      <c r="I62" t="str">
         <f t="shared" si="2"/>
         <v>E[_]WOF*</v>
       </c>
-      <c r="L57" t="str">
-        <f t="shared" ref="L57" si="8">L53</f>
+      <c r="L62" t="str">
+        <f t="shared" ref="L62" si="8">L58</f>
         <v>Wind offshore</v>
       </c>
-      <c r="M57" t="str">
+      <c r="M62" t="str">
         <f t="shared" si="1"/>
         <v>E[_]WOF*</v>
       </c>
     </row>
-    <row r="58" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="D58" s="2" t="s">
+    <row r="63" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="D63" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="E58" s="2">
+      <c r="E63" s="2">
         <v>1.5</v>
       </c>
-      <c r="F58" s="2">
+      <c r="F63" s="2">
         <v>1.5</v>
       </c>
-      <c r="G58" s="2">
+      <c r="G63" s="2">
         <v>1.5</v>
       </c>
-      <c r="H58" s="2">
+      <c r="H63" s="2">
         <v>1.5</v>
       </c>
-      <c r="I58" t="str">
+      <c r="I63" t="str">
         <f t="shared" si="2"/>
         <v>E[_]WON*</v>
       </c>
-      <c r="L58" t="str">
-        <f t="shared" ref="L58" si="9">L54</f>
+      <c r="L63" t="str">
+        <f t="shared" ref="L63" si="9">L59</f>
         <v>Wind onshore</v>
       </c>
-      <c r="M58" t="str">
+      <c r="M63" t="str">
         <f t="shared" si="1"/>
         <v>E[_]WON*</v>
       </c>
     </row>
-    <row r="59" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="D59" s="2" t="s">
+    <row r="64" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="D64" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="E59" s="2">
+      <c r="E64" s="2">
         <v>0</v>
       </c>
-      <c r="F59" s="2">
+      <c r="F64" s="2">
         <v>0</v>
       </c>
-      <c r="G59" s="2">
+      <c r="G64" s="2">
         <v>0</v>
       </c>
-      <c r="H59" s="2">
+      <c r="H64" s="2">
         <v>0</v>
       </c>
-      <c r="I59" t="s">
+      <c r="I64" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="60" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="D60" s="2" t="s">
+    <row r="65" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="D65" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="E60" s="2">
+      <c r="E65" s="2">
         <v>4.41</v>
       </c>
-      <c r="F60" s="2">
+      <c r="F65" s="2">
         <v>3.45</v>
       </c>
-      <c r="G60" s="2">
+      <c r="G65" s="2">
         <v>3.16</v>
       </c>
-      <c r="H60" s="2">
+      <c r="H65" s="2">
         <v>2.99</v>
       </c>
-      <c r="I60" t="s">
+      <c r="I65" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="61" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="D61" s="2" t="s">
+    <row r="66" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="D66" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="E61" s="2">
+      <c r="E66" s="2">
         <v>2.06</v>
       </c>
-      <c r="F61" s="2">
+      <c r="F66" s="2">
         <v>1.98</v>
       </c>
-      <c r="G61" s="2">
+      <c r="G66" s="2">
         <v>1.89</v>
       </c>
-      <c r="H61" s="2">
+      <c r="H66" s="2">
         <v>1.85</v>
       </c>
-      <c r="I61" t="s">
+      <c r="I66" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="63" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="B63" s="7" t="s">
+    <row r="68" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="B68" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="C63" s="4"/>
-      <c r="D63" s="4"/>
-      <c r="E63" s="4"/>
-    </row>
-    <row r="64" spans="2:13" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B64" s="12" t="s">
+      <c r="C68" s="4"/>
+      <c r="D68" s="4"/>
+      <c r="E68" s="4"/>
+    </row>
+    <row r="69" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B69" s="12" t="s">
         <v>68</v>
       </c>
-      <c r="C64" s="12" t="s">
+      <c r="C69" s="12" t="s">
         <v>70</v>
       </c>
-      <c r="D64" s="12" t="s">
+      <c r="D69" s="12" t="s">
         <v>71</v>
       </c>
-      <c r="E64" s="14"/>
-      <c r="F64" s="14"/>
-      <c r="J64" s="13"/>
-    </row>
-    <row r="65" spans="2:4" x14ac:dyDescent="0.35">
-      <c r="B65" t="s">
+      <c r="E69" s="14"/>
+      <c r="F69" s="14"/>
+      <c r="J69" s="13"/>
+    </row>
+    <row r="70" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="B70" t="s">
         <v>13</v>
       </c>
-      <c r="C65" t="s">
+      <c r="C70" t="s">
         <v>37</v>
       </c>
-      <c r="D65" t="s">
+      <c r="D70" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="66" spans="2:4" x14ac:dyDescent="0.35">
-      <c r="B66" t="s">
+    <row r="71" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="B71" t="s">
         <v>14</v>
       </c>
-      <c r="C66" t="s">
+      <c r="C71" t="s">
         <v>46</v>
       </c>
-      <c r="D66" t="s">
+      <c r="D71" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="67" spans="2:4" x14ac:dyDescent="0.35">
-      <c r="B67" t="s">
+    <row r="72" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="B72" t="s">
         <v>33</v>
       </c>
-      <c r="C67" t="s">
+      <c r="C72" t="s">
         <v>39</v>
       </c>
-      <c r="D67" t="s">
+      <c r="D72" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="68" spans="2:4" x14ac:dyDescent="0.35">
-      <c r="B68" t="s">
+    <row r="73" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="B73" t="s">
         <v>31</v>
       </c>
-      <c r="C68" t="s">
+      <c r="C73" t="s">
         <v>44</v>
       </c>
-      <c r="D68" t="s">
+      <c r="D73" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="69" spans="2:4" x14ac:dyDescent="0.35">
-      <c r="B69" t="s">
+    <row r="74" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="B74" t="s">
         <v>32</v>
       </c>
-      <c r="C69" t="s">
+      <c r="C74" t="s">
         <v>45</v>
       </c>
-      <c r="D69" t="s">
+      <c r="D74" t="s">
         <v>20</v>
       </c>
     </row>
